--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\ViewerSample\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E7C988D-38C0-4807-BCFB-04E79DC5E258}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E9AC98-041E-490F-9DB5-6DA2D691FFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1785" yWindow="3555" windowWidth="50490" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="420" yWindow="2670" windowWidth="56160" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -501,7 +501,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="32">
+  <fills count="31">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -656,12 +656,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1448,7 +1442,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1707,6 +1701,27 @@
     <xf numFmtId="176" fontId="5" fillId="29" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1723,33 +1738,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="30" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="31" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2516,11 +2504,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="86" t="s">
+      <c r="B3" s="93" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="88"/>
-      <c r="D3" s="89"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="96"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2615,9 +2603,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="87"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="91"/>
+      <c r="B4" s="94"/>
+      <c r="C4" s="97"/>
+      <c r="D4" s="98"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2784,7 +2772,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="92" t="s">
+      <c r="D5" s="90" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2845,7 +2833,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="93"/>
+      <c r="D6" s="91"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2904,7 +2892,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="92" t="s">
+      <c r="D7" s="90" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2965,7 +2953,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="93"/>
+      <c r="D8" s="91"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3024,7 +3012,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="92" t="s">
+      <c r="D9" s="90" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3085,7 +3073,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="93"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3144,7 +3132,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="92" t="s">
+      <c r="D11" s="90" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3205,7 +3193,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="93"/>
+      <c r="D12" s="91"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3264,7 +3252,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="92" t="s">
+      <c r="D13" s="90" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3325,7 +3313,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="93"/>
+      <c r="D14" s="91"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3386,7 +3374,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="92" t="s">
+      <c r="D15" s="90" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3447,7 +3435,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="93"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3506,7 +3494,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="92" t="s">
+      <c r="D17" s="90" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3567,7 +3555,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="93"/>
+      <c r="D18" s="91"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3628,7 +3616,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="92" t="s">
+      <c r="D19" s="90" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3689,7 +3677,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="93"/>
+      <c r="D20" s="91"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3748,7 +3736,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="92" t="s">
+      <c r="D21" s="90" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3809,7 +3797,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="93"/>
+      <c r="D22" s="91"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3824,7 +3812,7 @@
       <c r="N22" s="77"/>
       <c r="O22" s="78"/>
       <c r="P22" s="78"/>
-      <c r="Q22" s="96">
+      <c r="Q22" s="81">
         <v>45946</v>
       </c>
       <c r="R22" s="21"/>
@@ -3870,7 +3858,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="92" t="s">
+      <c r="D23" s="90" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3931,7 +3919,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="93"/>
+      <c r="D24" s="91"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -3990,7 +3978,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="92" t="s">
+      <c r="D25" s="90" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4051,7 +4039,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="93"/>
+      <c r="D26" s="91"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4110,7 +4098,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="92" t="s">
+      <c r="D27" s="90" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4171,7 +4159,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="93"/>
+      <c r="D28" s="91"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4232,7 +4220,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="92" t="s">
+      <c r="D29" s="90" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4293,7 +4281,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="93"/>
+      <c r="D30" s="91"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4352,7 +4340,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="92" t="s">
+      <c r="D31" s="90" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4413,7 +4401,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="93"/>
+      <c r="D32" s="91"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4429,16 +4417,18 @@
       <c r="O32" s="78"/>
       <c r="P32" s="78"/>
       <c r="Q32" s="79"/>
-      <c r="R32" s="97"/>
-      <c r="S32" s="98"/>
-      <c r="T32" s="98"/>
-      <c r="U32" s="99"/>
-      <c r="V32" s="100"/>
-      <c r="W32" s="12"/>
-      <c r="X32" s="13"/>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="20"/>
-      <c r="AA32" s="14"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="78"/>
+      <c r="T32" s="78"/>
+      <c r="U32" s="80"/>
+      <c r="V32" s="79"/>
+      <c r="W32" s="86"/>
+      <c r="X32" s="87"/>
+      <c r="Y32" s="87"/>
+      <c r="Z32" s="88"/>
+      <c r="AA32" s="89" t="s">
+        <v>43</v>
+      </c>
       <c r="AB32" s="12"/>
       <c r="AC32" s="13"/>
       <c r="AD32" s="13"/>
@@ -4470,7 +4460,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="92" t="s">
+      <c r="D33" s="90" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4531,7 +4521,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="93"/>
+      <c r="D34" s="91"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4561,7 +4551,7 @@
       <c r="AC34" s="78"/>
       <c r="AD34" s="78"/>
       <c r="AE34" s="78"/>
-      <c r="AF34" s="95">
+      <c r="AF34" s="81">
         <v>45946</v>
       </c>
       <c r="AG34" s="12"/>
@@ -4590,10 +4580,12 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="92" t="s">
+      <c r="D35" s="90" t="s">
         <v>62</v>
       </c>
-      <c r="E35" s="55"/>
+      <c r="E35" s="54" t="s">
+        <v>33</v>
+      </c>
       <c r="F35" s="12"/>
       <c r="G35" s="13"/>
       <c r="H35" s="14"/>
@@ -4649,8 +4641,10 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="93"/>
-      <c r="E36" s="55"/>
+      <c r="D36" s="91"/>
+      <c r="E36" s="55" t="s">
+        <v>34</v>
+      </c>
       <c r="F36" s="12"/>
       <c r="G36" s="13"/>
       <c r="H36" s="14"/>
@@ -4706,7 +4700,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="92" t="s">
+      <c r="D37" s="90" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4766,7 +4760,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="93"/>
+      <c r="D38" s="91"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4787,11 +4781,11 @@
       <c r="T38" s="18"/>
       <c r="U38" s="25"/>
       <c r="V38" s="26"/>
-      <c r="W38" s="12"/>
-      <c r="X38" s="12"/>
-      <c r="Y38" s="13"/>
-      <c r="Z38" s="13"/>
-      <c r="AA38" s="14"/>
+      <c r="W38" s="86"/>
+      <c r="X38" s="86"/>
+      <c r="Y38" s="87"/>
+      <c r="Z38" s="87"/>
+      <c r="AA38" s="89"/>
       <c r="AB38" s="12"/>
       <c r="AC38" s="13"/>
       <c r="AD38" s="13"/>
@@ -4825,7 +4819,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="92" t="s">
+      <c r="D39" s="90" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4888,7 +4882,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="94"/>
+      <c r="D40" s="92"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4945,7 +4939,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="93"/>
+      <c r="D41" s="91"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -5002,7 +4996,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="92" t="s">
+      <c r="D42" s="90" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5065,7 +5059,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="93"/>
+      <c r="D43" s="91"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5122,7 +5116,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="92" t="s">
+      <c r="D44" s="90" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5183,7 +5177,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="93"/>
+      <c r="D45" s="91"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5240,7 +5234,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="92" t="s">
+      <c r="D46" s="90" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5301,7 +5295,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="93"/>
+      <c r="D47" s="91"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5358,7 +5352,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="92" t="s">
+      <c r="D48" s="90" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5419,7 +5413,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="93"/>
+      <c r="D49" s="91"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5476,7 +5470,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="92" t="s">
+      <c r="D50" s="90" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5537,7 +5531,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="93"/>
+      <c r="D51" s="91"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5594,7 +5588,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="92" t="s">
+      <c r="D52" s="90" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5655,7 +5649,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="93"/>
+      <c r="D53" s="91"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -8485,16 +8479,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8511,6 +8495,16 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62E9AC98-041E-490F-9DB5-6DA2D691FFC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74504FA8-C6EA-4BBE-9B7F-05D2ADDF3FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="2670" windowWidth="56160" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2325" yWindow="2205" windowWidth="56160" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -4786,11 +4786,13 @@
       <c r="Y38" s="87"/>
       <c r="Z38" s="87"/>
       <c r="AA38" s="89"/>
-      <c r="AB38" s="12"/>
-      <c r="AC38" s="13"/>
-      <c r="AD38" s="13"/>
-      <c r="AE38" s="13"/>
-      <c r="AF38" s="14"/>
+      <c r="AB38" s="86"/>
+      <c r="AC38" s="87"/>
+      <c r="AD38" s="87"/>
+      <c r="AE38" s="87"/>
+      <c r="AF38" s="89" t="s">
+        <v>43</v>
+      </c>
       <c r="AG38" s="12"/>
       <c r="AH38" s="12"/>
       <c r="AI38" s="13"/>
@@ -4960,11 +4962,11 @@
       <c r="T41" s="18"/>
       <c r="U41" s="25"/>
       <c r="V41" s="26"/>
-      <c r="W41" s="21"/>
-      <c r="X41" s="21"/>
-      <c r="Y41" s="18"/>
-      <c r="Z41" s="18"/>
-      <c r="AA41" s="26"/>
+      <c r="W41" s="86"/>
+      <c r="X41" s="86"/>
+      <c r="Y41" s="87"/>
+      <c r="Z41" s="87"/>
+      <c r="AA41" s="89"/>
       <c r="AB41" s="21"/>
       <c r="AC41" s="18"/>
       <c r="AD41" s="18"/>
@@ -5080,11 +5082,11 @@
       <c r="T43" s="18"/>
       <c r="U43" s="25"/>
       <c r="V43" s="26"/>
-      <c r="W43" s="21"/>
-      <c r="X43" s="21"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="26"/>
+      <c r="W43" s="86"/>
+      <c r="X43" s="86"/>
+      <c r="Y43" s="87"/>
+      <c r="Z43" s="87"/>
+      <c r="AA43" s="89"/>
       <c r="AB43" s="21"/>
       <c r="AC43" s="18"/>
       <c r="AD43" s="18"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74504FA8-C6EA-4BBE-9B7F-05D2ADDF3FD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79FCA85-36AB-4C66-BEB5-B2B9E432D6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2325" yWindow="2205" windowWidth="56160" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="2205" windowWidth="51180" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="64">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -274,6 +274,10 @@
   </si>
   <si>
     <t>MPR 3뷰 출력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>10월 22일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1442,7 +1446,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1713,6 +1717,24 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1722,22 +1744,16 @@
     <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2504,11 +2520,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="93" t="s">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="95"/>
-      <c r="D3" s="96"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2603,9 +2619,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="94"/>
-      <c r="C4" s="97"/>
-      <c r="D4" s="98"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2772,7 +2788,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="90" t="s">
+      <c r="D5" s="96" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2833,7 +2849,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="91"/>
+      <c r="D6" s="97"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2892,7 +2908,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="90" t="s">
+      <c r="D7" s="96" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2953,7 +2969,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="91"/>
+      <c r="D8" s="97"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3012,7 +3028,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="90" t="s">
+      <c r="D9" s="96" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3073,7 +3089,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="91"/>
+      <c r="D10" s="97"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3132,7 +3148,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="90" t="s">
+      <c r="D11" s="96" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3193,7 +3209,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="91"/>
+      <c r="D12" s="97"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3252,7 +3268,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="90" t="s">
+      <c r="D13" s="96" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3313,7 +3329,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="91"/>
+      <c r="D14" s="97"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3374,7 +3390,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="90" t="s">
+      <c r="D15" s="96" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3435,7 +3451,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="91"/>
+      <c r="D16" s="97"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3494,7 +3510,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="90" t="s">
+      <c r="D17" s="96" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3555,7 +3571,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="91"/>
+      <c r="D18" s="97"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3616,7 +3632,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="90" t="s">
+      <c r="D19" s="96" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3677,7 +3693,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="91"/>
+      <c r="D20" s="97"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3736,7 +3752,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="90" t="s">
+      <c r="D21" s="96" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3797,7 +3813,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="91"/>
+      <c r="D22" s="97"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3858,7 +3874,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="90" t="s">
+      <c r="D23" s="96" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3919,7 +3935,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="91"/>
+      <c r="D24" s="97"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -3978,7 +3994,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="90" t="s">
+      <c r="D25" s="96" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4039,7 +4055,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="91"/>
+      <c r="D26" s="97"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4098,7 +4114,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="90" t="s">
+      <c r="D27" s="96" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4159,7 +4175,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="91"/>
+      <c r="D28" s="97"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4220,7 +4236,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="90" t="s">
+      <c r="D29" s="96" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4281,7 +4297,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="91"/>
+      <c r="D30" s="97"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4340,7 +4356,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="90" t="s">
+      <c r="D31" s="96" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4401,7 +4417,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="91"/>
+      <c r="D32" s="97"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4460,7 +4476,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="90" t="s">
+      <c r="D33" s="96" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4521,7 +4537,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="91"/>
+      <c r="D34" s="97"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4580,7 +4596,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="90" t="s">
+      <c r="D35" s="96" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4641,7 +4657,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="91"/>
+      <c r="D36" s="97"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4700,7 +4716,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="90" t="s">
+      <c r="D37" s="96" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4760,7 +4776,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="91"/>
+      <c r="D38" s="97"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4821,7 +4837,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="90" t="s">
+      <c r="D39" s="96" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4884,7 +4900,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="92"/>
+      <c r="D40" s="98"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4941,7 +4957,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="91"/>
+      <c r="D41" s="97"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -4967,26 +4983,28 @@
       <c r="Y41" s="87"/>
       <c r="Z41" s="87"/>
       <c r="AA41" s="89"/>
-      <c r="AB41" s="21"/>
-      <c r="AC41" s="18"/>
-      <c r="AD41" s="18"/>
-      <c r="AE41" s="18"/>
-      <c r="AF41" s="26"/>
-      <c r="AG41" s="73"/>
-      <c r="AH41" s="73"/>
-      <c r="AI41" s="74"/>
-      <c r="AJ41" s="74"/>
-      <c r="AK41" s="75"/>
-      <c r="AL41" s="73"/>
-      <c r="AM41" s="74"/>
-      <c r="AN41" s="74"/>
-      <c r="AO41" s="76"/>
-      <c r="AP41" s="75"/>
-      <c r="AQ41" s="21"/>
-      <c r="AR41" s="21"/>
-      <c r="AS41" s="18"/>
-      <c r="AT41" s="18"/>
-      <c r="AU41" s="26"/>
+      <c r="AB41" s="86"/>
+      <c r="AC41" s="87"/>
+      <c r="AD41" s="87"/>
+      <c r="AE41" s="87"/>
+      <c r="AF41" s="89"/>
+      <c r="AG41" s="99"/>
+      <c r="AH41" s="99"/>
+      <c r="AI41" s="100"/>
+      <c r="AJ41" s="100"/>
+      <c r="AK41" s="101"/>
+      <c r="AL41" s="99"/>
+      <c r="AM41" s="100"/>
+      <c r="AN41" s="100"/>
+      <c r="AO41" s="102"/>
+      <c r="AP41" s="101"/>
+      <c r="AQ41" s="86"/>
+      <c r="AR41" s="86"/>
+      <c r="AS41" s="87"/>
+      <c r="AT41" s="87"/>
+      <c r="AU41" s="89" t="s">
+        <v>63</v>
+      </c>
       <c r="AY41" s="3"/>
       <c r="BD41" s="3"/>
       <c r="BH41" s="3"/>
@@ -4998,7 +5016,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="90" t="s">
+      <c r="D42" s="96" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5061,7 +5079,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="91"/>
+      <c r="D43" s="97"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5087,26 +5105,28 @@
       <c r="Y43" s="87"/>
       <c r="Z43" s="87"/>
       <c r="AA43" s="89"/>
-      <c r="AB43" s="21"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="26"/>
-      <c r="AG43" s="21"/>
-      <c r="AH43" s="21"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="26"/>
-      <c r="AL43" s="21"/>
-      <c r="AM43" s="18"/>
-      <c r="AN43" s="18"/>
-      <c r="AO43" s="25"/>
-      <c r="AP43" s="26"/>
-      <c r="AQ43" s="21"/>
-      <c r="AR43" s="18"/>
-      <c r="AS43" s="18"/>
-      <c r="AT43" s="18"/>
-      <c r="AU43" s="26"/>
+      <c r="AB43" s="86"/>
+      <c r="AC43" s="87"/>
+      <c r="AD43" s="87"/>
+      <c r="AE43" s="87"/>
+      <c r="AF43" s="89"/>
+      <c r="AG43" s="86"/>
+      <c r="AH43" s="86"/>
+      <c r="AI43" s="87"/>
+      <c r="AJ43" s="87"/>
+      <c r="AK43" s="89"/>
+      <c r="AL43" s="86"/>
+      <c r="AM43" s="87"/>
+      <c r="AN43" s="87"/>
+      <c r="AO43" s="88"/>
+      <c r="AP43" s="89"/>
+      <c r="AQ43" s="86"/>
+      <c r="AR43" s="87"/>
+      <c r="AS43" s="87"/>
+      <c r="AT43" s="87"/>
+      <c r="AU43" s="89" t="s">
+        <v>63</v>
+      </c>
       <c r="AY43" s="3"/>
       <c r="BD43" s="3"/>
       <c r="BH43" s="3"/>
@@ -5118,7 +5138,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="90" t="s">
+      <c r="D44" s="96" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5179,7 +5199,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="91"/>
+      <c r="D45" s="97"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5236,7 +5256,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="90" t="s">
+      <c r="D46" s="96" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5297,7 +5317,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="91"/>
+      <c r="D47" s="97"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5354,7 +5374,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="90" t="s">
+      <c r="D48" s="96" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5415,7 +5435,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="91"/>
+      <c r="D49" s="97"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5472,7 +5492,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="90" t="s">
+      <c r="D50" s="96" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5533,7 +5553,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="91"/>
+      <c r="D51" s="97"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5590,7 +5610,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="90" t="s">
+      <c r="D52" s="96" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5651,7 +5671,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="91"/>
+      <c r="D53" s="97"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -8481,6 +8501,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8497,16 +8527,6 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D79FCA85-36AB-4C66-BEB5-B2B9E432D6B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC49EC7-A4FF-4139-9D2F-6A9CE78F035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2205" windowWidth="51180" windowHeight="23850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5190" yWindow="5205" windowWidth="43500" windowHeight="17445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -278,6 +278,18 @@
   </si>
   <si>
     <t>10월 22일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>금주 진행</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>~11월 21일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1717,6 +1729,27 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1733,27 +1766,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2390,8 +2402,8 @@
   <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="3"/>
-    <col min="2" max="2" width="20.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.44140625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" style="3" customWidth="1"/>
     <col min="4" max="4" width="51" style="3" customWidth="1"/>
     <col min="5" max="5" width="13.6640625" style="3" customWidth="1"/>
     <col min="6" max="7" width="7.77734375" style="3" customWidth="1"/>
@@ -2437,6 +2449,15 @@
       </c>
       <c r="D1" s="38"/>
       <c r="E1" s="38"/>
+      <c r="AS1" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT1" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU1" s="89" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="2" spans="1:78" s="1" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="1" t="s">
@@ -2485,7 +2506,9 @@
       <c r="AP2" s="27"/>
       <c r="AQ2" s="27"/>
       <c r="AR2" s="27"/>
-      <c r="AS2" s="27"/>
+      <c r="AS2" s="13" t="s">
+        <v>66</v>
+      </c>
       <c r="AT2" s="27"/>
       <c r="AU2" s="27"/>
       <c r="AV2" s="27"/>
@@ -2520,11 +2543,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="93"/>
+      <c r="C3" s="99"/>
+      <c r="D3" s="100"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2619,9 +2642,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="91"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="95"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="102"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2788,7 +2811,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="96" t="s">
+      <c r="D5" s="94" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2849,7 +2872,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="97"/>
+      <c r="D6" s="95"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2908,7 +2931,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="96" t="s">
+      <c r="D7" s="94" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2969,7 +2992,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="97"/>
+      <c r="D8" s="95"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3028,7 +3051,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="96" t="s">
+      <c r="D9" s="94" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3089,7 +3112,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="97"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3148,7 +3171,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="96" t="s">
+      <c r="D11" s="94" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3209,7 +3232,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="97"/>
+      <c r="D12" s="95"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3268,7 +3291,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="96" t="s">
+      <c r="D13" s="94" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3329,7 +3352,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="97"/>
+      <c r="D14" s="95"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3390,7 +3413,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="96" t="s">
+      <c r="D15" s="94" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3451,7 +3474,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="97"/>
+      <c r="D16" s="95"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3510,7 +3533,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="96" t="s">
+      <c r="D17" s="94" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3571,7 +3594,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="97"/>
+      <c r="D18" s="95"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3632,7 +3655,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="96" t="s">
+      <c r="D19" s="94" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3693,7 +3716,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="97"/>
+      <c r="D20" s="95"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3752,7 +3775,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="96" t="s">
+      <c r="D21" s="94" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3813,7 +3836,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="97"/>
+      <c r="D22" s="95"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3874,7 +3897,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="96" t="s">
+      <c r="D23" s="94" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3935,7 +3958,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="97"/>
+      <c r="D24" s="95"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -3994,7 +4017,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="96" t="s">
+      <c r="D25" s="94" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4055,7 +4078,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="97"/>
+      <c r="D26" s="95"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4114,7 +4137,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="96" t="s">
+      <c r="D27" s="94" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4175,7 +4198,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="97"/>
+      <c r="D28" s="95"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4236,7 +4259,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="96" t="s">
+      <c r="D29" s="94" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4297,7 +4320,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="97"/>
+      <c r="D30" s="95"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4356,7 +4379,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="96" t="s">
+      <c r="D31" s="94" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4417,7 +4440,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="97"/>
+      <c r="D32" s="95"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4442,7 +4465,7 @@
       <c r="X32" s="87"/>
       <c r="Y32" s="87"/>
       <c r="Z32" s="88"/>
-      <c r="AA32" s="89" t="s">
+      <c r="AA32" s="79" t="s">
         <v>43</v>
       </c>
       <c r="AB32" s="12"/>
@@ -4476,7 +4499,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="96" t="s">
+      <c r="D33" s="94" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4537,7 +4560,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="97"/>
+      <c r="D34" s="95"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4596,7 +4619,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="96" t="s">
+      <c r="D35" s="94" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4657,7 +4680,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="97"/>
+      <c r="D36" s="95"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4716,7 +4739,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="96" t="s">
+      <c r="D37" s="94" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4776,7 +4799,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="97"/>
+      <c r="D38" s="95"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4806,7 +4829,7 @@
       <c r="AC38" s="87"/>
       <c r="AD38" s="87"/>
       <c r="AE38" s="87"/>
-      <c r="AF38" s="89" t="s">
+      <c r="AF38" s="79" t="s">
         <v>43</v>
       </c>
       <c r="AG38" s="12"/>
@@ -4837,7 +4860,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="96" t="s">
+      <c r="D39" s="94" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4900,7 +4923,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="98"/>
+      <c r="D40" s="96"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4957,7 +4980,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="97"/>
+      <c r="D41" s="95"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -4988,21 +5011,21 @@
       <c r="AD41" s="87"/>
       <c r="AE41" s="87"/>
       <c r="AF41" s="89"/>
-      <c r="AG41" s="99"/>
-      <c r="AH41" s="99"/>
-      <c r="AI41" s="100"/>
-      <c r="AJ41" s="100"/>
-      <c r="AK41" s="101"/>
-      <c r="AL41" s="99"/>
-      <c r="AM41" s="100"/>
-      <c r="AN41" s="100"/>
-      <c r="AO41" s="102"/>
-      <c r="AP41" s="101"/>
+      <c r="AG41" s="90"/>
+      <c r="AH41" s="90"/>
+      <c r="AI41" s="91"/>
+      <c r="AJ41" s="91"/>
+      <c r="AK41" s="92"/>
+      <c r="AL41" s="90"/>
+      <c r="AM41" s="91"/>
+      <c r="AN41" s="91"/>
+      <c r="AO41" s="93"/>
+      <c r="AP41" s="92"/>
       <c r="AQ41" s="86"/>
       <c r="AR41" s="86"/>
       <c r="AS41" s="87"/>
       <c r="AT41" s="87"/>
-      <c r="AU41" s="89" t="s">
+      <c r="AU41" s="79" t="s">
         <v>63</v>
       </c>
       <c r="AY41" s="3"/>
@@ -5016,7 +5039,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="96" t="s">
+      <c r="D42" s="94" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5079,7 +5102,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="97"/>
+      <c r="D43" s="95"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5124,7 +5147,7 @@
       <c r="AR43" s="87"/>
       <c r="AS43" s="87"/>
       <c r="AT43" s="87"/>
-      <c r="AU43" s="89" t="s">
+      <c r="AU43" s="79" t="s">
         <v>63</v>
       </c>
       <c r="AY43" s="3"/>
@@ -5138,7 +5161,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="96" t="s">
+      <c r="D44" s="94" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5199,7 +5222,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="97"/>
+      <c r="D45" s="95"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5256,7 +5279,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="96" t="s">
+      <c r="D46" s="94" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5317,7 +5340,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="97"/>
+      <c r="D47" s="95"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5374,7 +5397,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="96" t="s">
+      <c r="D48" s="94" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5435,7 +5458,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="97"/>
+      <c r="D49" s="95"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5456,11 +5479,11 @@
       <c r="T49" s="18"/>
       <c r="U49" s="25"/>
       <c r="V49" s="26"/>
-      <c r="W49" s="21"/>
-      <c r="X49" s="21"/>
-      <c r="Y49" s="18"/>
-      <c r="Z49" s="18"/>
-      <c r="AA49" s="26"/>
+      <c r="W49" s="86"/>
+      <c r="X49" s="87"/>
+      <c r="Y49" s="87"/>
+      <c r="Z49" s="87"/>
+      <c r="AA49" s="89"/>
       <c r="AB49" s="21"/>
       <c r="AC49" s="18"/>
       <c r="AD49" s="18"/>
@@ -5492,7 +5515,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="96" t="s">
+      <c r="D50" s="94" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5553,7 +5576,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="97"/>
+      <c r="D51" s="95"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5610,7 +5633,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="96" t="s">
+      <c r="D52" s="94" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5671,7 +5694,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="97"/>
+      <c r="D53" s="95"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -8501,16 +8524,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8527,6 +8540,16 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC49EC7-A4FF-4139-9D2F-6A9CE78F035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B3EB04-0661-4666-A128-7E39153F9EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="5205" windowWidth="43500" windowHeight="17445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1605" yWindow="6975" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -1458,7 +1458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1717,28 +1717,25 @@
     <xf numFmtId="176" fontId="5" fillId="29" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1749,24 +1746,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="81">
@@ -2455,7 +2434,7 @@
       <c r="AT1" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="AU1" s="89" t="s">
+      <c r="AU1" s="86" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2543,11 +2522,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="90"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2642,9 +2621,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="98"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="102"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="91"/>
+      <c r="D4" s="92"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2811,7 +2790,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="93" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2872,7 +2851,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="95"/>
+      <c r="D6" s="94"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2931,7 +2910,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="93" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2992,7 +2971,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="95"/>
+      <c r="D8" s="94"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3051,7 +3030,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="94" t="s">
+      <c r="D9" s="93" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3112,7 +3091,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="95"/>
+      <c r="D10" s="94"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3171,7 +3150,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="93" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3232,7 +3211,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="95"/>
+      <c r="D12" s="94"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3291,7 +3270,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="94" t="s">
+      <c r="D13" s="93" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3352,7 +3331,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="95"/>
+      <c r="D14" s="94"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3413,7 +3392,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="93" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3474,7 +3453,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="95"/>
+      <c r="D16" s="94"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3533,7 +3512,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="94" t="s">
+      <c r="D17" s="93" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3594,7 +3573,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="95"/>
+      <c r="D18" s="94"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3655,7 +3634,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="94" t="s">
+      <c r="D19" s="93" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3716,7 +3695,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="95"/>
+      <c r="D20" s="94"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3775,7 +3754,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="94" t="s">
+      <c r="D21" s="93" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3836,7 +3815,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="95"/>
+      <c r="D22" s="94"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3897,7 +3876,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="94" t="s">
+      <c r="D23" s="93" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3958,7 +3937,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="95"/>
+      <c r="D24" s="94"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -4017,7 +3996,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="94" t="s">
+      <c r="D25" s="93" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4078,7 +4057,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="95"/>
+      <c r="D26" s="94"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4137,7 +4116,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="94" t="s">
+      <c r="D27" s="93" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4198,7 +4177,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="95"/>
+      <c r="D28" s="94"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4259,7 +4238,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="94" t="s">
+      <c r="D29" s="93" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4320,7 +4299,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="95"/>
+      <c r="D30" s="94"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4379,7 +4358,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="94" t="s">
+      <c r="D31" s="93" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4440,7 +4419,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="95"/>
+      <c r="D32" s="94"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4461,10 +4440,10 @@
       <c r="T32" s="78"/>
       <c r="U32" s="80"/>
       <c r="V32" s="79"/>
-      <c r="W32" s="86"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="88"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="78"/>
+      <c r="Y32" s="78"/>
+      <c r="Z32" s="80"/>
       <c r="AA32" s="79" t="s">
         <v>43</v>
       </c>
@@ -4499,7 +4478,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="94" t="s">
+      <c r="D33" s="93" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4560,7 +4539,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="95"/>
+      <c r="D34" s="94"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4619,7 +4598,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="94" t="s">
+      <c r="D35" s="93" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4680,7 +4659,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="95"/>
+      <c r="D36" s="94"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4739,7 +4718,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="94" t="s">
+      <c r="D37" s="93" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4799,7 +4778,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="95"/>
+      <c r="D38" s="94"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4820,15 +4799,15 @@
       <c r="T38" s="18"/>
       <c r="U38" s="25"/>
       <c r="V38" s="26"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="87"/>
-      <c r="Z38" s="87"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="86"/>
-      <c r="AC38" s="87"/>
-      <c r="AD38" s="87"/>
-      <c r="AE38" s="87"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="78"/>
+      <c r="Y38" s="78"/>
+      <c r="Z38" s="80"/>
+      <c r="AA38" s="79"/>
+      <c r="AB38" s="77"/>
+      <c r="AC38" s="78"/>
+      <c r="AD38" s="78"/>
+      <c r="AE38" s="78"/>
       <c r="AF38" s="79" t="s">
         <v>43</v>
       </c>
@@ -4860,7 +4839,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="94" t="s">
+      <c r="D39" s="93" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4923,7 +4902,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="96"/>
+      <c r="D40" s="95"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4980,7 +4959,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="95"/>
+      <c r="D41" s="94"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -5001,30 +4980,30 @@
       <c r="T41" s="18"/>
       <c r="U41" s="25"/>
       <c r="V41" s="26"/>
-      <c r="W41" s="86"/>
-      <c r="X41" s="86"/>
-      <c r="Y41" s="87"/>
-      <c r="Z41" s="87"/>
-      <c r="AA41" s="89"/>
-      <c r="AB41" s="86"/>
-      <c r="AC41" s="87"/>
-      <c r="AD41" s="87"/>
-      <c r="AE41" s="87"/>
-      <c r="AF41" s="89"/>
-      <c r="AG41" s="90"/>
-      <c r="AH41" s="90"/>
-      <c r="AI41" s="91"/>
-      <c r="AJ41" s="91"/>
-      <c r="AK41" s="92"/>
-      <c r="AL41" s="90"/>
-      <c r="AM41" s="91"/>
-      <c r="AN41" s="91"/>
-      <c r="AO41" s="93"/>
-      <c r="AP41" s="92"/>
-      <c r="AQ41" s="86"/>
-      <c r="AR41" s="86"/>
-      <c r="AS41" s="87"/>
-      <c r="AT41" s="87"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="78"/>
+      <c r="Y41" s="78"/>
+      <c r="Z41" s="80"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="77"/>
+      <c r="AC41" s="78"/>
+      <c r="AD41" s="78"/>
+      <c r="AE41" s="80"/>
+      <c r="AF41" s="79"/>
+      <c r="AG41" s="77"/>
+      <c r="AH41" s="78"/>
+      <c r="AI41" s="78"/>
+      <c r="AJ41" s="80"/>
+      <c r="AK41" s="79"/>
+      <c r="AL41" s="77"/>
+      <c r="AM41" s="78"/>
+      <c r="AN41" s="78"/>
+      <c r="AO41" s="80"/>
+      <c r="AP41" s="79"/>
+      <c r="AQ41" s="77"/>
+      <c r="AR41" s="78"/>
+      <c r="AS41" s="78"/>
+      <c r="AT41" s="80"/>
       <c r="AU41" s="79" t="s">
         <v>63</v>
       </c>
@@ -5039,7 +5018,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="94" t="s">
+      <c r="D42" s="93" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5102,7 +5081,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="95"/>
+      <c r="D43" s="94"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5123,30 +5102,30 @@
       <c r="T43" s="18"/>
       <c r="U43" s="25"/>
       <c r="V43" s="26"/>
-      <c r="W43" s="86"/>
-      <c r="X43" s="86"/>
-      <c r="Y43" s="87"/>
-      <c r="Z43" s="87"/>
-      <c r="AA43" s="89"/>
-      <c r="AB43" s="86"/>
-      <c r="AC43" s="87"/>
-      <c r="AD43" s="87"/>
-      <c r="AE43" s="87"/>
-      <c r="AF43" s="89"/>
-      <c r="AG43" s="86"/>
-      <c r="AH43" s="86"/>
-      <c r="AI43" s="87"/>
-      <c r="AJ43" s="87"/>
-      <c r="AK43" s="89"/>
-      <c r="AL43" s="86"/>
-      <c r="AM43" s="87"/>
-      <c r="AN43" s="87"/>
-      <c r="AO43" s="88"/>
-      <c r="AP43" s="89"/>
-      <c r="AQ43" s="86"/>
-      <c r="AR43" s="87"/>
-      <c r="AS43" s="87"/>
-      <c r="AT43" s="87"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="78"/>
+      <c r="Y43" s="78"/>
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="77"/>
+      <c r="AC43" s="78"/>
+      <c r="AD43" s="78"/>
+      <c r="AE43" s="80"/>
+      <c r="AF43" s="79"/>
+      <c r="AG43" s="77"/>
+      <c r="AH43" s="78"/>
+      <c r="AI43" s="78"/>
+      <c r="AJ43" s="80"/>
+      <c r="AK43" s="79"/>
+      <c r="AL43" s="77"/>
+      <c r="AM43" s="78"/>
+      <c r="AN43" s="78"/>
+      <c r="AO43" s="80"/>
+      <c r="AP43" s="79"/>
+      <c r="AQ43" s="77"/>
+      <c r="AR43" s="78"/>
+      <c r="AS43" s="78"/>
+      <c r="AT43" s="80"/>
       <c r="AU43" s="79" t="s">
         <v>63</v>
       </c>
@@ -5161,7 +5140,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="94" t="s">
+      <c r="D44" s="93" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5222,7 +5201,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="95"/>
+      <c r="D45" s="94"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5279,7 +5258,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="94" t="s">
+      <c r="D46" s="93" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5340,7 +5319,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="95"/>
+      <c r="D47" s="94"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5397,7 +5376,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="94" t="s">
+      <c r="D48" s="93" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5458,7 +5437,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="95"/>
+      <c r="D49" s="94"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5479,11 +5458,11 @@
       <c r="T49" s="18"/>
       <c r="U49" s="25"/>
       <c r="V49" s="26"/>
-      <c r="W49" s="86"/>
-      <c r="X49" s="87"/>
-      <c r="Y49" s="87"/>
-      <c r="Z49" s="87"/>
-      <c r="AA49" s="89"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="78"/>
+      <c r="Y49" s="78"/>
+      <c r="Z49" s="80"/>
+      <c r="AA49" s="79"/>
       <c r="AB49" s="21"/>
       <c r="AC49" s="18"/>
       <c r="AD49" s="18"/>
@@ -5515,7 +5494,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="94" t="s">
+      <c r="D50" s="93" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5576,7 +5555,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="95"/>
+      <c r="D51" s="94"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5633,7 +5612,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="94" t="s">
+      <c r="D52" s="93" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5694,7 +5673,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="95"/>
+      <c r="D53" s="94"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -8524,6 +8503,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8540,16 +8529,6 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0B3EB04-0661-4666-A128-7E39153F9EC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FDCA89-045A-43F1-9BFB-A1F9D3D0076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1605" yWindow="6975" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="10050" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1458,7 +1458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1720,6 +1720,15 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1738,14 +1747,11 @@
     <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="81">
@@ -2522,11 +2528,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="89"/>
-      <c r="D3" s="90"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2621,9 +2627,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="88"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2790,7 +2796,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="93" t="s">
+      <c r="D5" s="87" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2851,7 +2857,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="94"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2910,7 +2916,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="93" t="s">
+      <c r="D7" s="87" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2971,7 +2977,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="94"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3030,7 +3036,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="93" t="s">
+      <c r="D9" s="87" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3091,7 +3097,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="94"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3150,7 +3156,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="93" t="s">
+      <c r="D11" s="87" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3211,7 +3217,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="94"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3270,7 +3276,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="93" t="s">
+      <c r="D13" s="87" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3331,7 +3337,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="94"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3392,7 +3398,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="93" t="s">
+      <c r="D15" s="87" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3453,7 +3459,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="94"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3512,7 +3518,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="93" t="s">
+      <c r="D17" s="87" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3573,7 +3579,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="94"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3634,7 +3640,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="93" t="s">
+      <c r="D19" s="87" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3695,7 +3701,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="94"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3754,7 +3760,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="93" t="s">
+      <c r="D21" s="87" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3815,7 +3821,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="94"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3876,7 +3882,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="93" t="s">
+      <c r="D23" s="87" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3937,7 +3943,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="94"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -3996,7 +4002,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="93" t="s">
+      <c r="D25" s="87" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4057,7 +4063,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="94"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4116,7 +4122,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="93" t="s">
+      <c r="D27" s="87" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4177,7 +4183,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="94"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4238,7 +4244,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="93" t="s">
+      <c r="D29" s="87" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4299,7 +4305,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="94"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4358,7 +4364,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="87" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4419,7 +4425,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="94"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4478,7 +4484,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="93" t="s">
+      <c r="D33" s="87" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4539,7 +4545,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="94"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4598,7 +4604,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="93" t="s">
+      <c r="D35" s="87" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4659,7 +4665,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="94"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4718,7 +4724,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="93" t="s">
+      <c r="D37" s="87" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4778,7 +4784,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="94"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4839,7 +4845,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="93" t="s">
+      <c r="D39" s="87" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4902,7 +4908,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="95"/>
+      <c r="D40" s="89"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4959,7 +4965,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="94"/>
+      <c r="D41" s="88"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -5018,7 +5024,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="93" t="s">
+      <c r="D42" s="87" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5081,7 +5087,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="94"/>
+      <c r="D43" s="88"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5140,7 +5146,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="93" t="s">
+      <c r="D44" s="87" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5201,7 +5207,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="94"/>
+      <c r="D45" s="88"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5227,21 +5233,23 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="18"/>
       <c r="AA45" s="26"/>
-      <c r="AB45" s="21"/>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="26"/>
-      <c r="AG45" s="21"/>
-      <c r="AH45" s="21"/>
-      <c r="AI45" s="18"/>
-      <c r="AJ45" s="18"/>
-      <c r="AK45" s="26"/>
-      <c r="AL45" s="21"/>
-      <c r="AM45" s="18"/>
-      <c r="AN45" s="18"/>
-      <c r="AO45" s="25"/>
-      <c r="AP45" s="26"/>
+      <c r="AB45" s="96"/>
+      <c r="AC45" s="97"/>
+      <c r="AD45" s="97"/>
+      <c r="AE45" s="97"/>
+      <c r="AF45" s="86"/>
+      <c r="AG45" s="96"/>
+      <c r="AH45" s="97"/>
+      <c r="AI45" s="97"/>
+      <c r="AJ45" s="97"/>
+      <c r="AK45" s="86"/>
+      <c r="AL45" s="96"/>
+      <c r="AM45" s="97"/>
+      <c r="AN45" s="97"/>
+      <c r="AO45" s="97"/>
+      <c r="AP45" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AQ45" s="21"/>
       <c r="AR45" s="18"/>
       <c r="AS45" s="18"/>
@@ -5258,7 +5266,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="93" t="s">
+      <c r="D46" s="87" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5319,7 +5327,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="94"/>
+      <c r="D47" s="88"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5345,16 +5353,18 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="18"/>
       <c r="AA47" s="26"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="26"/>
-      <c r="AG47" s="51"/>
-      <c r="AH47" s="48"/>
-      <c r="AI47" s="48"/>
-      <c r="AJ47" s="48"/>
-      <c r="AK47" s="49"/>
+      <c r="AB47" s="96"/>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="86"/>
+      <c r="AG47" s="96"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="97"/>
+      <c r="AJ47" s="97"/>
+      <c r="AK47" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AL47" s="21"/>
       <c r="AM47" s="18"/>
       <c r="AN47" s="18"/>
@@ -5376,7 +5386,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="93" t="s">
+      <c r="D48" s="87" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5437,7 +5447,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="94"/>
+      <c r="D49" s="88"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5463,16 +5473,18 @@
       <c r="Y49" s="78"/>
       <c r="Z49" s="80"/>
       <c r="AA49" s="79"/>
-      <c r="AB49" s="21"/>
-      <c r="AC49" s="18"/>
-      <c r="AD49" s="18"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="26"/>
-      <c r="AG49" s="21"/>
-      <c r="AH49" s="21"/>
-      <c r="AI49" s="18"/>
-      <c r="AJ49" s="18"/>
-      <c r="AK49" s="26"/>
+      <c r="AB49" s="96"/>
+      <c r="AC49" s="97"/>
+      <c r="AD49" s="97"/>
+      <c r="AE49" s="97"/>
+      <c r="AF49" s="86"/>
+      <c r="AG49" s="96"/>
+      <c r="AH49" s="97"/>
+      <c r="AI49" s="97"/>
+      <c r="AJ49" s="97"/>
+      <c r="AK49" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AL49" s="21"/>
       <c r="AM49" s="18"/>
       <c r="AN49" s="18"/>
@@ -5494,7 +5506,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="93" t="s">
+      <c r="D50" s="87" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5555,7 +5567,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="94"/>
+      <c r="D51" s="88"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5581,11 +5593,11 @@
       <c r="Y51" s="18"/>
       <c r="Z51" s="18"/>
       <c r="AA51" s="26"/>
-      <c r="AB51" s="21"/>
-      <c r="AC51" s="18"/>
-      <c r="AD51" s="18"/>
-      <c r="AE51" s="18"/>
-      <c r="AF51" s="26"/>
+      <c r="AB51" s="96"/>
+      <c r="AC51" s="97"/>
+      <c r="AD51" s="97"/>
+      <c r="AE51" s="97"/>
+      <c r="AF51" s="86"/>
       <c r="AG51" s="12"/>
       <c r="AH51" s="12"/>
       <c r="AI51" s="13"/>
@@ -5612,7 +5624,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="93" t="s">
+      <c r="D52" s="87" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5673,7 +5685,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="94"/>
+      <c r="D53" s="88"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -5699,11 +5711,11 @@
       <c r="Y53" s="18"/>
       <c r="Z53" s="18"/>
       <c r="AA53" s="26"/>
-      <c r="AB53" s="21"/>
-      <c r="AC53" s="18"/>
-      <c r="AD53" s="18"/>
-      <c r="AE53" s="18"/>
-      <c r="AF53" s="26"/>
+      <c r="AB53" s="96"/>
+      <c r="AC53" s="97"/>
+      <c r="AD53" s="97"/>
+      <c r="AE53" s="97"/>
+      <c r="AF53" s="86"/>
       <c r="AG53" s="21"/>
       <c r="AH53" s="21"/>
       <c r="AI53" s="18"/>
@@ -8503,16 +8515,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8529,6 +8531,16 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC49EC7-A4FF-4139-9D2F-6A9CE78F035B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FDCA89-045A-43F1-9BFB-A1F9D3D0076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5190" yWindow="5205" windowWidth="43500" windowHeight="17445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="10050" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1458,7 +1458,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1717,55 +1717,40 @@
     <xf numFmtId="176" fontId="5" fillId="29" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="30" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2455,7 +2440,7 @@
       <c r="AT1" s="78" t="s">
         <v>64</v>
       </c>
-      <c r="AU1" s="89" t="s">
+      <c r="AU1" s="86" t="s">
         <v>65</v>
       </c>
     </row>
@@ -2543,11 +2528,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="97" t="s">
+      <c r="B3" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="99"/>
-      <c r="D3" s="100"/>
+      <c r="C3" s="92"/>
+      <c r="D3" s="93"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2642,9 +2627,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="98"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="102"/>
+      <c r="B4" s="91"/>
+      <c r="C4" s="94"/>
+      <c r="D4" s="95"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2811,7 +2796,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="94" t="s">
+      <c r="D5" s="87" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2872,7 +2857,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="95"/>
+      <c r="D6" s="88"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2931,7 +2916,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="87" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2992,7 +2977,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="95"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3051,7 +3036,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="94" t="s">
+      <c r="D9" s="87" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3112,7 +3097,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="95"/>
+      <c r="D10" s="88"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3171,7 +3156,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="94" t="s">
+      <c r="D11" s="87" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3232,7 +3217,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="95"/>
+      <c r="D12" s="88"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3291,7 +3276,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="94" t="s">
+      <c r="D13" s="87" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3352,7 +3337,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="95"/>
+      <c r="D14" s="88"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3413,7 +3398,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="94" t="s">
+      <c r="D15" s="87" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3474,7 +3459,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="95"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3533,7 +3518,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="94" t="s">
+      <c r="D17" s="87" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3594,7 +3579,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="95"/>
+      <c r="D18" s="88"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3655,7 +3640,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="94" t="s">
+      <c r="D19" s="87" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3716,7 +3701,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="95"/>
+      <c r="D20" s="88"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3775,7 +3760,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="94" t="s">
+      <c r="D21" s="87" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3836,7 +3821,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="95"/>
+      <c r="D22" s="88"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3897,7 +3882,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="94" t="s">
+      <c r="D23" s="87" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3958,7 +3943,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="95"/>
+      <c r="D24" s="88"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -4017,7 +4002,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="94" t="s">
+      <c r="D25" s="87" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4078,7 +4063,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="95"/>
+      <c r="D26" s="88"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4137,7 +4122,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="94" t="s">
+      <c r="D27" s="87" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4198,7 +4183,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="95"/>
+      <c r="D28" s="88"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4259,7 +4244,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="94" t="s">
+      <c r="D29" s="87" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4320,7 +4305,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="95"/>
+      <c r="D30" s="88"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4379,7 +4364,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="94" t="s">
+      <c r="D31" s="87" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4440,7 +4425,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="95"/>
+      <c r="D32" s="88"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4461,10 +4446,10 @@
       <c r="T32" s="78"/>
       <c r="U32" s="80"/>
       <c r="V32" s="79"/>
-      <c r="W32" s="86"/>
-      <c r="X32" s="87"/>
-      <c r="Y32" s="87"/>
-      <c r="Z32" s="88"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="78"/>
+      <c r="Y32" s="78"/>
+      <c r="Z32" s="80"/>
       <c r="AA32" s="79" t="s">
         <v>43</v>
       </c>
@@ -4499,7 +4484,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="94" t="s">
+      <c r="D33" s="87" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4560,7 +4545,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="95"/>
+      <c r="D34" s="88"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4619,7 +4604,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="94" t="s">
+      <c r="D35" s="87" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4680,7 +4665,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="95"/>
+      <c r="D36" s="88"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4739,7 +4724,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="94" t="s">
+      <c r="D37" s="87" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4799,7 +4784,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="95"/>
+      <c r="D38" s="88"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4820,15 +4805,15 @@
       <c r="T38" s="18"/>
       <c r="U38" s="25"/>
       <c r="V38" s="26"/>
-      <c r="W38" s="86"/>
-      <c r="X38" s="86"/>
-      <c r="Y38" s="87"/>
-      <c r="Z38" s="87"/>
-      <c r="AA38" s="89"/>
-      <c r="AB38" s="86"/>
-      <c r="AC38" s="87"/>
-      <c r="AD38" s="87"/>
-      <c r="AE38" s="87"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="78"/>
+      <c r="Y38" s="78"/>
+      <c r="Z38" s="80"/>
+      <c r="AA38" s="79"/>
+      <c r="AB38" s="77"/>
+      <c r="AC38" s="78"/>
+      <c r="AD38" s="78"/>
+      <c r="AE38" s="78"/>
       <c r="AF38" s="79" t="s">
         <v>43</v>
       </c>
@@ -4860,7 +4845,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="94" t="s">
+      <c r="D39" s="87" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4923,7 +4908,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="96"/>
+      <c r="D40" s="89"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4980,7 +4965,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="95"/>
+      <c r="D41" s="88"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -5001,30 +4986,30 @@
       <c r="T41" s="18"/>
       <c r="U41" s="25"/>
       <c r="V41" s="26"/>
-      <c r="W41" s="86"/>
-      <c r="X41" s="86"/>
-      <c r="Y41" s="87"/>
-      <c r="Z41" s="87"/>
-      <c r="AA41" s="89"/>
-      <c r="AB41" s="86"/>
-      <c r="AC41" s="87"/>
-      <c r="AD41" s="87"/>
-      <c r="AE41" s="87"/>
-      <c r="AF41" s="89"/>
-      <c r="AG41" s="90"/>
-      <c r="AH41" s="90"/>
-      <c r="AI41" s="91"/>
-      <c r="AJ41" s="91"/>
-      <c r="AK41" s="92"/>
-      <c r="AL41" s="90"/>
-      <c r="AM41" s="91"/>
-      <c r="AN41" s="91"/>
-      <c r="AO41" s="93"/>
-      <c r="AP41" s="92"/>
-      <c r="AQ41" s="86"/>
-      <c r="AR41" s="86"/>
-      <c r="AS41" s="87"/>
-      <c r="AT41" s="87"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="78"/>
+      <c r="Y41" s="78"/>
+      <c r="Z41" s="80"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="77"/>
+      <c r="AC41" s="78"/>
+      <c r="AD41" s="78"/>
+      <c r="AE41" s="80"/>
+      <c r="AF41" s="79"/>
+      <c r="AG41" s="77"/>
+      <c r="AH41" s="78"/>
+      <c r="AI41" s="78"/>
+      <c r="AJ41" s="80"/>
+      <c r="AK41" s="79"/>
+      <c r="AL41" s="77"/>
+      <c r="AM41" s="78"/>
+      <c r="AN41" s="78"/>
+      <c r="AO41" s="80"/>
+      <c r="AP41" s="79"/>
+      <c r="AQ41" s="77"/>
+      <c r="AR41" s="78"/>
+      <c r="AS41" s="78"/>
+      <c r="AT41" s="80"/>
       <c r="AU41" s="79" t="s">
         <v>63</v>
       </c>
@@ -5039,7 +5024,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="94" t="s">
+      <c r="D42" s="87" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5102,7 +5087,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="95"/>
+      <c r="D43" s="88"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5123,30 +5108,30 @@
       <c r="T43" s="18"/>
       <c r="U43" s="25"/>
       <c r="V43" s="26"/>
-      <c r="W43" s="86"/>
-      <c r="X43" s="86"/>
-      <c r="Y43" s="87"/>
-      <c r="Z43" s="87"/>
-      <c r="AA43" s="89"/>
-      <c r="AB43" s="86"/>
-      <c r="AC43" s="87"/>
-      <c r="AD43" s="87"/>
-      <c r="AE43" s="87"/>
-      <c r="AF43" s="89"/>
-      <c r="AG43" s="86"/>
-      <c r="AH43" s="86"/>
-      <c r="AI43" s="87"/>
-      <c r="AJ43" s="87"/>
-      <c r="AK43" s="89"/>
-      <c r="AL43" s="86"/>
-      <c r="AM43" s="87"/>
-      <c r="AN43" s="87"/>
-      <c r="AO43" s="88"/>
-      <c r="AP43" s="89"/>
-      <c r="AQ43" s="86"/>
-      <c r="AR43" s="87"/>
-      <c r="AS43" s="87"/>
-      <c r="AT43" s="87"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="78"/>
+      <c r="Y43" s="78"/>
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="77"/>
+      <c r="AC43" s="78"/>
+      <c r="AD43" s="78"/>
+      <c r="AE43" s="80"/>
+      <c r="AF43" s="79"/>
+      <c r="AG43" s="77"/>
+      <c r="AH43" s="78"/>
+      <c r="AI43" s="78"/>
+      <c r="AJ43" s="80"/>
+      <c r="AK43" s="79"/>
+      <c r="AL43" s="77"/>
+      <c r="AM43" s="78"/>
+      <c r="AN43" s="78"/>
+      <c r="AO43" s="80"/>
+      <c r="AP43" s="79"/>
+      <c r="AQ43" s="77"/>
+      <c r="AR43" s="78"/>
+      <c r="AS43" s="78"/>
+      <c r="AT43" s="80"/>
       <c r="AU43" s="79" t="s">
         <v>63</v>
       </c>
@@ -5161,7 +5146,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="94" t="s">
+      <c r="D44" s="87" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5222,7 +5207,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="95"/>
+      <c r="D45" s="88"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5248,21 +5233,23 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="18"/>
       <c r="AA45" s="26"/>
-      <c r="AB45" s="21"/>
-      <c r="AC45" s="18"/>
-      <c r="AD45" s="18"/>
-      <c r="AE45" s="18"/>
-      <c r="AF45" s="26"/>
-      <c r="AG45" s="21"/>
-      <c r="AH45" s="21"/>
-      <c r="AI45" s="18"/>
-      <c r="AJ45" s="18"/>
-      <c r="AK45" s="26"/>
-      <c r="AL45" s="21"/>
-      <c r="AM45" s="18"/>
-      <c r="AN45" s="18"/>
-      <c r="AO45" s="25"/>
-      <c r="AP45" s="26"/>
+      <c r="AB45" s="96"/>
+      <c r="AC45" s="97"/>
+      <c r="AD45" s="97"/>
+      <c r="AE45" s="97"/>
+      <c r="AF45" s="86"/>
+      <c r="AG45" s="96"/>
+      <c r="AH45" s="97"/>
+      <c r="AI45" s="97"/>
+      <c r="AJ45" s="97"/>
+      <c r="AK45" s="86"/>
+      <c r="AL45" s="96"/>
+      <c r="AM45" s="97"/>
+      <c r="AN45" s="97"/>
+      <c r="AO45" s="97"/>
+      <c r="AP45" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AQ45" s="21"/>
       <c r="AR45" s="18"/>
       <c r="AS45" s="18"/>
@@ -5279,7 +5266,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="94" t="s">
+      <c r="D46" s="87" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5340,7 +5327,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="95"/>
+      <c r="D47" s="88"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5366,16 +5353,18 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="18"/>
       <c r="AA47" s="26"/>
-      <c r="AB47" s="21"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="26"/>
-      <c r="AG47" s="51"/>
-      <c r="AH47" s="48"/>
-      <c r="AI47" s="48"/>
-      <c r="AJ47" s="48"/>
-      <c r="AK47" s="49"/>
+      <c r="AB47" s="96"/>
+      <c r="AC47" s="97"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="97"/>
+      <c r="AF47" s="86"/>
+      <c r="AG47" s="96"/>
+      <c r="AH47" s="97"/>
+      <c r="AI47" s="97"/>
+      <c r="AJ47" s="97"/>
+      <c r="AK47" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AL47" s="21"/>
       <c r="AM47" s="18"/>
       <c r="AN47" s="18"/>
@@ -5397,7 +5386,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="94" t="s">
+      <c r="D48" s="87" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5458,7 +5447,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="95"/>
+      <c r="D49" s="88"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5479,21 +5468,23 @@
       <c r="T49" s="18"/>
       <c r="U49" s="25"/>
       <c r="V49" s="26"/>
-      <c r="W49" s="86"/>
-      <c r="X49" s="87"/>
-      <c r="Y49" s="87"/>
-      <c r="Z49" s="87"/>
-      <c r="AA49" s="89"/>
-      <c r="AB49" s="21"/>
-      <c r="AC49" s="18"/>
-      <c r="AD49" s="18"/>
-      <c r="AE49" s="18"/>
-      <c r="AF49" s="26"/>
-      <c r="AG49" s="21"/>
-      <c r="AH49" s="21"/>
-      <c r="AI49" s="18"/>
-      <c r="AJ49" s="18"/>
-      <c r="AK49" s="26"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="78"/>
+      <c r="Y49" s="78"/>
+      <c r="Z49" s="80"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="96"/>
+      <c r="AC49" s="97"/>
+      <c r="AD49" s="97"/>
+      <c r="AE49" s="97"/>
+      <c r="AF49" s="86"/>
+      <c r="AG49" s="96"/>
+      <c r="AH49" s="97"/>
+      <c r="AI49" s="97"/>
+      <c r="AJ49" s="97"/>
+      <c r="AK49" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AL49" s="21"/>
       <c r="AM49" s="18"/>
       <c r="AN49" s="18"/>
@@ -5515,7 +5506,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="94" t="s">
+      <c r="D50" s="87" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5576,7 +5567,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="95"/>
+      <c r="D51" s="88"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5602,11 +5593,11 @@
       <c r="Y51" s="18"/>
       <c r="Z51" s="18"/>
       <c r="AA51" s="26"/>
-      <c r="AB51" s="21"/>
-      <c r="AC51" s="18"/>
-      <c r="AD51" s="18"/>
-      <c r="AE51" s="18"/>
-      <c r="AF51" s="26"/>
+      <c r="AB51" s="96"/>
+      <c r="AC51" s="97"/>
+      <c r="AD51" s="97"/>
+      <c r="AE51" s="97"/>
+      <c r="AF51" s="86"/>
       <c r="AG51" s="12"/>
       <c r="AH51" s="12"/>
       <c r="AI51" s="13"/>
@@ -5633,7 +5624,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="94" t="s">
+      <c r="D52" s="87" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5694,7 +5685,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="95"/>
+      <c r="D53" s="88"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -5720,11 +5711,11 @@
       <c r="Y53" s="18"/>
       <c r="Z53" s="18"/>
       <c r="AA53" s="26"/>
-      <c r="AB53" s="21"/>
-      <c r="AC53" s="18"/>
-      <c r="AD53" s="18"/>
-      <c r="AE53" s="18"/>
-      <c r="AF53" s="26"/>
+      <c r="AB53" s="96"/>
+      <c r="AC53" s="97"/>
+      <c r="AD53" s="97"/>
+      <c r="AE53" s="97"/>
+      <c r="AF53" s="86"/>
       <c r="AG53" s="21"/>
       <c r="AH53" s="21"/>
       <c r="AI53" s="18"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4FDCA89-045A-43F1-9BFB-A1F9D3D0076D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CB0A54-1DD6-44B5-8D96-4BEEE13EAC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="10050" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-255" yWindow="2460" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="67">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -5598,21 +5598,23 @@
       <c r="AD51" s="97"/>
       <c r="AE51" s="97"/>
       <c r="AF51" s="86"/>
-      <c r="AG51" s="12"/>
-      <c r="AH51" s="12"/>
-      <c r="AI51" s="13"/>
-      <c r="AJ51" s="13"/>
-      <c r="AK51" s="14"/>
-      <c r="AL51" s="21"/>
-      <c r="AM51" s="18"/>
-      <c r="AN51" s="18"/>
-      <c r="AO51" s="25"/>
-      <c r="AP51" s="26"/>
-      <c r="AQ51" s="21"/>
-      <c r="AR51" s="18"/>
-      <c r="AS51" s="18"/>
-      <c r="AT51" s="18"/>
-      <c r="AU51" s="26"/>
+      <c r="AG51" s="96"/>
+      <c r="AH51" s="97"/>
+      <c r="AI51" s="97"/>
+      <c r="AJ51" s="97"/>
+      <c r="AK51" s="86"/>
+      <c r="AL51" s="96"/>
+      <c r="AM51" s="97"/>
+      <c r="AN51" s="97"/>
+      <c r="AO51" s="97"/>
+      <c r="AP51" s="86"/>
+      <c r="AQ51" s="96"/>
+      <c r="AR51" s="97"/>
+      <c r="AS51" s="97"/>
+      <c r="AT51" s="97"/>
+      <c r="AU51" s="79" t="s">
+        <v>61</v>
+      </c>
       <c r="AY51" s="3"/>
       <c r="BD51" s="3"/>
       <c r="BH51" s="3"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89CB0A54-1DD6-44B5-8D96-4BEEE13EAC10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB592CC-A596-4F92-9019-9F27BAED28DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-255" yWindow="2460" windowWidth="50445" windowHeight="19890" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6900" yWindow="19395" windowWidth="41775" windowHeight="23130" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -289,7 +289,7 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>~11월 21일</t>
+    <t>~11월 28일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1720,6 +1720,30 @@
     <xf numFmtId="0" fontId="5" fillId="30" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1728,30 +1752,6 @@
     </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="81">
@@ -2528,11 +2528,11 @@
       <c r="BY2" s="27"/>
     </row>
     <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="90" t="s">
+      <c r="B3" s="89" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="92"/>
-      <c r="D3" s="93"/>
+      <c r="C3" s="91"/>
+      <c r="D3" s="92"/>
       <c r="E3" s="69"/>
       <c r="F3" s="72" t="s">
         <v>4</v>
@@ -2627,9 +2627,9 @@
       <c r="BZ3" s="3"/>
     </row>
     <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="91"/>
-      <c r="C4" s="94"/>
-      <c r="D4" s="95"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="94"/>
       <c r="E4" s="70"/>
       <c r="F4" s="71">
         <v>1</v>
@@ -2796,7 +2796,7 @@
       <c r="C5" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="87" t="s">
+      <c r="D5" s="95" t="s">
         <v>19</v>
       </c>
       <c r="E5" s="54" t="s">
@@ -2857,7 +2857,7 @@
     <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="17"/>
       <c r="C6" s="40"/>
-      <c r="D6" s="88"/>
+      <c r="D6" s="96"/>
       <c r="E6" s="55" t="s">
         <v>34</v>
       </c>
@@ -2916,7 +2916,7 @@
     <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="17"/>
       <c r="C7" s="40"/>
-      <c r="D7" s="87" t="s">
+      <c r="D7" s="95" t="s">
         <v>20</v>
       </c>
       <c r="E7" s="54" t="s">
@@ -2977,7 +2977,7 @@
     <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="17"/>
       <c r="C8" s="40"/>
-      <c r="D8" s="88"/>
+      <c r="D8" s="96"/>
       <c r="E8" s="55" t="s">
         <v>34</v>
       </c>
@@ -3036,7 +3036,7 @@
     <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="17"/>
       <c r="C9" s="40"/>
-      <c r="D9" s="87" t="s">
+      <c r="D9" s="95" t="s">
         <v>22</v>
       </c>
       <c r="E9" s="54" t="s">
@@ -3097,7 +3097,7 @@
     <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="17"/>
       <c r="C10" s="40"/>
-      <c r="D10" s="88"/>
+      <c r="D10" s="96"/>
       <c r="E10" s="55" t="s">
         <v>34</v>
       </c>
@@ -3156,7 +3156,7 @@
     <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="17"/>
       <c r="C11" s="40"/>
-      <c r="D11" s="87" t="s">
+      <c r="D11" s="95" t="s">
         <v>23</v>
       </c>
       <c r="E11" s="54" t="s">
@@ -3217,7 +3217,7 @@
     <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="17"/>
       <c r="C12" s="40"/>
-      <c r="D12" s="88"/>
+      <c r="D12" s="96"/>
       <c r="E12" s="55" t="s">
         <v>34</v>
       </c>
@@ -3276,7 +3276,7 @@
     <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="17"/>
       <c r="C13" s="40"/>
-      <c r="D13" s="87" t="s">
+      <c r="D13" s="95" t="s">
         <v>21</v>
       </c>
       <c r="E13" s="54" t="s">
@@ -3337,7 +3337,7 @@
     <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="17"/>
       <c r="C14" s="40"/>
-      <c r="D14" s="88"/>
+      <c r="D14" s="96"/>
       <c r="E14" s="61" t="s">
         <v>34</v>
       </c>
@@ -3398,7 +3398,7 @@
       <c r="C15" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="87" t="s">
+      <c r="D15" s="95" t="s">
         <v>24</v>
       </c>
       <c r="E15" s="54" t="s">
@@ -3459,7 +3459,7 @@
     <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="17"/>
       <c r="C16" s="40"/>
-      <c r="D16" s="88"/>
+      <c r="D16" s="96"/>
       <c r="E16" s="55" t="s">
         <v>34</v>
       </c>
@@ -3518,7 +3518,7 @@
     <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="17"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="87" t="s">
+      <c r="D17" s="95" t="s">
         <v>25</v>
       </c>
       <c r="E17" s="60" t="s">
@@ -3579,7 +3579,7 @@
     <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="17"/>
       <c r="C18" s="40"/>
-      <c r="D18" s="88"/>
+      <c r="D18" s="96"/>
       <c r="E18" s="61" t="s">
         <v>34</v>
       </c>
@@ -3640,7 +3640,7 @@
       <c r="C19" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="87" t="s">
+      <c r="D19" s="95" t="s">
         <v>26</v>
       </c>
       <c r="E19" s="54" t="s">
@@ -3701,7 +3701,7 @@
     <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="17"/>
       <c r="C20" s="40"/>
-      <c r="D20" s="88"/>
+      <c r="D20" s="96"/>
       <c r="E20" s="55" t="s">
         <v>34</v>
       </c>
@@ -3760,7 +3760,7 @@
     <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="17"/>
       <c r="C21" s="40"/>
-      <c r="D21" s="87" t="s">
+      <c r="D21" s="95" t="s">
         <v>27</v>
       </c>
       <c r="E21" s="60" t="s">
@@ -3821,7 +3821,7 @@
     <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="17"/>
       <c r="C22" s="40"/>
-      <c r="D22" s="88"/>
+      <c r="D22" s="96"/>
       <c r="E22" s="61" t="s">
         <v>34</v>
       </c>
@@ -3882,7 +3882,7 @@
       <c r="C23" s="40" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="87" t="s">
+      <c r="D23" s="95" t="s">
         <v>28</v>
       </c>
       <c r="E23" s="54" t="s">
@@ -3943,7 +3943,7 @@
     <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="17"/>
       <c r="C24" s="40"/>
-      <c r="D24" s="88"/>
+      <c r="D24" s="96"/>
       <c r="E24" s="55" t="s">
         <v>34</v>
       </c>
@@ -4002,7 +4002,7 @@
     <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="17"/>
       <c r="C25" s="40"/>
-      <c r="D25" s="87" t="s">
+      <c r="D25" s="95" t="s">
         <v>29</v>
       </c>
       <c r="E25" s="54" t="s">
@@ -4063,7 +4063,7 @@
     <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="17"/>
       <c r="C26" s="40"/>
-      <c r="D26" s="88"/>
+      <c r="D26" s="96"/>
       <c r="E26" s="55" t="s">
         <v>34</v>
       </c>
@@ -4122,7 +4122,7 @@
     <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="17"/>
       <c r="C27" s="40"/>
-      <c r="D27" s="87" t="s">
+      <c r="D27" s="95" t="s">
         <v>30</v>
       </c>
       <c r="E27" s="60" t="s">
@@ -4183,7 +4183,7 @@
     <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="17"/>
       <c r="C28" s="40"/>
-      <c r="D28" s="88"/>
+      <c r="D28" s="96"/>
       <c r="E28" s="61" t="s">
         <v>34</v>
       </c>
@@ -4244,7 +4244,7 @@
       <c r="C29" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="D29" s="87" t="s">
+      <c r="D29" s="95" t="s">
         <v>32</v>
       </c>
       <c r="E29" s="54" t="s">
@@ -4305,7 +4305,7 @@
     <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="17"/>
       <c r="C30" s="40"/>
-      <c r="D30" s="88"/>
+      <c r="D30" s="96"/>
       <c r="E30" s="55" t="s">
         <v>34</v>
       </c>
@@ -4364,7 +4364,7 @@
     <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="17"/>
       <c r="C31" s="40"/>
-      <c r="D31" s="87" t="s">
+      <c r="D31" s="95" t="s">
         <v>60</v>
       </c>
       <c r="E31" s="54" t="s">
@@ -4425,7 +4425,7 @@
     <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="17"/>
       <c r="C32" s="40"/>
-      <c r="D32" s="88"/>
+      <c r="D32" s="96"/>
       <c r="E32" s="55" t="s">
         <v>34</v>
       </c>
@@ -4484,7 +4484,7 @@
     <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="17"/>
       <c r="C33" s="40"/>
-      <c r="D33" s="87" t="s">
+      <c r="D33" s="95" t="s">
         <v>31</v>
       </c>
       <c r="E33" s="54" t="s">
@@ -4545,7 +4545,7 @@
     <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="17"/>
       <c r="C34" s="40"/>
-      <c r="D34" s="88"/>
+      <c r="D34" s="96"/>
       <c r="E34" s="55" t="s">
         <v>34</v>
       </c>
@@ -4604,7 +4604,7 @@
     <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="17"/>
       <c r="C35" s="40"/>
-      <c r="D35" s="87" t="s">
+      <c r="D35" s="95" t="s">
         <v>62</v>
       </c>
       <c r="E35" s="54" t="s">
@@ -4665,7 +4665,7 @@
     <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="17"/>
       <c r="C36" s="40"/>
-      <c r="D36" s="88"/>
+      <c r="D36" s="96"/>
       <c r="E36" s="55" t="s">
         <v>34</v>
       </c>
@@ -4724,7 +4724,7 @@
     <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="17"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="87" t="s">
+      <c r="D37" s="95" t="s">
         <v>57</v>
       </c>
       <c r="E37" s="60" t="s">
@@ -4784,7 +4784,7 @@
     <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="17"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="88"/>
+      <c r="D38" s="96"/>
       <c r="E38" s="61" t="s">
         <v>34</v>
       </c>
@@ -4845,7 +4845,7 @@
       <c r="C39" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="D39" s="87" t="s">
+      <c r="D39" s="95" t="s">
         <v>54</v>
       </c>
       <c r="E39" s="60" t="s">
@@ -4908,7 +4908,7 @@
     <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="17"/>
       <c r="C40" s="40"/>
-      <c r="D40" s="89"/>
+      <c r="D40" s="97"/>
       <c r="E40" s="62" t="s">
         <v>34</v>
       </c>
@@ -4965,7 +4965,7 @@
     <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="17"/>
       <c r="C41" s="40"/>
-      <c r="D41" s="88"/>
+      <c r="D41" s="96"/>
       <c r="E41" s="61" t="s">
         <v>34</v>
       </c>
@@ -5024,7 +5024,7 @@
     <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="17"/>
       <c r="C42" s="40"/>
-      <c r="D42" s="87" t="s">
+      <c r="D42" s="95" t="s">
         <v>45</v>
       </c>
       <c r="E42" s="60" t="s">
@@ -5087,7 +5087,7 @@
     <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="17"/>
       <c r="C43" s="40"/>
-      <c r="D43" s="88"/>
+      <c r="D43" s="96"/>
       <c r="E43" s="62" t="s">
         <v>34</v>
       </c>
@@ -5146,7 +5146,7 @@
     <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="17"/>
       <c r="C44" s="40"/>
-      <c r="D44" s="87" t="s">
+      <c r="D44" s="95" t="s">
         <v>46</v>
       </c>
       <c r="E44" s="60" t="s">
@@ -5207,7 +5207,7 @@
     <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="17"/>
       <c r="C45" s="40"/>
-      <c r="D45" s="88"/>
+      <c r="D45" s="96"/>
       <c r="E45" s="62" t="s">
         <v>34</v>
       </c>
@@ -5233,20 +5233,20 @@
       <c r="Y45" s="18"/>
       <c r="Z45" s="18"/>
       <c r="AA45" s="26"/>
-      <c r="AB45" s="96"/>
-      <c r="AC45" s="97"/>
-      <c r="AD45" s="97"/>
-      <c r="AE45" s="97"/>
+      <c r="AB45" s="87"/>
+      <c r="AC45" s="88"/>
+      <c r="AD45" s="88"/>
+      <c r="AE45" s="88"/>
       <c r="AF45" s="86"/>
-      <c r="AG45" s="96"/>
-      <c r="AH45" s="97"/>
-      <c r="AI45" s="97"/>
-      <c r="AJ45" s="97"/>
+      <c r="AG45" s="87"/>
+      <c r="AH45" s="88"/>
+      <c r="AI45" s="88"/>
+      <c r="AJ45" s="88"/>
       <c r="AK45" s="86"/>
-      <c r="AL45" s="96"/>
-      <c r="AM45" s="97"/>
-      <c r="AN45" s="97"/>
-      <c r="AO45" s="97"/>
+      <c r="AL45" s="87"/>
+      <c r="AM45" s="88"/>
+      <c r="AN45" s="88"/>
+      <c r="AO45" s="88"/>
       <c r="AP45" s="79" t="s">
         <v>61</v>
       </c>
@@ -5266,7 +5266,7 @@
     <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="17"/>
       <c r="C46" s="40"/>
-      <c r="D46" s="87" t="s">
+      <c r="D46" s="95" t="s">
         <v>47</v>
       </c>
       <c r="E46" s="60" t="s">
@@ -5327,7 +5327,7 @@
     <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="17"/>
       <c r="C47" s="40"/>
-      <c r="D47" s="88"/>
+      <c r="D47" s="96"/>
       <c r="E47" s="62" t="s">
         <v>34</v>
       </c>
@@ -5353,15 +5353,15 @@
       <c r="Y47" s="18"/>
       <c r="Z47" s="18"/>
       <c r="AA47" s="26"/>
-      <c r="AB47" s="96"/>
-      <c r="AC47" s="97"/>
-      <c r="AD47" s="97"/>
-      <c r="AE47" s="97"/>
+      <c r="AB47" s="87"/>
+      <c r="AC47" s="88"/>
+      <c r="AD47" s="88"/>
+      <c r="AE47" s="88"/>
       <c r="AF47" s="86"/>
-      <c r="AG47" s="96"/>
-      <c r="AH47" s="97"/>
-      <c r="AI47" s="97"/>
-      <c r="AJ47" s="97"/>
+      <c r="AG47" s="87"/>
+      <c r="AH47" s="88"/>
+      <c r="AI47" s="88"/>
+      <c r="AJ47" s="88"/>
       <c r="AK47" s="79" t="s">
         <v>61</v>
       </c>
@@ -5386,7 +5386,7 @@
     <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="17"/>
       <c r="C48" s="40"/>
-      <c r="D48" s="87" t="s">
+      <c r="D48" s="95" t="s">
         <v>48</v>
       </c>
       <c r="E48" s="60" t="s">
@@ -5447,7 +5447,7 @@
     <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="17"/>
       <c r="C49" s="40"/>
-      <c r="D49" s="88"/>
+      <c r="D49" s="96"/>
       <c r="E49" s="62" t="s">
         <v>34</v>
       </c>
@@ -5473,15 +5473,15 @@
       <c r="Y49" s="78"/>
       <c r="Z49" s="80"/>
       <c r="AA49" s="79"/>
-      <c r="AB49" s="96"/>
-      <c r="AC49" s="97"/>
-      <c r="AD49" s="97"/>
-      <c r="AE49" s="97"/>
+      <c r="AB49" s="87"/>
+      <c r="AC49" s="88"/>
+      <c r="AD49" s="88"/>
+      <c r="AE49" s="88"/>
       <c r="AF49" s="86"/>
-      <c r="AG49" s="96"/>
-      <c r="AH49" s="97"/>
-      <c r="AI49" s="97"/>
-      <c r="AJ49" s="97"/>
+      <c r="AG49" s="87"/>
+      <c r="AH49" s="88"/>
+      <c r="AI49" s="88"/>
+      <c r="AJ49" s="88"/>
       <c r="AK49" s="79" t="s">
         <v>61</v>
       </c>
@@ -5506,7 +5506,7 @@
     <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="17"/>
       <c r="C50" s="40"/>
-      <c r="D50" s="87" t="s">
+      <c r="D50" s="95" t="s">
         <v>49</v>
       </c>
       <c r="E50" s="60" t="s">
@@ -5567,7 +5567,7 @@
     <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="17"/>
       <c r="C51" s="40"/>
-      <c r="D51" s="88"/>
+      <c r="D51" s="96"/>
       <c r="E51" s="62" t="s">
         <v>34</v>
       </c>
@@ -5593,25 +5593,25 @@
       <c r="Y51" s="18"/>
       <c r="Z51" s="18"/>
       <c r="AA51" s="26"/>
-      <c r="AB51" s="96"/>
-      <c r="AC51" s="97"/>
-      <c r="AD51" s="97"/>
-      <c r="AE51" s="97"/>
+      <c r="AB51" s="87"/>
+      <c r="AC51" s="88"/>
+      <c r="AD51" s="88"/>
+      <c r="AE51" s="88"/>
       <c r="AF51" s="86"/>
-      <c r="AG51" s="96"/>
-      <c r="AH51" s="97"/>
-      <c r="AI51" s="97"/>
-      <c r="AJ51" s="97"/>
+      <c r="AG51" s="87"/>
+      <c r="AH51" s="88"/>
+      <c r="AI51" s="88"/>
+      <c r="AJ51" s="88"/>
       <c r="AK51" s="86"/>
-      <c r="AL51" s="96"/>
-      <c r="AM51" s="97"/>
-      <c r="AN51" s="97"/>
-      <c r="AO51" s="97"/>
+      <c r="AL51" s="87"/>
+      <c r="AM51" s="88"/>
+      <c r="AN51" s="88"/>
+      <c r="AO51" s="88"/>
       <c r="AP51" s="86"/>
-      <c r="AQ51" s="96"/>
-      <c r="AR51" s="97"/>
-      <c r="AS51" s="97"/>
-      <c r="AT51" s="97"/>
+      <c r="AQ51" s="87"/>
+      <c r="AR51" s="88"/>
+      <c r="AS51" s="88"/>
+      <c r="AT51" s="88"/>
       <c r="AU51" s="79" t="s">
         <v>61</v>
       </c>
@@ -5626,7 +5626,7 @@
     <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="17"/>
       <c r="C52" s="40"/>
-      <c r="D52" s="87" t="s">
+      <c r="D52" s="95" t="s">
         <v>50</v>
       </c>
       <c r="E52" s="60" t="s">
@@ -5687,7 +5687,7 @@
     <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="17"/>
       <c r="C53" s="40"/>
-      <c r="D53" s="88"/>
+      <c r="D53" s="96"/>
       <c r="E53" s="62" t="s">
         <v>34</v>
       </c>
@@ -5713,10 +5713,10 @@
       <c r="Y53" s="18"/>
       <c r="Z53" s="18"/>
       <c r="AA53" s="26"/>
-      <c r="AB53" s="96"/>
-      <c r="AC53" s="97"/>
-      <c r="AD53" s="97"/>
-      <c r="AE53" s="97"/>
+      <c r="AB53" s="87"/>
+      <c r="AC53" s="88"/>
+      <c r="AD53" s="88"/>
+      <c r="AE53" s="88"/>
       <c r="AF53" s="86"/>
       <c r="AG53" s="21"/>
       <c r="AH53" s="21"/>
@@ -8517,6 +8517,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:D4"/>
     <mergeCell ref="D35:D36"/>
@@ -8533,16 +8543,6 @@
     <mergeCell ref="D25:D26"/>
     <mergeCell ref="D27:D28"/>
     <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="D33:D34"/>
-    <mergeCell ref="D37:D38"/>
-    <mergeCell ref="D39:D41"/>
-    <mergeCell ref="D52:D53"/>
-    <mergeCell ref="D42:D43"/>
-    <mergeCell ref="D44:D45"/>
-    <mergeCell ref="D46:D47"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="D50:D51"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions horizontalCentered="1"/>

--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -1,3 +1,26 @@
+
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1056BD-9380-44A3-887C-97C1E55549FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="8700" yWindow="3990" windowWidth="39510" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Viewer 샘플'!$B$1:$D$54</definedName>
+  </definedNames>
+  <calcPr calcId="152511"/>
+</workbook>
+</file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="70">
@@ -1721,26 +1744,26 @@
     <xf numFmtId="0" fontId="28" fillId="27" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="28" fillId="27" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="81">
@@ -2365,4 +2388,6196 @@
   <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BZ548"/>
+  <sheetFormatPr defaultColWidth="3" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="3" style="3"/>
+    <col min="2" max="2" width="9.6640625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="51" style="3" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" style="3" customWidth="1"/>
+    <col min="6" max="7" width="7.77734375" style="3" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="28" customWidth="1"/>
+    <col min="9" max="12" width="7.77734375" style="3" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" style="24" customWidth="1"/>
+    <col min="14" max="16" width="7.77734375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="7.77734375" style="28" customWidth="1"/>
+    <col min="18" max="21" width="7.77734375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="7.77734375" style="24" customWidth="1"/>
+    <col min="23" max="26" width="7.77734375" style="3" customWidth="1"/>
+    <col min="27" max="27" width="7.77734375" style="24" customWidth="1"/>
+    <col min="28" max="31" width="7.77734375" style="3" customWidth="1"/>
+    <col min="32" max="32" width="7.77734375" style="24" customWidth="1"/>
+    <col min="33" max="36" width="7.77734375" style="3" customWidth="1"/>
+    <col min="37" max="37" width="7.77734375" style="24" customWidth="1"/>
+    <col min="38" max="41" width="7.77734375" style="3" customWidth="1"/>
+    <col min="42" max="42" width="7.77734375" style="24" customWidth="1"/>
+    <col min="43" max="46" width="7.77734375" style="3" customWidth="1"/>
+    <col min="47" max="47" width="7.77734375" style="24" customWidth="1"/>
+    <col min="48" max="50" width="4.6640625" style="3" customWidth="1"/>
+    <col min="51" max="51" width="4.6640625" style="24" customWidth="1"/>
+    <col min="52" max="55" width="4.6640625" style="3" customWidth="1"/>
+    <col min="56" max="56" width="4.6640625" style="24" customWidth="1"/>
+    <col min="57" max="59" width="4.6640625" style="3" customWidth="1"/>
+    <col min="60" max="60" width="4.6640625" style="24" customWidth="1"/>
+    <col min="61" max="64" width="4.6640625" style="3" customWidth="1"/>
+    <col min="65" max="65" width="4.6640625" style="24" customWidth="1"/>
+    <col min="66" max="68" width="4.6640625" style="3" customWidth="1"/>
+    <col min="69" max="69" width="4.6640625" style="24" customWidth="1"/>
+    <col min="70" max="72" width="4.6640625" style="3" customWidth="1"/>
+    <col min="73" max="73" width="4.6640625" style="24" customWidth="1"/>
+    <col min="74" max="77" width="4.6640625" style="3" customWidth="1"/>
+    <col min="78" max="78" width="4.6640625" style="24" customWidth="1"/>
+    <col min="79" max="108" width="2.6640625" style="3" customWidth="1"/>
+    <col min="109" max="16384" width="3" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:78" s="1" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B1" s="38"/>
+      <c r="C1" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="AS1" s="58" t="s">
+        <v>33</v>
+      </c>
+      <c r="AT1" s="78" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU1" s="86" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:78" s="1" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="11"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+      <c r="J2" s="27"/>
+      <c r="K2" s="27"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="39"/>
+      <c r="T2" s="39"/>
+      <c r="U2" s="39"/>
+      <c r="V2" s="27"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="27"/>
+      <c r="Y2" s="27"/>
+      <c r="Z2" s="27"/>
+      <c r="AA2" s="27"/>
+      <c r="AB2" s="27"/>
+      <c r="AC2" s="27"/>
+      <c r="AD2" s="27"/>
+      <c r="AE2" s="27"/>
+      <c r="AF2" s="27"/>
+      <c r="AG2" s="27"/>
+      <c r="AH2" s="27"/>
+      <c r="AI2" s="27"/>
+      <c r="AJ2" s="27"/>
+      <c r="AK2" s="27"/>
+      <c r="AL2" s="27"/>
+      <c r="AM2" s="27"/>
+      <c r="AN2" s="27"/>
+      <c r="AO2" s="39"/>
+      <c r="AP2" s="27"/>
+      <c r="AQ2" s="27"/>
+      <c r="AR2" s="27"/>
+      <c r="AS2" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="AT2" s="27"/>
+      <c r="AU2" s="27"/>
+      <c r="AV2" s="27"/>
+      <c r="AW2" s="27"/>
+      <c r="AX2" s="27"/>
+      <c r="AY2" s="27"/>
+      <c r="AZ2" s="27"/>
+      <c r="BA2" s="27"/>
+      <c r="BB2" s="27"/>
+      <c r="BC2" s="27"/>
+      <c r="BD2" s="27"/>
+      <c r="BE2" s="27"/>
+      <c r="BF2" s="27"/>
+      <c r="BG2" s="27"/>
+      <c r="BH2" s="27"/>
+      <c r="BI2" s="27"/>
+      <c r="BJ2" s="27"/>
+      <c r="BK2" s="27"/>
+      <c r="BL2" s="27"/>
+      <c r="BM2" s="27"/>
+      <c r="BN2" s="27"/>
+      <c r="BO2" s="27"/>
+      <c r="BP2" s="27"/>
+      <c r="BQ2" s="27"/>
+      <c r="BR2" s="27"/>
+      <c r="BS2" s="27"/>
+      <c r="BT2" s="27"/>
+      <c r="BU2" s="27"/>
+      <c r="BV2" s="27"/>
+      <c r="BW2" s="27"/>
+      <c r="BX2" s="27"/>
+      <c r="BY2" s="27"/>
+    </row>
+    <row r="3" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B3" s="91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="93"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="72" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="4"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3" s="4"/>
+      <c r="T3" s="4"/>
+      <c r="U3" s="4"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="4"/>
+      <c r="AA3" s="22"/>
+      <c r="AB3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC3" s="4"/>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="22"/>
+      <c r="AG3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="4"/>
+      <c r="AJ3" s="4"/>
+      <c r="AK3" s="22"/>
+      <c r="AL3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM3" s="4"/>
+      <c r="AN3" s="4"/>
+      <c r="AO3" s="4"/>
+      <c r="AP3" s="22"/>
+      <c r="AQ3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AR3" s="4"/>
+      <c r="AS3" s="4"/>
+      <c r="AT3" s="4"/>
+      <c r="AU3" s="22"/>
+      <c r="AV3" s="3"/>
+      <c r="AW3" s="3"/>
+      <c r="AX3" s="3"/>
+      <c r="AY3" s="3"/>
+      <c r="AZ3" s="3"/>
+      <c r="BA3" s="3"/>
+      <c r="BB3" s="3"/>
+      <c r="BC3" s="3"/>
+      <c r="BD3" s="3"/>
+      <c r="BE3" s="3"/>
+      <c r="BF3" s="3"/>
+      <c r="BG3" s="3"/>
+      <c r="BH3" s="3"/>
+      <c r="BI3" s="3"/>
+      <c r="BJ3" s="3"/>
+      <c r="BK3" s="3"/>
+      <c r="BL3" s="3"/>
+      <c r="BM3" s="3"/>
+      <c r="BN3" s="3"/>
+      <c r="BO3" s="3"/>
+      <c r="BP3" s="3"/>
+      <c r="BQ3" s="3"/>
+      <c r="BR3" s="3"/>
+      <c r="BS3" s="3"/>
+      <c r="BT3" s="3"/>
+      <c r="BU3" s="3"/>
+      <c r="BV3" s="3"/>
+      <c r="BW3" s="3"/>
+      <c r="BX3" s="3"/>
+      <c r="BY3" s="3"/>
+      <c r="BZ3" s="3"/>
+    </row>
+    <row r="4" spans="1:78" s="2" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B4" s="92"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="96"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="71">
+        <v>1</v>
+      </c>
+      <c r="G4" s="8">
+        <v>2</v>
+      </c>
+      <c r="H4" s="7">
+        <v>3</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1</v>
+      </c>
+      <c r="J4" s="8">
+        <v>2</v>
+      </c>
+      <c r="K4" s="8">
+        <v>3</v>
+      </c>
+      <c r="L4" s="8">
+        <v>4</v>
+      </c>
+      <c r="M4" s="23">
+        <v>5</v>
+      </c>
+      <c r="N4" s="5">
+        <v>1</v>
+      </c>
+      <c r="O4" s="8">
+        <v>2</v>
+      </c>
+      <c r="P4" s="8">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="23">
+        <v>4</v>
+      </c>
+      <c r="R4" s="5">
+        <v>1</v>
+      </c>
+      <c r="S4" s="8">
+        <v>2</v>
+      </c>
+      <c r="T4" s="8">
+        <v>3</v>
+      </c>
+      <c r="U4" s="8">
+        <v>4</v>
+      </c>
+      <c r="V4" s="23">
+        <v>5</v>
+      </c>
+      <c r="W4" s="5">
+        <v>1</v>
+      </c>
+      <c r="X4" s="8">
+        <v>2</v>
+      </c>
+      <c r="Y4" s="8">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AA4" s="23">
+        <v>5</v>
+      </c>
+      <c r="AB4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AD4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AE4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AF4" s="23">
+        <v>5</v>
+      </c>
+      <c r="AG4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AI4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AJ4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AK4" s="23">
+        <v>5</v>
+      </c>
+      <c r="AL4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AN4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AO4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AP4" s="23">
+        <v>5</v>
+      </c>
+      <c r="AQ4" s="5">
+        <v>1</v>
+      </c>
+      <c r="AR4" s="8">
+        <v>2</v>
+      </c>
+      <c r="AS4" s="8">
+        <v>3</v>
+      </c>
+      <c r="AT4" s="8">
+        <v>4</v>
+      </c>
+      <c r="AU4" s="23">
+        <v>5</v>
+      </c>
+      <c r="AV4" s="3"/>
+      <c r="AW4" s="3"/>
+      <c r="AX4" s="3"/>
+      <c r="AY4" s="3"/>
+      <c r="AZ4" s="3"/>
+      <c r="BA4" s="3"/>
+      <c r="BB4" s="3"/>
+      <c r="BC4" s="3"/>
+      <c r="BD4" s="3"/>
+      <c r="BE4" s="3"/>
+      <c r="BF4" s="3"/>
+      <c r="BG4" s="3"/>
+      <c r="BH4" s="3"/>
+      <c r="BI4" s="3"/>
+      <c r="BJ4" s="3"/>
+      <c r="BK4" s="3"/>
+      <c r="BL4" s="3"/>
+      <c r="BM4" s="3"/>
+      <c r="BN4" s="3"/>
+      <c r="BO4" s="3"/>
+      <c r="BP4" s="3"/>
+      <c r="BQ4" s="3"/>
+      <c r="BR4" s="3"/>
+      <c r="BS4" s="3"/>
+      <c r="BT4" s="3"/>
+      <c r="BU4" s="3"/>
+      <c r="BV4" s="3"/>
+      <c r="BW4" s="3"/>
+      <c r="BX4" s="3"/>
+      <c r="BY4" s="3"/>
+      <c r="BZ4" s="3"/>
+    </row>
+    <row r="5" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B5" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="52"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="63">
+        <v>45919</v>
+      </c>
+      <c r="I5" s="47"/>
+      <c r="J5" s="44"/>
+      <c r="K5" s="44"/>
+      <c r="L5" s="46"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="19"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="15"/>
+      <c r="X5" s="15"/>
+      <c r="Y5" s="9"/>
+      <c r="Z5" s="9"/>
+      <c r="AA5" s="10"/>
+      <c r="AB5" s="15"/>
+      <c r="AC5" s="9"/>
+      <c r="AD5" s="9"/>
+      <c r="AE5" s="9"/>
+      <c r="AF5" s="10"/>
+      <c r="AG5" s="15"/>
+      <c r="AH5" s="15"/>
+      <c r="AI5" s="9"/>
+      <c r="AJ5" s="9"/>
+      <c r="AK5" s="10"/>
+      <c r="AL5" s="15"/>
+      <c r="AM5" s="9"/>
+      <c r="AN5" s="9"/>
+      <c r="AO5" s="19"/>
+      <c r="AP5" s="10"/>
+      <c r="AQ5" s="15"/>
+      <c r="AR5" s="9"/>
+      <c r="AS5" s="9"/>
+      <c r="AT5" s="9"/>
+      <c r="AU5" s="10"/>
+      <c r="AY5" s="3"/>
+      <c r="BD5" s="3"/>
+      <c r="BH5" s="3"/>
+      <c r="BM5" s="3"/>
+      <c r="BQ5" s="3"/>
+      <c r="BU5" s="3"/>
+      <c r="BZ5" s="3"/>
+    </row>
+    <row r="6" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B6" s="17"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="90"/>
+      <c r="E6" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="82"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="85">
+        <v>45917</v>
+      </c>
+      <c r="I6" s="51"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="49"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="30"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="32"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="29"/>
+      <c r="Z6" s="29"/>
+      <c r="AA6" s="30"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="30"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="31"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="32"/>
+      <c r="AP6" s="30"/>
+      <c r="AQ6" s="31"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="30"/>
+      <c r="AY6" s="3"/>
+      <c r="BD6" s="3"/>
+      <c r="BH6" s="3"/>
+      <c r="BM6" s="3"/>
+      <c r="BQ6" s="3"/>
+      <c r="BU6" s="3"/>
+      <c r="BZ6" s="3"/>
+    </row>
+    <row r="7" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B7" s="17"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="89" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="52"/>
+      <c r="G7" s="53"/>
+      <c r="H7" s="63">
+        <v>45919</v>
+      </c>
+      <c r="I7" s="65"/>
+      <c r="J7" s="66"/>
+      <c r="K7" s="66"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="68"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="29"/>
+      <c r="Q7" s="30"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="29"/>
+      <c r="T7" s="29"/>
+      <c r="U7" s="32"/>
+      <c r="V7" s="30"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29"/>
+      <c r="AA7" s="30"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="29"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="29"/>
+      <c r="AF7" s="30"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="31"/>
+      <c r="AI7" s="29"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="30"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="29"/>
+      <c r="AO7" s="32"/>
+      <c r="AP7" s="30"/>
+      <c r="AQ7" s="31"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="30"/>
+      <c r="AY7" s="3"/>
+      <c r="BD7" s="3"/>
+      <c r="BH7" s="3"/>
+      <c r="BM7" s="3"/>
+      <c r="BQ7" s="3"/>
+      <c r="BU7" s="3"/>
+      <c r="BZ7" s="3"/>
+    </row>
+    <row r="8" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B8" s="17"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="90"/>
+      <c r="E8" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="82"/>
+      <c r="G8" s="83"/>
+      <c r="H8" s="85">
+        <v>45917</v>
+      </c>
+      <c r="I8" s="51"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="30"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="29"/>
+      <c r="T8" s="29"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="30"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="29"/>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="30"/>
+      <c r="AB8" s="31"/>
+      <c r="AC8" s="29"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="29"/>
+      <c r="AF8" s="30"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="31"/>
+      <c r="AI8" s="29"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="30"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="29"/>
+      <c r="AO8" s="32"/>
+      <c r="AP8" s="30"/>
+      <c r="AQ8" s="31"/>
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="30"/>
+      <c r="AY8" s="3"/>
+      <c r="BD8" s="3"/>
+      <c r="BH8" s="3"/>
+      <c r="BM8" s="3"/>
+      <c r="BQ8" s="3"/>
+      <c r="BU8" s="3"/>
+      <c r="BZ8" s="3"/>
+    </row>
+    <row r="9" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B9" s="17"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="89" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="53"/>
+      <c r="G9" s="53"/>
+      <c r="H9" s="64">
+        <v>45917</v>
+      </c>
+      <c r="I9" s="51"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="49"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="29"/>
+      <c r="Q9" s="30"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="29"/>
+      <c r="T9" s="29"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="30"/>
+      <c r="AB9" s="31"/>
+      <c r="AC9" s="29"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="29"/>
+      <c r="AF9" s="30"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="31"/>
+      <c r="AI9" s="29"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="29"/>
+      <c r="AO9" s="32"/>
+      <c r="AP9" s="30"/>
+      <c r="AQ9" s="31"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="30"/>
+      <c r="AY9" s="3"/>
+      <c r="BD9" s="3"/>
+      <c r="BH9" s="3"/>
+      <c r="BM9" s="3"/>
+      <c r="BQ9" s="3"/>
+      <c r="BU9" s="3"/>
+      <c r="BZ9" s="3"/>
+    </row>
+    <row r="10" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B10" s="17"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="90"/>
+      <c r="E10" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" s="82"/>
+      <c r="G10" s="83"/>
+      <c r="H10" s="85">
+        <v>45918</v>
+      </c>
+      <c r="I10" s="51"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="49"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="29"/>
+      <c r="Q10" s="30"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="29"/>
+      <c r="T10" s="29"/>
+      <c r="U10" s="32"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="29"/>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="30"/>
+      <c r="AB10" s="31"/>
+      <c r="AC10" s="29"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="29"/>
+      <c r="AF10" s="30"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="31"/>
+      <c r="AI10" s="29"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="29"/>
+      <c r="AO10" s="32"/>
+      <c r="AP10" s="30"/>
+      <c r="AQ10" s="31"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="30"/>
+      <c r="AY10" s="3"/>
+      <c r="BD10" s="3"/>
+      <c r="BH10" s="3"/>
+      <c r="BM10" s="3"/>
+      <c r="BQ10" s="3"/>
+      <c r="BU10" s="3"/>
+      <c r="BZ10" s="3"/>
+    </row>
+    <row r="11" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B11" s="17"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="64">
+        <v>45917</v>
+      </c>
+      <c r="I11" s="51"/>
+      <c r="J11" s="48"/>
+      <c r="K11" s="48"/>
+      <c r="L11" s="50"/>
+      <c r="M11" s="49"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="30"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="32"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="30"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="29"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="31"/>
+      <c r="AI11" s="29"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="29"/>
+      <c r="AO11" s="32"/>
+      <c r="AP11" s="30"/>
+      <c r="AQ11" s="31"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="30"/>
+      <c r="AY11" s="3"/>
+      <c r="BD11" s="3"/>
+      <c r="BH11" s="3"/>
+      <c r="BM11" s="3"/>
+      <c r="BQ11" s="3"/>
+      <c r="BU11" s="3"/>
+      <c r="BZ11" s="3"/>
+    </row>
+    <row r="12" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B12" s="17"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="90"/>
+      <c r="E12" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="82"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="85">
+        <v>45917</v>
+      </c>
+      <c r="I12" s="51"/>
+      <c r="J12" s="48"/>
+      <c r="K12" s="48"/>
+      <c r="L12" s="50"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="29"/>
+      <c r="Q12" s="30"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="29"/>
+      <c r="T12" s="29"/>
+      <c r="U12" s="32"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="30"/>
+      <c r="AB12" s="31"/>
+      <c r="AC12" s="29"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="29"/>
+      <c r="AF12" s="30"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="31"/>
+      <c r="AI12" s="29"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="29"/>
+      <c r="AO12" s="32"/>
+      <c r="AP12" s="30"/>
+      <c r="AQ12" s="31"/>
+      <c r="AR12" s="29"/>
+      <c r="AS12" s="29"/>
+      <c r="AT12" s="29"/>
+      <c r="AU12" s="30"/>
+      <c r="AY12" s="3"/>
+      <c r="BD12" s="3"/>
+      <c r="BH12" s="3"/>
+      <c r="BM12" s="3"/>
+      <c r="BQ12" s="3"/>
+      <c r="BU12" s="3"/>
+      <c r="BZ12" s="3"/>
+    </row>
+    <row r="13" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B13" s="17"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="89" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="64">
+        <v>45917</v>
+      </c>
+      <c r="I13" s="51"/>
+      <c r="J13" s="48"/>
+      <c r="K13" s="48"/>
+      <c r="L13" s="50"/>
+      <c r="M13" s="49"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="29"/>
+      <c r="Q13" s="30"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="29"/>
+      <c r="U13" s="32"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="30"/>
+      <c r="AB13" s="31"/>
+      <c r="AC13" s="29"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="29"/>
+      <c r="AF13" s="30"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="31"/>
+      <c r="AI13" s="29"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="29"/>
+      <c r="AO13" s="32"/>
+      <c r="AP13" s="30"/>
+      <c r="AQ13" s="31"/>
+      <c r="AR13" s="29"/>
+      <c r="AS13" s="29"/>
+      <c r="AT13" s="29"/>
+      <c r="AU13" s="30"/>
+      <c r="AY13" s="3"/>
+      <c r="BD13" s="3"/>
+      <c r="BH13" s="3"/>
+      <c r="BM13" s="3"/>
+      <c r="BQ13" s="3"/>
+      <c r="BU13" s="3"/>
+      <c r="BZ13" s="3"/>
+    </row>
+    <row r="14" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B14" s="17"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="90"/>
+      <c r="E14" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F14" s="82"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="85">
+        <v>45917</v>
+      </c>
+      <c r="I14" s="51"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="50"/>
+      <c r="M14" s="49"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="30"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="29"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="32"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="30"/>
+      <c r="AB14" s="31"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="29"/>
+      <c r="AF14" s="30"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="31"/>
+      <c r="AI14" s="29"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="30"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="29"/>
+      <c r="AO14" s="32"/>
+      <c r="AP14" s="30"/>
+      <c r="AQ14" s="31"/>
+      <c r="AR14" s="29"/>
+      <c r="AS14" s="29"/>
+      <c r="AT14" s="29"/>
+      <c r="AU14" s="30"/>
+      <c r="AY14" s="3"/>
+      <c r="BD14" s="3"/>
+      <c r="BH14" s="3"/>
+      <c r="BM14" s="3"/>
+      <c r="BQ14" s="3"/>
+      <c r="BU14" s="3"/>
+      <c r="BZ14" s="3"/>
+    </row>
+    <row r="15" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B15" s="17"/>
+      <c r="C15" s="40" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="49"/>
+      <c r="I15" s="57"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="59" t="s">
+        <v>36</v>
+      </c>
+      <c r="N15" s="31"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="30"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="29"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="32"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="30"/>
+      <c r="AB15" s="31"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="29"/>
+      <c r="AF15" s="30"/>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="31"/>
+      <c r="AI15" s="29"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="29"/>
+      <c r="AO15" s="32"/>
+      <c r="AP15" s="30"/>
+      <c r="AQ15" s="31"/>
+      <c r="AR15" s="29"/>
+      <c r="AS15" s="29"/>
+      <c r="AT15" s="29"/>
+      <c r="AU15" s="30"/>
+      <c r="AY15" s="3"/>
+      <c r="BD15" s="3"/>
+      <c r="BH15" s="3"/>
+      <c r="BM15" s="3"/>
+      <c r="BQ15" s="3"/>
+      <c r="BU15" s="3"/>
+      <c r="BZ15" s="3"/>
+    </row>
+    <row r="16" spans="1:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B16" s="17"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F16" s="82"/>
+      <c r="G16" s="83"/>
+      <c r="H16" s="84"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="78"/>
+      <c r="L16" s="80"/>
+      <c r="M16" s="81">
+        <v>45919</v>
+      </c>
+      <c r="N16" s="31"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="29"/>
+      <c r="Q16" s="30"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="29"/>
+      <c r="T16" s="29"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="30"/>
+      <c r="AB16" s="31"/>
+      <c r="AC16" s="29"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="29"/>
+      <c r="AF16" s="30"/>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="31"/>
+      <c r="AI16" s="29"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="31"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="29"/>
+      <c r="AO16" s="32"/>
+      <c r="AP16" s="30"/>
+      <c r="AQ16" s="31"/>
+      <c r="AR16" s="29"/>
+      <c r="AS16" s="29"/>
+      <c r="AT16" s="29"/>
+      <c r="AU16" s="30"/>
+      <c r="AY16" s="3"/>
+      <c r="BD16" s="3"/>
+      <c r="BH16" s="3"/>
+      <c r="BM16" s="3"/>
+      <c r="BQ16" s="3"/>
+      <c r="BU16" s="3"/>
+      <c r="BZ16" s="3"/>
+    </row>
+    <row r="17" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B17" s="17"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="89" t="s">
+        <v>25</v>
+      </c>
+      <c r="E17" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="51"/>
+      <c r="G17" s="48"/>
+      <c r="H17" s="49"/>
+      <c r="I17" s="57"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="59" t="s">
+        <v>35</v>
+      </c>
+      <c r="N17" s="31"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="29"/>
+      <c r="Q17" s="30"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="29"/>
+      <c r="T17" s="29"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="30"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="29"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="29"/>
+      <c r="AF17" s="30"/>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="31"/>
+      <c r="AI17" s="29"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="30"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="29"/>
+      <c r="AO17" s="32"/>
+      <c r="AP17" s="30"/>
+      <c r="AQ17" s="31"/>
+      <c r="AR17" s="29"/>
+      <c r="AS17" s="29"/>
+      <c r="AT17" s="29"/>
+      <c r="AU17" s="30"/>
+      <c r="AY17" s="3"/>
+      <c r="BD17" s="3"/>
+      <c r="BH17" s="3"/>
+      <c r="BM17" s="3"/>
+      <c r="BQ17" s="3"/>
+      <c r="BU17" s="3"/>
+      <c r="BZ17" s="3"/>
+    </row>
+    <row r="18" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="17"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="82"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="84"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="78"/>
+      <c r="L18" s="80"/>
+      <c r="M18" s="81">
+        <v>45919</v>
+      </c>
+      <c r="N18" s="31"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="29"/>
+      <c r="Q18" s="30"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="29"/>
+      <c r="T18" s="29"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="30"/>
+      <c r="AB18" s="31"/>
+      <c r="AC18" s="29"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="29"/>
+      <c r="AF18" s="30"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="31"/>
+      <c r="AI18" s="29"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="29"/>
+      <c r="AN18" s="29"/>
+      <c r="AO18" s="32"/>
+      <c r="AP18" s="30"/>
+      <c r="AQ18" s="31"/>
+      <c r="AR18" s="29"/>
+      <c r="AS18" s="29"/>
+      <c r="AT18" s="29"/>
+      <c r="AU18" s="30"/>
+      <c r="AY18" s="3"/>
+      <c r="BD18" s="3"/>
+      <c r="BH18" s="3"/>
+      <c r="BM18" s="3"/>
+      <c r="BQ18" s="3"/>
+      <c r="BU18" s="3"/>
+      <c r="BZ18" s="3"/>
+    </row>
+    <row r="19" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B19" s="17"/>
+      <c r="C19" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="D19" s="89" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="12"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="48"/>
+      <c r="K19" s="48"/>
+      <c r="L19" s="48"/>
+      <c r="M19" s="49"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="59" t="s">
+        <v>37</v>
+      </c>
+      <c r="R19" s="21"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="13"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="12"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+      <c r="AF19" s="14"/>
+      <c r="AG19" s="12"/>
+      <c r="AH19" s="12"/>
+      <c r="AI19" s="13"/>
+      <c r="AJ19" s="13"/>
+      <c r="AK19" s="14"/>
+      <c r="AL19" s="12"/>
+      <c r="AM19" s="13"/>
+      <c r="AN19" s="13"/>
+      <c r="AO19" s="20"/>
+      <c r="AP19" s="14"/>
+      <c r="AQ19" s="12"/>
+      <c r="AR19" s="13"/>
+      <c r="AS19" s="13"/>
+      <c r="AT19" s="13"/>
+      <c r="AU19" s="14"/>
+      <c r="AY19" s="3"/>
+      <c r="BD19" s="3"/>
+      <c r="BH19" s="3"/>
+      <c r="BM19" s="3"/>
+      <c r="BQ19" s="3"/>
+      <c r="BU19" s="3"/>
+      <c r="BZ19" s="3"/>
+    </row>
+    <row r="20" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B20" s="17"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="12"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="79"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="81">
+        <v>45922</v>
+      </c>
+      <c r="R20" s="21"/>
+      <c r="S20" s="18"/>
+      <c r="T20" s="18"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="26"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+      <c r="AF20" s="14"/>
+      <c r="AG20" s="12"/>
+      <c r="AH20" s="12"/>
+      <c r="AI20" s="13"/>
+      <c r="AJ20" s="13"/>
+      <c r="AK20" s="14"/>
+      <c r="AL20" s="12"/>
+      <c r="AM20" s="13"/>
+      <c r="AN20" s="13"/>
+      <c r="AO20" s="20"/>
+      <c r="AP20" s="14"/>
+      <c r="AQ20" s="12"/>
+      <c r="AR20" s="13"/>
+      <c r="AS20" s="13"/>
+      <c r="AT20" s="13"/>
+      <c r="AU20" s="14"/>
+      <c r="AY20" s="3"/>
+      <c r="BD20" s="3"/>
+      <c r="BH20" s="3"/>
+      <c r="BM20" s="3"/>
+      <c r="BQ20" s="3"/>
+      <c r="BU20" s="3"/>
+      <c r="BZ20" s="3"/>
+    </row>
+    <row r="21" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B21" s="17"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="12"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="51"/>
+      <c r="J21" s="48"/>
+      <c r="K21" s="48"/>
+      <c r="L21" s="48"/>
+      <c r="M21" s="49"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="R21" s="21"/>
+      <c r="S21" s="18"/>
+      <c r="T21" s="18"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="26"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="12"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+      <c r="AF21" s="14"/>
+      <c r="AG21" s="12"/>
+      <c r="AH21" s="12"/>
+      <c r="AI21" s="13"/>
+      <c r="AJ21" s="13"/>
+      <c r="AK21" s="14"/>
+      <c r="AL21" s="12"/>
+      <c r="AM21" s="13"/>
+      <c r="AN21" s="13"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="14"/>
+      <c r="AQ21" s="12"/>
+      <c r="AR21" s="13"/>
+      <c r="AS21" s="13"/>
+      <c r="AT21" s="13"/>
+      <c r="AU21" s="14"/>
+      <c r="AY21" s="3"/>
+      <c r="BD21" s="3"/>
+      <c r="BH21" s="3"/>
+      <c r="BM21" s="3"/>
+      <c r="BQ21" s="3"/>
+      <c r="BU21" s="3"/>
+      <c r="BZ21" s="3"/>
+    </row>
+    <row r="22" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B22" s="17"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="90"/>
+      <c r="E22" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="12"/>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="79"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="78"/>
+      <c r="Q22" s="81">
+        <v>45946</v>
+      </c>
+      <c r="R22" s="21"/>
+      <c r="S22" s="18"/>
+      <c r="T22" s="18"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="26"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="12"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+      <c r="AF22" s="14"/>
+      <c r="AG22" s="12"/>
+      <c r="AH22" s="12"/>
+      <c r="AI22" s="13"/>
+      <c r="AJ22" s="13"/>
+      <c r="AK22" s="14"/>
+      <c r="AL22" s="12"/>
+      <c r="AM22" s="13"/>
+      <c r="AN22" s="13"/>
+      <c r="AO22" s="20"/>
+      <c r="AP22" s="14"/>
+      <c r="AQ22" s="12"/>
+      <c r="AR22" s="13"/>
+      <c r="AS22" s="13"/>
+      <c r="AT22" s="13"/>
+      <c r="AU22" s="14"/>
+      <c r="AY22" s="3"/>
+      <c r="BD22" s="3"/>
+      <c r="BH22" s="3"/>
+      <c r="BM22" s="3"/>
+      <c r="BQ22" s="3"/>
+      <c r="BU22" s="3"/>
+      <c r="BZ22" s="3"/>
+    </row>
+    <row r="23" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B23" s="17"/>
+      <c r="C23" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" s="89" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="12"/>
+      <c r="G23" s="13"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="51"/>
+      <c r="J23" s="48"/>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23" s="49"/>
+      <c r="N23" s="21"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="57"/>
+      <c r="S23" s="58"/>
+      <c r="T23" s="58"/>
+      <c r="U23" s="58"/>
+      <c r="V23" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+      <c r="AF23" s="14"/>
+      <c r="AG23" s="12"/>
+      <c r="AH23" s="12"/>
+      <c r="AI23" s="13"/>
+      <c r="AJ23" s="13"/>
+      <c r="AK23" s="14"/>
+      <c r="AL23" s="12"/>
+      <c r="AM23" s="13"/>
+      <c r="AN23" s="13"/>
+      <c r="AO23" s="20"/>
+      <c r="AP23" s="14"/>
+      <c r="AQ23" s="12"/>
+      <c r="AR23" s="13"/>
+      <c r="AS23" s="13"/>
+      <c r="AT23" s="13"/>
+      <c r="AU23" s="14"/>
+      <c r="AY23" s="3"/>
+      <c r="BD23" s="3"/>
+      <c r="BH23" s="3"/>
+      <c r="BM23" s="3"/>
+      <c r="BQ23" s="3"/>
+      <c r="BU23" s="3"/>
+      <c r="BZ23" s="3"/>
+    </row>
+    <row r="24" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B24" s="17"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="12"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="77"/>
+      <c r="J24" s="78"/>
+      <c r="K24" s="78"/>
+      <c r="L24" s="80"/>
+      <c r="M24" s="79"/>
+      <c r="N24" s="77"/>
+      <c r="O24" s="78"/>
+      <c r="P24" s="78"/>
+      <c r="Q24" s="79"/>
+      <c r="R24" s="77"/>
+      <c r="S24" s="78"/>
+      <c r="T24" s="78"/>
+      <c r="U24" s="80"/>
+      <c r="V24" s="81">
+        <v>45923</v>
+      </c>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="12"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+      <c r="AF24" s="14"/>
+      <c r="AG24" s="12"/>
+      <c r="AH24" s="12"/>
+      <c r="AI24" s="13"/>
+      <c r="AJ24" s="13"/>
+      <c r="AK24" s="14"/>
+      <c r="AL24" s="12"/>
+      <c r="AM24" s="13"/>
+      <c r="AN24" s="13"/>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="14"/>
+      <c r="AQ24" s="12"/>
+      <c r="AR24" s="13"/>
+      <c r="AS24" s="13"/>
+      <c r="AT24" s="13"/>
+      <c r="AU24" s="14"/>
+      <c r="AY24" s="3"/>
+      <c r="BD24" s="3"/>
+      <c r="BH24" s="3"/>
+      <c r="BM24" s="3"/>
+      <c r="BQ24" s="3"/>
+      <c r="BU24" s="3"/>
+      <c r="BZ24" s="3"/>
+    </row>
+    <row r="25" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B25" s="17"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="89" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="12"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="51"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="49"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="18"/>
+      <c r="P25" s="18"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="57"/>
+      <c r="S25" s="58"/>
+      <c r="T25" s="58"/>
+      <c r="U25" s="58"/>
+      <c r="V25" s="59" t="s">
+        <v>40</v>
+      </c>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="12"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="13"/>
+      <c r="AF25" s="14"/>
+      <c r="AG25" s="12"/>
+      <c r="AH25" s="12"/>
+      <c r="AI25" s="13"/>
+      <c r="AJ25" s="13"/>
+      <c r="AK25" s="14"/>
+      <c r="AL25" s="12"/>
+      <c r="AM25" s="13"/>
+      <c r="AN25" s="13"/>
+      <c r="AO25" s="20"/>
+      <c r="AP25" s="14"/>
+      <c r="AQ25" s="12"/>
+      <c r="AR25" s="13"/>
+      <c r="AS25" s="13"/>
+      <c r="AT25" s="13"/>
+      <c r="AU25" s="14"/>
+      <c r="AY25" s="3"/>
+      <c r="BD25" s="3"/>
+      <c r="BH25" s="3"/>
+      <c r="BM25" s="3"/>
+      <c r="BQ25" s="3"/>
+      <c r="BU25" s="3"/>
+      <c r="BZ25" s="3"/>
+    </row>
+    <row r="26" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B26" s="17"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="90"/>
+      <c r="E26" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="12"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="77"/>
+      <c r="J26" s="78"/>
+      <c r="K26" s="78"/>
+      <c r="L26" s="80"/>
+      <c r="M26" s="79"/>
+      <c r="N26" s="77"/>
+      <c r="O26" s="78"/>
+      <c r="P26" s="78"/>
+      <c r="Q26" s="79"/>
+      <c r="R26" s="77"/>
+      <c r="S26" s="78"/>
+      <c r="T26" s="78"/>
+      <c r="U26" s="80"/>
+      <c r="V26" s="81">
+        <v>45924</v>
+      </c>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+      <c r="AF26" s="14"/>
+      <c r="AG26" s="12"/>
+      <c r="AH26" s="12"/>
+      <c r="AI26" s="13"/>
+      <c r="AJ26" s="13"/>
+      <c r="AK26" s="14"/>
+      <c r="AL26" s="12"/>
+      <c r="AM26" s="13"/>
+      <c r="AN26" s="13"/>
+      <c r="AO26" s="20"/>
+      <c r="AP26" s="14"/>
+      <c r="AQ26" s="12"/>
+      <c r="AR26" s="13"/>
+      <c r="AS26" s="13"/>
+      <c r="AT26" s="13"/>
+      <c r="AU26" s="14"/>
+      <c r="AY26" s="3"/>
+      <c r="BD26" s="3"/>
+      <c r="BH26" s="3"/>
+      <c r="BM26" s="3"/>
+      <c r="BQ26" s="3"/>
+      <c r="BU26" s="3"/>
+      <c r="BZ26" s="3"/>
+    </row>
+    <row r="27" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B27" s="17"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="89" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="12"/>
+      <c r="G27" s="13"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="51"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="49"/>
+      <c r="N27" s="21"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="57"/>
+      <c r="S27" s="58"/>
+      <c r="T27" s="58"/>
+      <c r="U27" s="58"/>
+      <c r="V27" s="59" t="s">
+        <v>41</v>
+      </c>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="12"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+      <c r="AF27" s="14"/>
+      <c r="AG27" s="12"/>
+      <c r="AH27" s="12"/>
+      <c r="AI27" s="13"/>
+      <c r="AJ27" s="13"/>
+      <c r="AK27" s="14"/>
+      <c r="AL27" s="12"/>
+      <c r="AM27" s="13"/>
+      <c r="AN27" s="13"/>
+      <c r="AO27" s="20"/>
+      <c r="AP27" s="14"/>
+      <c r="AQ27" s="12"/>
+      <c r="AR27" s="13"/>
+      <c r="AS27" s="13"/>
+      <c r="AT27" s="13"/>
+      <c r="AU27" s="14"/>
+      <c r="AY27" s="3"/>
+      <c r="BD27" s="3"/>
+      <c r="BH27" s="3"/>
+      <c r="BM27" s="3"/>
+      <c r="BQ27" s="3"/>
+      <c r="BU27" s="3"/>
+      <c r="BZ27" s="3"/>
+    </row>
+    <row r="28" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B28" s="17"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F28" s="12"/>
+      <c r="G28" s="13"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="77"/>
+      <c r="J28" s="78"/>
+      <c r="K28" s="78"/>
+      <c r="L28" s="80"/>
+      <c r="M28" s="79"/>
+      <c r="N28" s="77"/>
+      <c r="O28" s="78"/>
+      <c r="P28" s="78"/>
+      <c r="Q28" s="79"/>
+      <c r="R28" s="77"/>
+      <c r="S28" s="78"/>
+      <c r="T28" s="78"/>
+      <c r="U28" s="80"/>
+      <c r="V28" s="81">
+        <v>45924</v>
+      </c>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="12"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+      <c r="AF28" s="14"/>
+      <c r="AG28" s="12"/>
+      <c r="AH28" s="12"/>
+      <c r="AI28" s="13"/>
+      <c r="AJ28" s="13"/>
+      <c r="AK28" s="14"/>
+      <c r="AL28" s="12"/>
+      <c r="AM28" s="13"/>
+      <c r="AN28" s="13"/>
+      <c r="AO28" s="20"/>
+      <c r="AP28" s="14"/>
+      <c r="AQ28" s="12"/>
+      <c r="AR28" s="13"/>
+      <c r="AS28" s="13"/>
+      <c r="AT28" s="13"/>
+      <c r="AU28" s="14"/>
+      <c r="AY28" s="3"/>
+      <c r="BD28" s="3"/>
+      <c r="BH28" s="3"/>
+      <c r="BM28" s="3"/>
+      <c r="BQ28" s="3"/>
+      <c r="BU28" s="3"/>
+      <c r="BZ28" s="3"/>
+    </row>
+    <row r="29" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B29" s="17"/>
+      <c r="C29" s="40" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="89" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="12"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="51"/>
+      <c r="J29" s="48"/>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29" s="49"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="18"/>
+      <c r="P29" s="18"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="18"/>
+      <c r="T29" s="18"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="57"/>
+      <c r="X29" s="58"/>
+      <c r="Y29" s="58"/>
+      <c r="Z29" s="58"/>
+      <c r="AA29" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB29" s="12"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+      <c r="AF29" s="14"/>
+      <c r="AG29" s="12"/>
+      <c r="AH29" s="12"/>
+      <c r="AI29" s="13"/>
+      <c r="AJ29" s="13"/>
+      <c r="AK29" s="14"/>
+      <c r="AL29" s="12"/>
+      <c r="AM29" s="13"/>
+      <c r="AN29" s="13"/>
+      <c r="AO29" s="20"/>
+      <c r="AP29" s="14"/>
+      <c r="AQ29" s="12"/>
+      <c r="AR29" s="13"/>
+      <c r="AS29" s="13"/>
+      <c r="AT29" s="13"/>
+      <c r="AU29" s="14"/>
+      <c r="AY29" s="3"/>
+      <c r="BD29" s="3"/>
+      <c r="BH29" s="3"/>
+      <c r="BM29" s="3"/>
+      <c r="BQ29" s="3"/>
+      <c r="BU29" s="3"/>
+      <c r="BZ29" s="3"/>
+    </row>
+    <row r="30" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B30" s="17"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="12"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="77"/>
+      <c r="O30" s="78"/>
+      <c r="P30" s="78"/>
+      <c r="Q30" s="79"/>
+      <c r="R30" s="77"/>
+      <c r="S30" s="78"/>
+      <c r="T30" s="78"/>
+      <c r="U30" s="80"/>
+      <c r="V30" s="79"/>
+      <c r="W30" s="77"/>
+      <c r="X30" s="78"/>
+      <c r="Y30" s="78"/>
+      <c r="Z30" s="80"/>
+      <c r="AA30" s="81">
+        <v>45929</v>
+      </c>
+      <c r="AB30" s="12"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="13"/>
+      <c r="AF30" s="14"/>
+      <c r="AG30" s="12"/>
+      <c r="AH30" s="12"/>
+      <c r="AI30" s="13"/>
+      <c r="AJ30" s="13"/>
+      <c r="AK30" s="14"/>
+      <c r="AL30" s="12"/>
+      <c r="AM30" s="13"/>
+      <c r="AN30" s="13"/>
+      <c r="AO30" s="20"/>
+      <c r="AP30" s="14"/>
+      <c r="AQ30" s="12"/>
+      <c r="AR30" s="13"/>
+      <c r="AS30" s="13"/>
+      <c r="AT30" s="13"/>
+      <c r="AU30" s="14"/>
+      <c r="AY30" s="3"/>
+      <c r="BD30" s="3"/>
+      <c r="BH30" s="3"/>
+      <c r="BM30" s="3"/>
+      <c r="BQ30" s="3"/>
+      <c r="BU30" s="3"/>
+      <c r="BZ30" s="3"/>
+    </row>
+    <row r="31" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="17"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="89" t="s">
+        <v>60</v>
+      </c>
+      <c r="E31" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="12"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="48"/>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31" s="49"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="18"/>
+      <c r="P31" s="18"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="21"/>
+      <c r="S31" s="18"/>
+      <c r="T31" s="18"/>
+      <c r="U31" s="25"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="57"/>
+      <c r="X31" s="58"/>
+      <c r="Y31" s="58"/>
+      <c r="Z31" s="58"/>
+      <c r="AA31" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="AB31" s="12"/>
+      <c r="AC31" s="13"/>
+      <c r="AD31" s="13"/>
+      <c r="AE31" s="13"/>
+      <c r="AF31" s="14"/>
+      <c r="AG31" s="12"/>
+      <c r="AH31" s="12"/>
+      <c r="AI31" s="13"/>
+      <c r="AJ31" s="13"/>
+      <c r="AK31" s="14"/>
+      <c r="AL31" s="12"/>
+      <c r="AM31" s="13"/>
+      <c r="AN31" s="13"/>
+      <c r="AO31" s="20"/>
+      <c r="AP31" s="14"/>
+      <c r="AQ31" s="12"/>
+      <c r="AR31" s="13"/>
+      <c r="AS31" s="13"/>
+      <c r="AT31" s="13"/>
+      <c r="AU31" s="14"/>
+      <c r="AY31" s="3"/>
+      <c r="BD31" s="3"/>
+      <c r="BH31" s="3"/>
+      <c r="BM31" s="3"/>
+      <c r="BQ31" s="3"/>
+      <c r="BU31" s="3"/>
+      <c r="BZ31" s="3"/>
+    </row>
+    <row r="32" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="17"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="90"/>
+      <c r="E32" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="12"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="77"/>
+      <c r="O32" s="78"/>
+      <c r="P32" s="78"/>
+      <c r="Q32" s="79"/>
+      <c r="R32" s="77"/>
+      <c r="S32" s="78"/>
+      <c r="T32" s="78"/>
+      <c r="U32" s="80"/>
+      <c r="V32" s="79"/>
+      <c r="W32" s="77"/>
+      <c r="X32" s="78"/>
+      <c r="Y32" s="78"/>
+      <c r="Z32" s="80"/>
+      <c r="AA32" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="13"/>
+      <c r="AF32" s="14"/>
+      <c r="AG32" s="12"/>
+      <c r="AH32" s="12"/>
+      <c r="AI32" s="13"/>
+      <c r="AJ32" s="13"/>
+      <c r="AK32" s="14"/>
+      <c r="AL32" s="12"/>
+      <c r="AM32" s="13"/>
+      <c r="AN32" s="13"/>
+      <c r="AO32" s="20"/>
+      <c r="AP32" s="14"/>
+      <c r="AQ32" s="12"/>
+      <c r="AR32" s="13"/>
+      <c r="AS32" s="13"/>
+      <c r="AT32" s="13"/>
+      <c r="AU32" s="14"/>
+      <c r="AY32" s="3"/>
+      <c r="BD32" s="3"/>
+      <c r="BH32" s="3"/>
+      <c r="BM32" s="3"/>
+      <c r="BQ32" s="3"/>
+      <c r="BU32" s="3"/>
+      <c r="BZ32" s="3"/>
+    </row>
+    <row r="33" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B33" s="17"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="12"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="51"/>
+      <c r="J33" s="48"/>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33" s="49"/>
+      <c r="N33" s="21"/>
+      <c r="O33" s="18"/>
+      <c r="P33" s="18"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="21"/>
+      <c r="S33" s="18"/>
+      <c r="T33" s="18"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="51"/>
+      <c r="X33" s="48"/>
+      <c r="Y33" s="48"/>
+      <c r="Z33" s="48"/>
+      <c r="AA33" s="49"/>
+      <c r="AB33" s="57"/>
+      <c r="AC33" s="58"/>
+      <c r="AD33" s="58"/>
+      <c r="AE33" s="58"/>
+      <c r="AF33" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG33" s="12"/>
+      <c r="AH33" s="12"/>
+      <c r="AI33" s="13"/>
+      <c r="AJ33" s="13"/>
+      <c r="AK33" s="14"/>
+      <c r="AL33" s="12"/>
+      <c r="AM33" s="13"/>
+      <c r="AN33" s="13"/>
+      <c r="AO33" s="20"/>
+      <c r="AP33" s="14"/>
+      <c r="AQ33" s="12"/>
+      <c r="AR33" s="13"/>
+      <c r="AS33" s="13"/>
+      <c r="AT33" s="13"/>
+      <c r="AU33" s="14"/>
+      <c r="AY33" s="3"/>
+      <c r="BD33" s="3"/>
+      <c r="BH33" s="3"/>
+      <c r="BM33" s="3"/>
+      <c r="BQ33" s="3"/>
+      <c r="BU33" s="3"/>
+      <c r="BZ33" s="3"/>
+    </row>
+    <row r="34" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B34" s="17"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="90"/>
+      <c r="E34" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="77"/>
+      <c r="O34" s="78"/>
+      <c r="P34" s="78"/>
+      <c r="Q34" s="79"/>
+      <c r="R34" s="77"/>
+      <c r="S34" s="78"/>
+      <c r="T34" s="78"/>
+      <c r="U34" s="80"/>
+      <c r="V34" s="79"/>
+      <c r="W34" s="77"/>
+      <c r="X34" s="78"/>
+      <c r="Y34" s="78"/>
+      <c r="Z34" s="80"/>
+      <c r="AA34" s="79"/>
+      <c r="AB34" s="77"/>
+      <c r="AC34" s="78"/>
+      <c r="AD34" s="78"/>
+      <c r="AE34" s="78"/>
+      <c r="AF34" s="81">
+        <v>45946</v>
+      </c>
+      <c r="AG34" s="12"/>
+      <c r="AH34" s="12"/>
+      <c r="AI34" s="13"/>
+      <c r="AJ34" s="13"/>
+      <c r="AK34" s="14"/>
+      <c r="AL34" s="12"/>
+      <c r="AM34" s="13"/>
+      <c r="AN34" s="13"/>
+      <c r="AO34" s="20"/>
+      <c r="AP34" s="14"/>
+      <c r="AQ34" s="12"/>
+      <c r="AR34" s="13"/>
+      <c r="AS34" s="13"/>
+      <c r="AT34" s="13"/>
+      <c r="AU34" s="14"/>
+      <c r="AY34" s="3"/>
+      <c r="BD34" s="3"/>
+      <c r="BH34" s="3"/>
+      <c r="BM34" s="3"/>
+      <c r="BQ34" s="3"/>
+      <c r="BU34" s="3"/>
+      <c r="BZ34" s="3"/>
+    </row>
+    <row r="35" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B35" s="17"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="89" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35" s="54" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="12"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="21"/>
+      <c r="O35" s="18"/>
+      <c r="P35" s="18"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="21"/>
+      <c r="S35" s="18"/>
+      <c r="T35" s="18"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="26"/>
+      <c r="W35" s="57"/>
+      <c r="X35" s="58"/>
+      <c r="Y35" s="58"/>
+      <c r="Z35" s="58"/>
+      <c r="AA35" s="59" t="s">
+        <v>43</v>
+      </c>
+      <c r="AB35" s="12"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+      <c r="AF35" s="14"/>
+      <c r="AG35" s="12"/>
+      <c r="AH35" s="12"/>
+      <c r="AI35" s="13"/>
+      <c r="AJ35" s="13"/>
+      <c r="AK35" s="14"/>
+      <c r="AL35" s="12"/>
+      <c r="AM35" s="13"/>
+      <c r="AN35" s="13"/>
+      <c r="AO35" s="20"/>
+      <c r="AP35" s="14"/>
+      <c r="AQ35" s="12"/>
+      <c r="AR35" s="13"/>
+      <c r="AS35" s="13"/>
+      <c r="AT35" s="13"/>
+      <c r="AU35" s="14"/>
+      <c r="AY35" s="3"/>
+      <c r="BD35" s="3"/>
+      <c r="BH35" s="3"/>
+      <c r="BM35" s="3"/>
+      <c r="BQ35" s="3"/>
+      <c r="BU35" s="3"/>
+      <c r="BZ35" s="3"/>
+    </row>
+    <row r="36" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="17"/>
+      <c r="C36" s="40"/>
+      <c r="D36" s="90"/>
+      <c r="E36" s="55" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="12"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="77"/>
+      <c r="J36" s="78"/>
+      <c r="K36" s="78"/>
+      <c r="L36" s="80"/>
+      <c r="M36" s="79"/>
+      <c r="N36" s="77"/>
+      <c r="O36" s="78"/>
+      <c r="P36" s="78"/>
+      <c r="Q36" s="79"/>
+      <c r="R36" s="77"/>
+      <c r="S36" s="78"/>
+      <c r="T36" s="78"/>
+      <c r="U36" s="80"/>
+      <c r="V36" s="79"/>
+      <c r="W36" s="77"/>
+      <c r="X36" s="78"/>
+      <c r="Y36" s="78"/>
+      <c r="Z36" s="80"/>
+      <c r="AA36" s="81">
+        <v>45929</v>
+      </c>
+      <c r="AB36" s="21"/>
+      <c r="AC36" s="18"/>
+      <c r="AD36" s="18"/>
+      <c r="AE36" s="18"/>
+      <c r="AF36" s="26"/>
+      <c r="AG36" s="12"/>
+      <c r="AH36" s="12"/>
+      <c r="AI36" s="13"/>
+      <c r="AJ36" s="13"/>
+      <c r="AK36" s="14"/>
+      <c r="AL36" s="12"/>
+      <c r="AM36" s="13"/>
+      <c r="AN36" s="13"/>
+      <c r="AO36" s="20"/>
+      <c r="AP36" s="14"/>
+      <c r="AQ36" s="12"/>
+      <c r="AR36" s="13"/>
+      <c r="AS36" s="13"/>
+      <c r="AT36" s="13"/>
+      <c r="AU36" s="14"/>
+      <c r="AY36" s="3"/>
+      <c r="BD36" s="3"/>
+      <c r="BH36" s="3"/>
+      <c r="BM36" s="3"/>
+      <c r="BQ36" s="3"/>
+      <c r="BU36" s="3"/>
+      <c r="BZ36" s="3"/>
+    </row>
+    <row r="37" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="17"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="89" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="12"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="14"/>
+      <c r="J37" s="48"/>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37" s="49"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="18"/>
+      <c r="P37" s="18"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="21"/>
+      <c r="S37" s="18"/>
+      <c r="T37" s="18"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="26"/>
+      <c r="W37" s="51"/>
+      <c r="X37" s="48"/>
+      <c r="Y37" s="48"/>
+      <c r="Z37" s="48"/>
+      <c r="AA37" s="49"/>
+      <c r="AB37" s="57"/>
+      <c r="AC37" s="58"/>
+      <c r="AD37" s="58"/>
+      <c r="AE37" s="58"/>
+      <c r="AF37" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG37" s="12"/>
+      <c r="AH37" s="12"/>
+      <c r="AI37" s="13"/>
+      <c r="AJ37" s="13"/>
+      <c r="AK37" s="14"/>
+      <c r="AL37" s="12"/>
+      <c r="AM37" s="13"/>
+      <c r="AN37" s="13"/>
+      <c r="AO37" s="20"/>
+      <c r="AP37" s="14"/>
+      <c r="AQ37" s="12"/>
+      <c r="AR37" s="13"/>
+      <c r="AS37" s="13"/>
+      <c r="AT37" s="13"/>
+      <c r="AU37" s="14"/>
+      <c r="AY37" s="3"/>
+      <c r="BD37" s="3"/>
+      <c r="BH37" s="3"/>
+      <c r="BM37" s="3"/>
+      <c r="BQ37" s="3"/>
+      <c r="BU37" s="3"/>
+      <c r="BZ37" s="3"/>
+    </row>
+    <row r="38" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B38" s="17"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="90"/>
+      <c r="E38" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F38" s="12"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="12"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="14"/>
+      <c r="N38" s="21"/>
+      <c r="O38" s="18"/>
+      <c r="P38" s="18"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="21"/>
+      <c r="S38" s="18"/>
+      <c r="T38" s="18"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="77"/>
+      <c r="X38" s="78"/>
+      <c r="Y38" s="78"/>
+      <c r="Z38" s="80"/>
+      <c r="AA38" s="79"/>
+      <c r="AB38" s="77"/>
+      <c r="AC38" s="78"/>
+      <c r="AD38" s="78"/>
+      <c r="AE38" s="78"/>
+      <c r="AF38" s="79" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG38" s="12"/>
+      <c r="AH38" s="12"/>
+      <c r="AI38" s="13"/>
+      <c r="AJ38" s="13"/>
+      <c r="AK38" s="14"/>
+      <c r="AL38" s="12"/>
+      <c r="AM38" s="13"/>
+      <c r="AN38" s="13"/>
+      <c r="AO38" s="20"/>
+      <c r="AP38" s="14"/>
+      <c r="AQ38" s="12"/>
+      <c r="AR38" s="13"/>
+      <c r="AS38" s="13"/>
+      <c r="AT38" s="13"/>
+      <c r="AU38" s="14"/>
+      <c r="AY38" s="3"/>
+      <c r="BD38" s="3"/>
+      <c r="BH38" s="3"/>
+      <c r="BM38" s="3"/>
+      <c r="BQ38" s="3"/>
+      <c r="BU38" s="3"/>
+      <c r="BZ38" s="3"/>
+    </row>
+    <row r="39" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B39" s="17"/>
+      <c r="C39" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="89" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="12"/>
+      <c r="G39" s="13"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="12"/>
+      <c r="J39" s="13"/>
+      <c r="K39" s="13"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="14"/>
+      <c r="N39" s="18"/>
+      <c r="O39" s="18"/>
+      <c r="P39" s="18"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="21"/>
+      <c r="S39" s="18"/>
+      <c r="T39" s="18"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="21"/>
+      <c r="X39" s="21"/>
+      <c r="Y39" s="18"/>
+      <c r="Z39" s="18"/>
+      <c r="AA39" s="26"/>
+      <c r="AB39" s="21"/>
+      <c r="AC39" s="18"/>
+      <c r="AD39" s="18"/>
+      <c r="AE39" s="18"/>
+      <c r="AF39" s="26"/>
+      <c r="AG39" s="65"/>
+      <c r="AH39" s="66"/>
+      <c r="AI39" s="66"/>
+      <c r="AJ39" s="66"/>
+      <c r="AK39" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="AL39" s="65"/>
+      <c r="AM39" s="66"/>
+      <c r="AN39" s="66"/>
+      <c r="AO39" s="66"/>
+      <c r="AP39" s="68"/>
+      <c r="AQ39" s="57"/>
+      <c r="AR39" s="58"/>
+      <c r="AS39" s="58"/>
+      <c r="AT39" s="58"/>
+      <c r="AU39" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY39" s="3"/>
+      <c r="BD39" s="3"/>
+      <c r="BH39" s="3"/>
+      <c r="BM39" s="3"/>
+      <c r="BQ39" s="3"/>
+      <c r="BU39" s="3"/>
+      <c r="BZ39" s="3"/>
+    </row>
+    <row r="40" spans="2:78" ht="22.15" hidden="1" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="17"/>
+      <c r="C40" s="40"/>
+      <c r="D40" s="97"/>
+      <c r="E40" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F40" s="12"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="12"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="14"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="18"/>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="21"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="25"/>
+      <c r="V40" s="26"/>
+      <c r="W40" s="21"/>
+      <c r="X40" s="21"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="26"/>
+      <c r="AB40" s="21"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="26"/>
+      <c r="AG40" s="73"/>
+      <c r="AH40" s="73"/>
+      <c r="AI40" s="74"/>
+      <c r="AJ40" s="74"/>
+      <c r="AK40" s="75"/>
+      <c r="AL40" s="73"/>
+      <c r="AM40" s="74"/>
+      <c r="AN40" s="74"/>
+      <c r="AO40" s="76"/>
+      <c r="AP40" s="75"/>
+      <c r="AQ40" s="21"/>
+      <c r="AR40" s="21"/>
+      <c r="AS40" s="18"/>
+      <c r="AT40" s="18"/>
+      <c r="AU40" s="26"/>
+      <c r="AY40" s="3"/>
+      <c r="BD40" s="3"/>
+      <c r="BH40" s="3"/>
+      <c r="BM40" s="3"/>
+      <c r="BQ40" s="3"/>
+      <c r="BU40" s="3"/>
+      <c r="BZ40" s="3"/>
+    </row>
+    <row r="41" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="17"/>
+      <c r="C41" s="40"/>
+      <c r="D41" s="90"/>
+      <c r="E41" s="61" t="s">
+        <v>34</v>
+      </c>
+      <c r="F41" s="12"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="14"/>
+      <c r="N41" s="18"/>
+      <c r="O41" s="18"/>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="21"/>
+      <c r="S41" s="18"/>
+      <c r="T41" s="18"/>
+      <c r="U41" s="25"/>
+      <c r="V41" s="26"/>
+      <c r="W41" s="77"/>
+      <c r="X41" s="78"/>
+      <c r="Y41" s="78"/>
+      <c r="Z41" s="80"/>
+      <c r="AA41" s="79"/>
+      <c r="AB41" s="77"/>
+      <c r="AC41" s="78"/>
+      <c r="AD41" s="78"/>
+      <c r="AE41" s="80"/>
+      <c r="AF41" s="79"/>
+      <c r="AG41" s="77"/>
+      <c r="AH41" s="78"/>
+      <c r="AI41" s="78"/>
+      <c r="AJ41" s="80"/>
+      <c r="AK41" s="79"/>
+      <c r="AL41" s="77"/>
+      <c r="AM41" s="78"/>
+      <c r="AN41" s="78"/>
+      <c r="AO41" s="80"/>
+      <c r="AP41" s="79"/>
+      <c r="AQ41" s="77"/>
+      <c r="AR41" s="78"/>
+      <c r="AS41" s="78"/>
+      <c r="AT41" s="80"/>
+      <c r="AU41" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY41" s="3"/>
+      <c r="BD41" s="3"/>
+      <c r="BH41" s="3"/>
+      <c r="BM41" s="3"/>
+      <c r="BQ41" s="3"/>
+      <c r="BU41" s="3"/>
+      <c r="BZ41" s="3"/>
+    </row>
+    <row r="42" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B42" s="17"/>
+      <c r="C42" s="40"/>
+      <c r="D42" s="89" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="12"/>
+      <c r="G42" s="13"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="12"/>
+      <c r="J42" s="13"/>
+      <c r="K42" s="13"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="14"/>
+      <c r="N42" s="18"/>
+      <c r="O42" s="18"/>
+      <c r="P42" s="18"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="21"/>
+      <c r="S42" s="18"/>
+      <c r="T42" s="18"/>
+      <c r="U42" s="25"/>
+      <c r="V42" s="26"/>
+      <c r="W42" s="21"/>
+      <c r="X42" s="21"/>
+      <c r="Y42" s="18"/>
+      <c r="Z42" s="18"/>
+      <c r="AA42" s="26"/>
+      <c r="AB42" s="21"/>
+      <c r="AC42" s="18"/>
+      <c r="AD42" s="18"/>
+      <c r="AE42" s="18"/>
+      <c r="AF42" s="26"/>
+      <c r="AG42" s="65"/>
+      <c r="AH42" s="66"/>
+      <c r="AI42" s="66"/>
+      <c r="AJ42" s="66"/>
+      <c r="AK42" s="68" t="s">
+        <v>55</v>
+      </c>
+      <c r="AL42" s="73"/>
+      <c r="AM42" s="74"/>
+      <c r="AN42" s="74"/>
+      <c r="AO42" s="76"/>
+      <c r="AP42" s="75"/>
+      <c r="AQ42" s="57"/>
+      <c r="AR42" s="58"/>
+      <c r="AS42" s="58"/>
+      <c r="AT42" s="58"/>
+      <c r="AU42" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="AY42" s="3"/>
+      <c r="BD42" s="3"/>
+      <c r="BH42" s="3"/>
+      <c r="BM42" s="3"/>
+      <c r="BQ42" s="3"/>
+      <c r="BU42" s="3"/>
+      <c r="BZ42" s="3"/>
+    </row>
+    <row r="43" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="17"/>
+      <c r="C43" s="40"/>
+      <c r="D43" s="90"/>
+      <c r="E43" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F43" s="12"/>
+      <c r="G43" s="13"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="13"/>
+      <c r="K43" s="13"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="18"/>
+      <c r="O43" s="18"/>
+      <c r="P43" s="18"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="21"/>
+      <c r="S43" s="18"/>
+      <c r="T43" s="18"/>
+      <c r="U43" s="25"/>
+      <c r="V43" s="26"/>
+      <c r="W43" s="77"/>
+      <c r="X43" s="78"/>
+      <c r="Y43" s="78"/>
+      <c r="Z43" s="80"/>
+      <c r="AA43" s="79"/>
+      <c r="AB43" s="77"/>
+      <c r="AC43" s="78"/>
+      <c r="AD43" s="78"/>
+      <c r="AE43" s="80"/>
+      <c r="AF43" s="79"/>
+      <c r="AG43" s="77"/>
+      <c r="AH43" s="78"/>
+      <c r="AI43" s="78"/>
+      <c r="AJ43" s="80"/>
+      <c r="AK43" s="79"/>
+      <c r="AL43" s="77"/>
+      <c r="AM43" s="78"/>
+      <c r="AN43" s="78"/>
+      <c r="AO43" s="80"/>
+      <c r="AP43" s="79"/>
+      <c r="AQ43" s="77"/>
+      <c r="AR43" s="78"/>
+      <c r="AS43" s="78"/>
+      <c r="AT43" s="80"/>
+      <c r="AU43" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY43" s="3"/>
+      <c r="BD43" s="3"/>
+      <c r="BH43" s="3"/>
+      <c r="BM43" s="3"/>
+      <c r="BQ43" s="3"/>
+      <c r="BU43" s="3"/>
+      <c r="BZ43" s="3"/>
+    </row>
+    <row r="44" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B44" s="17"/>
+      <c r="C44" s="40"/>
+      <c r="D44" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="E44" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="12"/>
+      <c r="G44" s="13"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="13"/>
+      <c r="K44" s="13"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="14"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="18"/>
+      <c r="P44" s="18"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="21"/>
+      <c r="S44" s="18"/>
+      <c r="T44" s="18"/>
+      <c r="U44" s="25"/>
+      <c r="V44" s="26"/>
+      <c r="W44" s="21"/>
+      <c r="X44" s="21"/>
+      <c r="Y44" s="18"/>
+      <c r="Z44" s="18"/>
+      <c r="AA44" s="26"/>
+      <c r="AB44" s="21"/>
+      <c r="AC44" s="18"/>
+      <c r="AD44" s="18"/>
+      <c r="AE44" s="18"/>
+      <c r="AF44" s="26"/>
+      <c r="AG44" s="51"/>
+      <c r="AH44" s="48"/>
+      <c r="AI44" s="48"/>
+      <c r="AJ44" s="48"/>
+      <c r="AK44" s="49"/>
+      <c r="AL44" s="57"/>
+      <c r="AM44" s="58"/>
+      <c r="AN44" s="58"/>
+      <c r="AO44" s="58"/>
+      <c r="AP44" s="59" t="s">
+        <v>53</v>
+      </c>
+      <c r="AQ44" s="21"/>
+      <c r="AR44" s="18"/>
+      <c r="AS44" s="18"/>
+      <c r="AT44" s="18"/>
+      <c r="AU44" s="26"/>
+      <c r="AY44" s="3"/>
+      <c r="BD44" s="3"/>
+      <c r="BH44" s="3"/>
+      <c r="BM44" s="3"/>
+      <c r="BQ44" s="3"/>
+      <c r="BU44" s="3"/>
+      <c r="BZ44" s="3"/>
+    </row>
+    <row r="45" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B45" s="17"/>
+      <c r="C45" s="40"/>
+      <c r="D45" s="90"/>
+      <c r="E45" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F45" s="12"/>
+      <c r="G45" s="13"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="13"/>
+      <c r="K45" s="13"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="14"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="18"/>
+      <c r="P45" s="18"/>
+      <c r="Q45" s="26"/>
+      <c r="R45" s="21"/>
+      <c r="S45" s="18"/>
+      <c r="T45" s="18"/>
+      <c r="U45" s="25"/>
+      <c r="V45" s="26"/>
+      <c r="W45" s="21"/>
+      <c r="X45" s="21"/>
+      <c r="Y45" s="18"/>
+      <c r="Z45" s="18"/>
+      <c r="AA45" s="26"/>
+      <c r="AB45" s="77"/>
+      <c r="AC45" s="78"/>
+      <c r="AD45" s="78"/>
+      <c r="AE45" s="80"/>
+      <c r="AF45" s="79"/>
+      <c r="AG45" s="77"/>
+      <c r="AH45" s="78"/>
+      <c r="AI45" s="78"/>
+      <c r="AJ45" s="80"/>
+      <c r="AK45" s="79"/>
+      <c r="AL45" s="77"/>
+      <c r="AM45" s="78"/>
+      <c r="AN45" s="78"/>
+      <c r="AO45" s="80"/>
+      <c r="AP45" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="AQ45" s="21"/>
+      <c r="AR45" s="18"/>
+      <c r="AS45" s="18"/>
+      <c r="AT45" s="18"/>
+      <c r="AU45" s="26"/>
+      <c r="AY45" s="3"/>
+      <c r="BD45" s="3"/>
+      <c r="BH45" s="3"/>
+      <c r="BM45" s="3"/>
+      <c r="BQ45" s="3"/>
+      <c r="BU45" s="3"/>
+      <c r="BZ45" s="3"/>
+    </row>
+    <row r="46" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B46" s="17"/>
+      <c r="C46" s="40"/>
+      <c r="D46" s="89" t="s">
+        <v>47</v>
+      </c>
+      <c r="E46" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="12"/>
+      <c r="G46" s="18"/>
+      <c r="H46" s="26"/>
+      <c r="I46" s="21"/>
+      <c r="J46" s="18"/>
+      <c r="K46" s="18"/>
+      <c r="L46" s="25"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="18"/>
+      <c r="P46" s="18"/>
+      <c r="Q46" s="26"/>
+      <c r="R46" s="21"/>
+      <c r="S46" s="18"/>
+      <c r="T46" s="18"/>
+      <c r="U46" s="25"/>
+      <c r="V46" s="26"/>
+      <c r="W46" s="21"/>
+      <c r="X46" s="21"/>
+      <c r="Y46" s="18"/>
+      <c r="Z46" s="18"/>
+      <c r="AA46" s="26"/>
+      <c r="AB46" s="21"/>
+      <c r="AC46" s="18"/>
+      <c r="AD46" s="18"/>
+      <c r="AE46" s="18"/>
+      <c r="AF46" s="26"/>
+      <c r="AG46" s="57"/>
+      <c r="AH46" s="58"/>
+      <c r="AI46" s="58"/>
+      <c r="AJ46" s="58"/>
+      <c r="AK46" s="59" t="s">
+        <v>52</v>
+      </c>
+      <c r="AL46" s="21"/>
+      <c r="AM46" s="18"/>
+      <c r="AN46" s="18"/>
+      <c r="AO46" s="25"/>
+      <c r="AP46" s="26"/>
+      <c r="AQ46" s="21"/>
+      <c r="AR46" s="18"/>
+      <c r="AS46" s="18"/>
+      <c r="AT46" s="18"/>
+      <c r="AU46" s="26"/>
+      <c r="AY46" s="3"/>
+      <c r="BD46" s="3"/>
+      <c r="BH46" s="3"/>
+      <c r="BM46" s="3"/>
+      <c r="BQ46" s="3"/>
+      <c r="BU46" s="3"/>
+      <c r="BZ46" s="3"/>
+    </row>
+    <row r="47" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B47" s="17"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="90"/>
+      <c r="E47" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F47" s="12"/>
+      <c r="G47" s="18"/>
+      <c r="H47" s="26"/>
+      <c r="I47" s="21"/>
+      <c r="J47" s="18"/>
+      <c r="K47" s="18"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="26"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="18"/>
+      <c r="P47" s="18"/>
+      <c r="Q47" s="26"/>
+      <c r="R47" s="21"/>
+      <c r="S47" s="18"/>
+      <c r="T47" s="18"/>
+      <c r="U47" s="25"/>
+      <c r="V47" s="26"/>
+      <c r="W47" s="21"/>
+      <c r="X47" s="21"/>
+      <c r="Y47" s="18"/>
+      <c r="Z47" s="18"/>
+      <c r="AA47" s="26"/>
+      <c r="AB47" s="77"/>
+      <c r="AC47" s="78"/>
+      <c r="AD47" s="78"/>
+      <c r="AE47" s="80"/>
+      <c r="AF47" s="79"/>
+      <c r="AG47" s="77"/>
+      <c r="AH47" s="78"/>
+      <c r="AI47" s="78"/>
+      <c r="AJ47" s="80"/>
+      <c r="AK47" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL47" s="21"/>
+      <c r="AM47" s="18"/>
+      <c r="AN47" s="18"/>
+      <c r="AO47" s="25"/>
+      <c r="AP47" s="26"/>
+      <c r="AQ47" s="21"/>
+      <c r="AR47" s="18"/>
+      <c r="AS47" s="18"/>
+      <c r="AT47" s="18"/>
+      <c r="AU47" s="26"/>
+      <c r="AY47" s="3"/>
+      <c r="BD47" s="3"/>
+      <c r="BH47" s="3"/>
+      <c r="BM47" s="3"/>
+      <c r="BQ47" s="3"/>
+      <c r="BU47" s="3"/>
+      <c r="BZ47" s="3"/>
+    </row>
+    <row r="48" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B48" s="17"/>
+      <c r="C48" s="40"/>
+      <c r="D48" s="89" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="21"/>
+      <c r="G48" s="18"/>
+      <c r="H48" s="26"/>
+      <c r="I48" s="21"/>
+      <c r="J48" s="18"/>
+      <c r="K48" s="18"/>
+      <c r="L48" s="25"/>
+      <c r="M48" s="26"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="18"/>
+      <c r="P48" s="18"/>
+      <c r="Q48" s="26"/>
+      <c r="R48" s="21"/>
+      <c r="S48" s="18"/>
+      <c r="T48" s="18"/>
+      <c r="U48" s="25"/>
+      <c r="V48" s="26"/>
+      <c r="W48" s="21"/>
+      <c r="X48" s="21"/>
+      <c r="Y48" s="18"/>
+      <c r="Z48" s="18"/>
+      <c r="AA48" s="26"/>
+      <c r="AB48" s="21"/>
+      <c r="AC48" s="18"/>
+      <c r="AD48" s="18"/>
+      <c r="AE48" s="18"/>
+      <c r="AF48" s="26"/>
+      <c r="AG48" s="57"/>
+      <c r="AH48" s="58"/>
+      <c r="AI48" s="58"/>
+      <c r="AJ48" s="58"/>
+      <c r="AK48" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL48" s="21"/>
+      <c r="AM48" s="18"/>
+      <c r="AN48" s="18"/>
+      <c r="AO48" s="25"/>
+      <c r="AP48" s="26"/>
+      <c r="AQ48" s="21"/>
+      <c r="AR48" s="18"/>
+      <c r="AS48" s="18"/>
+      <c r="AT48" s="18"/>
+      <c r="AU48" s="26"/>
+      <c r="AY48" s="3"/>
+      <c r="BD48" s="3"/>
+      <c r="BH48" s="3"/>
+      <c r="BM48" s="3"/>
+      <c r="BQ48" s="3"/>
+      <c r="BU48" s="3"/>
+      <c r="BZ48" s="3"/>
+    </row>
+    <row r="49" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B49" s="17"/>
+      <c r="C49" s="40"/>
+      <c r="D49" s="90"/>
+      <c r="E49" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F49" s="21"/>
+      <c r="G49" s="18"/>
+      <c r="H49" s="26"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="25"/>
+      <c r="M49" s="26"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="18"/>
+      <c r="P49" s="18"/>
+      <c r="Q49" s="26"/>
+      <c r="R49" s="21"/>
+      <c r="S49" s="18"/>
+      <c r="T49" s="18"/>
+      <c r="U49" s="25"/>
+      <c r="V49" s="26"/>
+      <c r="W49" s="77"/>
+      <c r="X49" s="78"/>
+      <c r="Y49" s="78"/>
+      <c r="Z49" s="80"/>
+      <c r="AA49" s="79"/>
+      <c r="AB49" s="77"/>
+      <c r="AC49" s="78"/>
+      <c r="AD49" s="78"/>
+      <c r="AE49" s="80"/>
+      <c r="AF49" s="79"/>
+      <c r="AG49" s="77"/>
+      <c r="AH49" s="78"/>
+      <c r="AI49" s="78"/>
+      <c r="AJ49" s="80"/>
+      <c r="AK49" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="AL49" s="21"/>
+      <c r="AM49" s="18"/>
+      <c r="AN49" s="18"/>
+      <c r="AO49" s="25"/>
+      <c r="AP49" s="26"/>
+      <c r="AQ49" s="21"/>
+      <c r="AR49" s="18"/>
+      <c r="AS49" s="18"/>
+      <c r="AT49" s="18"/>
+      <c r="AU49" s="26"/>
+      <c r="AY49" s="3"/>
+      <c r="BD49" s="3"/>
+      <c r="BH49" s="3"/>
+      <c r="BM49" s="3"/>
+      <c r="BQ49" s="3"/>
+      <c r="BU49" s="3"/>
+      <c r="BZ49" s="3"/>
+    </row>
+    <row r="50" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="17"/>
+      <c r="C50" s="40"/>
+      <c r="D50" s="89" t="s">
+        <v>49</v>
+      </c>
+      <c r="E50" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="21"/>
+      <c r="G50" s="18"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="18"/>
+      <c r="K50" s="18"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="26"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="18"/>
+      <c r="P50" s="18"/>
+      <c r="Q50" s="26"/>
+      <c r="R50" s="21"/>
+      <c r="S50" s="18"/>
+      <c r="T50" s="18"/>
+      <c r="U50" s="25"/>
+      <c r="V50" s="26"/>
+      <c r="W50" s="21"/>
+      <c r="X50" s="21"/>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="18"/>
+      <c r="AA50" s="26"/>
+      <c r="AB50" s="21"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="18"/>
+      <c r="AE50" s="18"/>
+      <c r="AF50" s="26"/>
+      <c r="AG50" s="51"/>
+      <c r="AH50" s="48"/>
+      <c r="AI50" s="48"/>
+      <c r="AJ50" s="48"/>
+      <c r="AK50" s="49"/>
+      <c r="AL50" s="57"/>
+      <c r="AM50" s="58"/>
+      <c r="AN50" s="58"/>
+      <c r="AO50" s="58"/>
+      <c r="AP50" s="59"/>
+      <c r="AQ50" s="57"/>
+      <c r="AR50" s="58"/>
+      <c r="AS50" s="58"/>
+      <c r="AT50" s="58"/>
+      <c r="AU50" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="AY50" s="3"/>
+      <c r="BD50" s="3"/>
+      <c r="BH50" s="3"/>
+      <c r="BM50" s="3"/>
+      <c r="BQ50" s="3"/>
+      <c r="BU50" s="3"/>
+      <c r="BZ50" s="3"/>
+    </row>
+    <row r="51" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="17"/>
+      <c r="C51" s="40"/>
+      <c r="D51" s="90"/>
+      <c r="E51" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="21"/>
+      <c r="G51" s="18"/>
+      <c r="H51" s="26"/>
+      <c r="I51" s="21"/>
+      <c r="J51" s="18"/>
+      <c r="K51" s="18"/>
+      <c r="L51" s="25"/>
+      <c r="M51" s="26"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="18"/>
+      <c r="P51" s="18"/>
+      <c r="Q51" s="26"/>
+      <c r="R51" s="21"/>
+      <c r="S51" s="18"/>
+      <c r="T51" s="18"/>
+      <c r="U51" s="25"/>
+      <c r="V51" s="26"/>
+      <c r="W51" s="21"/>
+      <c r="X51" s="21"/>
+      <c r="Y51" s="18"/>
+      <c r="Z51" s="18"/>
+      <c r="AA51" s="26"/>
+      <c r="AB51" s="77"/>
+      <c r="AC51" s="78"/>
+      <c r="AD51" s="78"/>
+      <c r="AE51" s="80"/>
+      <c r="AF51" s="79"/>
+      <c r="AG51" s="77"/>
+      <c r="AH51" s="78"/>
+      <c r="AI51" s="78"/>
+      <c r="AJ51" s="80"/>
+      <c r="AK51" s="79"/>
+      <c r="AL51" s="77"/>
+      <c r="AM51" s="78"/>
+      <c r="AN51" s="78"/>
+      <c r="AO51" s="80"/>
+      <c r="AP51" s="79"/>
+      <c r="AQ51" s="77"/>
+      <c r="AR51" s="78"/>
+      <c r="AS51" s="78"/>
+      <c r="AT51" s="80"/>
+      <c r="AU51" s="79" t="s">
+        <v>61</v>
+      </c>
+      <c r="AY51" s="3"/>
+      <c r="BD51" s="3"/>
+      <c r="BH51" s="3"/>
+      <c r="BM51" s="3"/>
+      <c r="BQ51" s="3"/>
+      <c r="BU51" s="3"/>
+      <c r="BZ51" s="3"/>
+    </row>
+    <row r="52" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="17"/>
+      <c r="C52" s="40"/>
+      <c r="D52" s="89" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="21"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="26"/>
+      <c r="I52" s="21"/>
+      <c r="J52" s="18"/>
+      <c r="K52" s="18"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="18"/>
+      <c r="P52" s="18"/>
+      <c r="Q52" s="26"/>
+      <c r="R52" s="21"/>
+      <c r="S52" s="18"/>
+      <c r="T52" s="18"/>
+      <c r="U52" s="25"/>
+      <c r="V52" s="26"/>
+      <c r="W52" s="21"/>
+      <c r="X52" s="21"/>
+      <c r="Y52" s="18"/>
+      <c r="Z52" s="18"/>
+      <c r="AA52" s="26"/>
+      <c r="AB52" s="21"/>
+      <c r="AC52" s="18"/>
+      <c r="AD52" s="18"/>
+      <c r="AE52" s="18"/>
+      <c r="AF52" s="26"/>
+      <c r="AG52" s="51"/>
+      <c r="AH52" s="48"/>
+      <c r="AI52" s="48"/>
+      <c r="AJ52" s="48"/>
+      <c r="AK52" s="49"/>
+      <c r="AL52" s="57"/>
+      <c r="AM52" s="58"/>
+      <c r="AN52" s="58"/>
+      <c r="AO52" s="58"/>
+      <c r="AP52" s="59"/>
+      <c r="AQ52" s="57"/>
+      <c r="AR52" s="58"/>
+      <c r="AS52" s="58"/>
+      <c r="AT52" s="58"/>
+      <c r="AU52" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="AY52" s="3"/>
+      <c r="BD52" s="3"/>
+      <c r="BH52" s="3"/>
+      <c r="BM52" s="3"/>
+      <c r="BQ52" s="3"/>
+      <c r="BU52" s="3"/>
+      <c r="BZ52" s="3"/>
+    </row>
+    <row r="53" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="17"/>
+      <c r="C53" s="40"/>
+      <c r="D53" s="90"/>
+      <c r="E53" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F53" s="21"/>
+      <c r="G53" s="18"/>
+      <c r="H53" s="26"/>
+      <c r="I53" s="21"/>
+      <c r="J53" s="18"/>
+      <c r="K53" s="18"/>
+      <c r="L53" s="25"/>
+      <c r="M53" s="26"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="18"/>
+      <c r="P53" s="18"/>
+      <c r="Q53" s="26"/>
+      <c r="R53" s="21"/>
+      <c r="S53" s="18"/>
+      <c r="T53" s="18"/>
+      <c r="U53" s="25"/>
+      <c r="V53" s="26"/>
+      <c r="W53" s="21"/>
+      <c r="X53" s="21"/>
+      <c r="Y53" s="18"/>
+      <c r="Z53" s="18"/>
+      <c r="AA53" s="26"/>
+      <c r="AB53" s="87"/>
+      <c r="AC53" s="88"/>
+      <c r="AD53" s="88"/>
+      <c r="AE53" s="88"/>
+      <c r="AF53" s="86"/>
+      <c r="AG53" s="87"/>
+      <c r="AH53" s="88"/>
+      <c r="AI53" s="88"/>
+      <c r="AJ53" s="88"/>
+      <c r="AK53" s="86"/>
+      <c r="AL53" s="87"/>
+      <c r="AM53" s="88"/>
+      <c r="AN53" s="88"/>
+      <c r="AO53" s="88"/>
+      <c r="AP53" s="86"/>
+      <c r="AQ53" s="21"/>
+      <c r="AR53" s="18"/>
+      <c r="AS53" s="18"/>
+      <c r="AT53" s="18"/>
+      <c r="AU53" s="26"/>
+      <c r="AY53" s="3"/>
+      <c r="BD53" s="3"/>
+      <c r="BH53" s="3"/>
+      <c r="BM53" s="3"/>
+      <c r="BQ53" s="3"/>
+      <c r="BU53" s="3"/>
+      <c r="BZ53" s="3"/>
+    </row>
+    <row r="54" spans="2:78" ht="22.15" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="17"/>
+      <c r="C54" s="40"/>
+      <c r="D54" s="89" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="21"/>
+      <c r="G54" s="18"/>
+      <c r="H54" s="26"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="18"/>
+      <c r="K54" s="18"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="26"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="18"/>
+      <c r="P54" s="18"/>
+      <c r="Q54" s="26"/>
+      <c r="R54" s="21"/>
+      <c r="S54" s="18"/>
+      <c r="T54" s="18"/>
+      <c r="U54" s="25"/>
+      <c r="V54" s="26"/>
+      <c r="W54" s="21"/>
+      <c r="X54" s="21"/>
+      <c r="Y54" s="18"/>
+      <c r="Z54" s="18"/>
+      <c r="AA54" s="26"/>
+      <c r="AB54" s="21"/>
+      <c r="AC54" s="18"/>
+      <c r="AD54" s="18"/>
+      <c r="AE54" s="18"/>
+      <c r="AF54" s="26"/>
+      <c r="AG54" s="51"/>
+      <c r="AH54" s="48"/>
+      <c r="AI54" s="48"/>
+      <c r="AJ54" s="48"/>
+      <c r="AK54" s="49"/>
+      <c r="AL54" s="51"/>
+      <c r="AM54" s="48"/>
+      <c r="AN54" s="48"/>
+      <c r="AO54" s="48"/>
+      <c r="AP54" s="49"/>
+      <c r="AQ54" s="57"/>
+      <c r="AR54" s="58"/>
+      <c r="AS54" s="58"/>
+      <c r="AT54" s="58"/>
+      <c r="AU54" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY54" s="3"/>
+      <c r="BD54" s="3"/>
+      <c r="BH54" s="3"/>
+      <c r="BM54" s="3"/>
+      <c r="BQ54" s="3"/>
+      <c r="BU54" s="3"/>
+      <c r="BZ54" s="3"/>
+    </row>
+    <row r="55" spans="2:78" ht="21" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B55" s="17"/>
+      <c r="C55" s="40"/>
+      <c r="D55" s="90"/>
+      <c r="E55" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F55" s="21"/>
+      <c r="G55" s="18"/>
+      <c r="H55" s="26"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="18"/>
+      <c r="K55" s="18"/>
+      <c r="L55" s="25"/>
+      <c r="M55" s="26"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="18"/>
+      <c r="P55" s="18"/>
+      <c r="Q55" s="26"/>
+      <c r="R55" s="21"/>
+      <c r="S55" s="18"/>
+      <c r="T55" s="18"/>
+      <c r="U55" s="25"/>
+      <c r="V55" s="26"/>
+      <c r="W55" s="21"/>
+      <c r="X55" s="21"/>
+      <c r="Y55" s="18"/>
+      <c r="Z55" s="18"/>
+      <c r="AA55" s="26"/>
+      <c r="AB55" s="87"/>
+      <c r="AC55" s="88"/>
+      <c r="AD55" s="88"/>
+      <c r="AE55" s="88"/>
+      <c r="AF55" s="86"/>
+      <c r="AG55" s="87"/>
+      <c r="AH55" s="88"/>
+      <c r="AI55" s="88"/>
+      <c r="AJ55" s="88"/>
+      <c r="AK55" s="86"/>
+      <c r="AL55" s="87"/>
+      <c r="AM55" s="88"/>
+      <c r="AN55" s="88"/>
+      <c r="AO55" s="88"/>
+      <c r="AP55" s="86"/>
+      <c r="AQ55" s="21"/>
+      <c r="AR55" s="18"/>
+      <c r="AS55" s="18"/>
+      <c r="AT55" s="18"/>
+      <c r="AU55" s="26"/>
+      <c r="AY55" s="3"/>
+      <c r="BD55" s="3"/>
+      <c r="BH55" s="3"/>
+      <c r="BM55" s="3"/>
+      <c r="BQ55" s="3"/>
+      <c r="BU55" s="3"/>
+      <c r="BZ55" s="3"/>
+    </row>
+    <row r="56" spans="2:78" ht="20.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B56" s="17"/>
+      <c r="C56" s="40"/>
+      <c r="D56" s="89" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="60" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="21"/>
+      <c r="G56" s="18"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="21"/>
+      <c r="J56" s="18"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="26"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="18"/>
+      <c r="P56" s="18"/>
+      <c r="Q56" s="26"/>
+      <c r="R56" s="21"/>
+      <c r="S56" s="18"/>
+      <c r="T56" s="18"/>
+      <c r="U56" s="25"/>
+      <c r="V56" s="26"/>
+      <c r="W56" s="21"/>
+      <c r="X56" s="21"/>
+      <c r="Y56" s="18"/>
+      <c r="Z56" s="18"/>
+      <c r="AA56" s="26"/>
+      <c r="AB56" s="21"/>
+      <c r="AC56" s="18"/>
+      <c r="AD56" s="18"/>
+      <c r="AE56" s="18"/>
+      <c r="AF56" s="26"/>
+      <c r="AG56" s="51"/>
+      <c r="AH56" s="48"/>
+      <c r="AI56" s="48"/>
+      <c r="AJ56" s="48"/>
+      <c r="AK56" s="49"/>
+      <c r="AL56" s="51"/>
+      <c r="AM56" s="48"/>
+      <c r="AN56" s="48"/>
+      <c r="AO56" s="48"/>
+      <c r="AP56" s="49"/>
+      <c r="AQ56" s="57"/>
+      <c r="AR56" s="58"/>
+      <c r="AS56" s="58"/>
+      <c r="AT56" s="58"/>
+      <c r="AU56" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="AY56" s="3"/>
+      <c r="BD56" s="3"/>
+      <c r="BH56" s="3"/>
+      <c r="BM56" s="3"/>
+      <c r="BQ56" s="3"/>
+      <c r="BU56" s="3"/>
+      <c r="BZ56" s="3"/>
+    </row>
+    <row r="57" spans="2:78" ht="18.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B57" s="17"/>
+      <c r="C57" s="40"/>
+      <c r="D57" s="90"/>
+      <c r="E57" s="62" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="21"/>
+      <c r="G57" s="18"/>
+      <c r="H57" s="26"/>
+      <c r="I57" s="21"/>
+      <c r="J57" s="18"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="18"/>
+      <c r="P57" s="18"/>
+      <c r="Q57" s="26"/>
+      <c r="R57" s="21"/>
+      <c r="S57" s="18"/>
+      <c r="T57" s="18"/>
+      <c r="U57" s="25"/>
+      <c r="V57" s="26"/>
+      <c r="W57" s="21"/>
+      <c r="X57" s="21"/>
+      <c r="Y57" s="18"/>
+      <c r="Z57" s="18"/>
+      <c r="AA57" s="26"/>
+      <c r="AB57" s="12"/>
+      <c r="AC57" s="13"/>
+      <c r="AD57" s="13"/>
+      <c r="AE57" s="13"/>
+      <c r="AF57" s="14"/>
+      <c r="AG57" s="12"/>
+      <c r="AH57" s="13"/>
+      <c r="AI57" s="13"/>
+      <c r="AJ57" s="13"/>
+      <c r="AK57" s="14"/>
+      <c r="AL57" s="21"/>
+      <c r="AM57" s="18"/>
+      <c r="AN57" s="18"/>
+      <c r="AO57" s="25"/>
+      <c r="AP57" s="26"/>
+      <c r="AQ57" s="21"/>
+      <c r="AR57" s="18"/>
+      <c r="AS57" s="18"/>
+      <c r="AT57" s="18"/>
+      <c r="AU57" s="26"/>
+      <c r="AY57" s="3"/>
+      <c r="BD57" s="3"/>
+      <c r="BH57" s="3"/>
+      <c r="BM57" s="3"/>
+      <c r="BQ57" s="3"/>
+      <c r="BU57" s="3"/>
+      <c r="BZ57" s="3"/>
+    </row>
+    <row r="58" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B58" s="17"/>
+      <c r="C58" s="40"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="56"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="34"/>
+      <c r="H58" s="35"/>
+      <c r="I58" s="36"/>
+      <c r="J58" s="34"/>
+      <c r="K58" s="34"/>
+      <c r="L58" s="37"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="36"/>
+      <c r="O58" s="34"/>
+      <c r="P58" s="34"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="36"/>
+      <c r="S58" s="34"/>
+      <c r="T58" s="34"/>
+      <c r="U58" s="37"/>
+      <c r="V58" s="35"/>
+      <c r="W58" s="36"/>
+      <c r="X58" s="36"/>
+      <c r="Y58" s="34"/>
+      <c r="Z58" s="34"/>
+      <c r="AA58" s="35"/>
+      <c r="AB58" s="36"/>
+      <c r="AC58" s="34"/>
+      <c r="AD58" s="34"/>
+      <c r="AE58" s="34"/>
+      <c r="AF58" s="35"/>
+      <c r="AG58" s="36"/>
+      <c r="AH58" s="36"/>
+      <c r="AI58" s="34"/>
+      <c r="AJ58" s="34"/>
+      <c r="AK58" s="35"/>
+      <c r="AL58" s="36"/>
+      <c r="AM58" s="34"/>
+      <c r="AN58" s="34"/>
+      <c r="AO58" s="37"/>
+      <c r="AP58" s="35"/>
+      <c r="AQ58" s="36"/>
+      <c r="AR58" s="34"/>
+      <c r="AS58" s="34"/>
+      <c r="AT58" s="34"/>
+      <c r="AU58" s="35"/>
+      <c r="AY58" s="3"/>
+      <c r="BD58" s="3"/>
+      <c r="BH58" s="3"/>
+      <c r="BM58" s="3"/>
+      <c r="BQ58" s="3"/>
+      <c r="BU58" s="3"/>
+      <c r="BZ58" s="3"/>
+    </row>
+    <row r="59" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B59" s="17"/>
+      <c r="C59" s="40"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="56"/>
+      <c r="F59" s="21"/>
+      <c r="G59" s="34"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="36"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="37"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="36"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="34"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="36"/>
+      <c r="S59" s="34"/>
+      <c r="T59" s="34"/>
+      <c r="U59" s="37"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="36"/>
+      <c r="X59" s="36"/>
+      <c r="Y59" s="34"/>
+      <c r="Z59" s="34"/>
+      <c r="AA59" s="35"/>
+      <c r="AB59" s="36"/>
+      <c r="AC59" s="34"/>
+      <c r="AD59" s="34"/>
+      <c r="AE59" s="34"/>
+      <c r="AF59" s="35"/>
+      <c r="AG59" s="36"/>
+      <c r="AH59" s="36"/>
+      <c r="AI59" s="34"/>
+      <c r="AJ59" s="34"/>
+      <c r="AK59" s="35"/>
+      <c r="AL59" s="36"/>
+      <c r="AM59" s="34"/>
+      <c r="AN59" s="34"/>
+      <c r="AO59" s="37"/>
+      <c r="AP59" s="35"/>
+      <c r="AQ59" s="36"/>
+      <c r="AR59" s="34"/>
+      <c r="AS59" s="34"/>
+      <c r="AT59" s="34"/>
+      <c r="AU59" s="35"/>
+      <c r="AY59" s="3"/>
+      <c r="BD59" s="3"/>
+      <c r="BH59" s="3"/>
+      <c r="BM59" s="3"/>
+      <c r="BQ59" s="3"/>
+      <c r="BU59" s="3"/>
+      <c r="BZ59" s="3"/>
+    </row>
+    <row r="60" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B60" s="17"/>
+      <c r="C60" s="40"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="56"/>
+      <c r="F60" s="21"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="35"/>
+      <c r="I60" s="36"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="37"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="36"/>
+      <c r="O60" s="34"/>
+      <c r="P60" s="34"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="36"/>
+      <c r="S60" s="34"/>
+      <c r="T60" s="34"/>
+      <c r="U60" s="37"/>
+      <c r="V60" s="35"/>
+      <c r="W60" s="36"/>
+      <c r="X60" s="36"/>
+      <c r="Y60" s="34"/>
+      <c r="Z60" s="34"/>
+      <c r="AA60" s="35"/>
+      <c r="AB60" s="36"/>
+      <c r="AC60" s="34"/>
+      <c r="AD60" s="34"/>
+      <c r="AE60" s="34"/>
+      <c r="AF60" s="35"/>
+      <c r="AG60" s="36"/>
+      <c r="AH60" s="36"/>
+      <c r="AI60" s="34"/>
+      <c r="AJ60" s="34"/>
+      <c r="AK60" s="35"/>
+      <c r="AL60" s="36"/>
+      <c r="AM60" s="34"/>
+      <c r="AN60" s="34"/>
+      <c r="AO60" s="37"/>
+      <c r="AP60" s="35"/>
+      <c r="AQ60" s="36"/>
+      <c r="AR60" s="34"/>
+      <c r="AS60" s="34"/>
+      <c r="AT60" s="34"/>
+      <c r="AU60" s="35"/>
+      <c r="AY60" s="3"/>
+      <c r="BD60" s="3"/>
+      <c r="BH60" s="3"/>
+      <c r="BM60" s="3"/>
+      <c r="BQ60" s="3"/>
+      <c r="BU60" s="3"/>
+      <c r="BZ60" s="3"/>
+    </row>
+    <row r="61" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B61" s="17"/>
+      <c r="C61" s="40"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="56"/>
+      <c r="F61" s="21"/>
+      <c r="G61" s="34"/>
+      <c r="H61" s="35"/>
+      <c r="I61" s="36"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="37"/>
+      <c r="M61" s="35"/>
+      <c r="N61" s="36"/>
+      <c r="O61" s="34"/>
+      <c r="P61" s="34"/>
+      <c r="Q61" s="35"/>
+      <c r="R61" s="36"/>
+      <c r="S61" s="34"/>
+      <c r="T61" s="34"/>
+      <c r="U61" s="37"/>
+      <c r="V61" s="35"/>
+      <c r="W61" s="36"/>
+      <c r="X61" s="36"/>
+      <c r="Y61" s="34"/>
+      <c r="Z61" s="34"/>
+      <c r="AA61" s="35"/>
+      <c r="AB61" s="36"/>
+      <c r="AC61" s="34"/>
+      <c r="AD61" s="34"/>
+      <c r="AE61" s="34"/>
+      <c r="AF61" s="35"/>
+      <c r="AG61" s="36"/>
+      <c r="AH61" s="36"/>
+      <c r="AI61" s="34"/>
+      <c r="AJ61" s="34"/>
+      <c r="AK61" s="35"/>
+      <c r="AL61" s="36"/>
+      <c r="AM61" s="34"/>
+      <c r="AN61" s="34"/>
+      <c r="AO61" s="37"/>
+      <c r="AP61" s="35"/>
+      <c r="AQ61" s="36"/>
+      <c r="AR61" s="34"/>
+      <c r="AS61" s="34"/>
+      <c r="AT61" s="34"/>
+      <c r="AU61" s="35"/>
+      <c r="AY61" s="3"/>
+      <c r="BD61" s="3"/>
+      <c r="BH61" s="3"/>
+      <c r="BM61" s="3"/>
+      <c r="BQ61" s="3"/>
+      <c r="BU61" s="3"/>
+      <c r="BZ61" s="3"/>
+    </row>
+    <row r="62" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B62" s="17"/>
+      <c r="C62" s="40"/>
+      <c r="D62" s="43"/>
+      <c r="E62" s="56"/>
+      <c r="F62" s="21"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="35"/>
+      <c r="I62" s="36"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="37"/>
+      <c r="M62" s="35"/>
+      <c r="N62" s="36"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+      <c r="Q62" s="35"/>
+      <c r="R62" s="36"/>
+      <c r="S62" s="34"/>
+      <c r="T62" s="34"/>
+      <c r="U62" s="37"/>
+      <c r="V62" s="35"/>
+      <c r="W62" s="36"/>
+      <c r="X62" s="36"/>
+      <c r="Y62" s="34"/>
+      <c r="Z62" s="34"/>
+      <c r="AA62" s="35"/>
+      <c r="AB62" s="36"/>
+      <c r="AC62" s="34"/>
+      <c r="AD62" s="34"/>
+      <c r="AE62" s="34"/>
+      <c r="AF62" s="35"/>
+      <c r="AG62" s="36"/>
+      <c r="AH62" s="36"/>
+      <c r="AI62" s="34"/>
+      <c r="AJ62" s="34"/>
+      <c r="AK62" s="35"/>
+      <c r="AL62" s="36"/>
+      <c r="AM62" s="34"/>
+      <c r="AN62" s="34"/>
+      <c r="AO62" s="37"/>
+      <c r="AP62" s="35"/>
+      <c r="AQ62" s="36"/>
+      <c r="AR62" s="34"/>
+      <c r="AS62" s="34"/>
+      <c r="AT62" s="34"/>
+      <c r="AU62" s="35"/>
+      <c r="AY62" s="3"/>
+      <c r="BD62" s="3"/>
+      <c r="BH62" s="3"/>
+      <c r="BM62" s="3"/>
+      <c r="BQ62" s="3"/>
+      <c r="BU62" s="3"/>
+      <c r="BZ62" s="3"/>
+    </row>
+    <row r="63" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B63" s="17"/>
+      <c r="C63" s="40"/>
+      <c r="D63" s="43"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="21"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="35"/>
+      <c r="I63" s="36"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="37"/>
+      <c r="M63" s="35"/>
+      <c r="N63" s="36"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="35"/>
+      <c r="R63" s="36"/>
+      <c r="S63" s="34"/>
+      <c r="T63" s="34"/>
+      <c r="U63" s="37"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="36"/>
+      <c r="X63" s="36"/>
+      <c r="Y63" s="34"/>
+      <c r="Z63" s="34"/>
+      <c r="AA63" s="35"/>
+      <c r="AB63" s="36"/>
+      <c r="AC63" s="34"/>
+      <c r="AD63" s="34"/>
+      <c r="AE63" s="34"/>
+      <c r="AF63" s="35"/>
+      <c r="AG63" s="36"/>
+      <c r="AH63" s="36"/>
+      <c r="AI63" s="34"/>
+      <c r="AJ63" s="34"/>
+      <c r="AK63" s="35"/>
+      <c r="AL63" s="36"/>
+      <c r="AM63" s="34"/>
+      <c r="AN63" s="34"/>
+      <c r="AO63" s="37"/>
+      <c r="AP63" s="35"/>
+      <c r="AQ63" s="36"/>
+      <c r="AR63" s="34"/>
+      <c r="AS63" s="34"/>
+      <c r="AT63" s="34"/>
+      <c r="AU63" s="35"/>
+      <c r="AY63" s="3"/>
+      <c r="BD63" s="3"/>
+      <c r="BH63" s="3"/>
+      <c r="BM63" s="3"/>
+      <c r="BQ63" s="3"/>
+      <c r="BU63" s="3"/>
+      <c r="BZ63" s="3"/>
+    </row>
+    <row r="64" spans="2:78" x14ac:dyDescent="0.15">
+      <c r="B64" s="33"/>
+      <c r="C64" s="40"/>
+      <c r="D64" s="43"/>
+      <c r="E64" s="56"/>
+      <c r="F64" s="21"/>
+      <c r="G64" s="34"/>
+      <c r="H64" s="35"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="34"/>
+      <c r="L64" s="37"/>
+      <c r="M64" s="35"/>
+      <c r="N64" s="36"/>
+      <c r="O64" s="34"/>
+      <c r="P64" s="34"/>
+      <c r="Q64" s="35"/>
+      <c r="R64" s="36"/>
+      <c r="S64" s="34"/>
+      <c r="T64" s="34"/>
+      <c r="U64" s="37"/>
+      <c r="V64" s="35"/>
+      <c r="W64" s="36"/>
+      <c r="X64" s="36"/>
+      <c r="Y64" s="34"/>
+      <c r="Z64" s="34"/>
+      <c r="AA64" s="35"/>
+      <c r="AB64" s="36"/>
+      <c r="AC64" s="34"/>
+      <c r="AD64" s="34"/>
+      <c r="AE64" s="34"/>
+      <c r="AF64" s="35"/>
+      <c r="AG64" s="36"/>
+      <c r="AH64" s="36"/>
+      <c r="AI64" s="34"/>
+      <c r="AJ64" s="34"/>
+      <c r="AK64" s="35"/>
+      <c r="AL64" s="36"/>
+      <c r="AM64" s="34"/>
+      <c r="AN64" s="34"/>
+      <c r="AO64" s="37"/>
+      <c r="AP64" s="35"/>
+      <c r="AQ64" s="36"/>
+      <c r="AR64" s="34"/>
+      <c r="AS64" s="34"/>
+      <c r="AT64" s="34"/>
+      <c r="AU64" s="35"/>
+      <c r="AY64" s="3"/>
+      <c r="BD64" s="3"/>
+      <c r="BH64" s="3"/>
+      <c r="BM64" s="3"/>
+      <c r="BQ64" s="3"/>
+      <c r="BU64" s="3"/>
+      <c r="BZ64" s="3"/>
+    </row>
+    <row r="65" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H65" s="3"/>
+      <c r="M65" s="3"/>
+      <c r="Q65" s="3"/>
+      <c r="V65" s="3"/>
+      <c r="AA65" s="3"/>
+      <c r="AF65" s="3"/>
+      <c r="AK65" s="3"/>
+      <c r="AP65" s="3"/>
+      <c r="AU65" s="3"/>
+      <c r="AY65" s="3"/>
+      <c r="BD65" s="3"/>
+      <c r="BH65" s="3"/>
+      <c r="BM65" s="3"/>
+      <c r="BQ65" s="3"/>
+      <c r="BU65" s="3"/>
+      <c r="BZ65" s="3"/>
+    </row>
+    <row r="66" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="C66" s="41"/>
+      <c r="D66" s="42"/>
+      <c r="E66" s="42"/>
+      <c r="H66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="AA66" s="3"/>
+      <c r="AF66" s="3"/>
+      <c r="AK66" s="3"/>
+      <c r="AP66" s="3"/>
+      <c r="AU66" s="3"/>
+      <c r="AY66" s="3"/>
+      <c r="BD66" s="3"/>
+      <c r="BH66" s="3"/>
+      <c r="BM66" s="3"/>
+      <c r="BQ66" s="3"/>
+      <c r="BU66" s="3"/>
+      <c r="BZ66" s="3"/>
+    </row>
+    <row r="67" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="C67" s="41"/>
+      <c r="H67" s="3"/>
+      <c r="M67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="V67" s="3"/>
+      <c r="AA67" s="3"/>
+      <c r="AF67" s="3"/>
+      <c r="AK67" s="3"/>
+      <c r="AP67" s="3"/>
+      <c r="AU67" s="3"/>
+      <c r="AY67" s="3"/>
+      <c r="BD67" s="3"/>
+      <c r="BH67" s="3"/>
+      <c r="BM67" s="3"/>
+      <c r="BQ67" s="3"/>
+      <c r="BU67" s="3"/>
+      <c r="BZ67" s="3"/>
+    </row>
+    <row r="68" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="C68" s="41"/>
+      <c r="H68" s="3"/>
+      <c r="M68" s="3"/>
+      <c r="Q68" s="3"/>
+      <c r="V68" s="3"/>
+      <c r="AA68" s="3"/>
+      <c r="AF68" s="3"/>
+      <c r="AK68" s="3"/>
+      <c r="AP68" s="3"/>
+      <c r="AU68" s="3"/>
+      <c r="AY68" s="3"/>
+      <c r="BD68" s="3"/>
+      <c r="BH68" s="3"/>
+      <c r="BM68" s="3"/>
+      <c r="BQ68" s="3"/>
+      <c r="BU68" s="3"/>
+      <c r="BZ68" s="3"/>
+    </row>
+    <row r="69" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="C69" s="41"/>
+      <c r="H69" s="3"/>
+      <c r="M69" s="3"/>
+      <c r="Q69" s="3"/>
+      <c r="V69" s="3"/>
+      <c r="AA69" s="3"/>
+      <c r="AF69" s="3"/>
+      <c r="AK69" s="3"/>
+      <c r="AP69" s="3"/>
+      <c r="AU69" s="3"/>
+      <c r="AY69" s="3"/>
+      <c r="BD69" s="3"/>
+      <c r="BH69" s="3"/>
+      <c r="BM69" s="3"/>
+      <c r="BQ69" s="3"/>
+      <c r="BU69" s="3"/>
+      <c r="BZ69" s="3"/>
+    </row>
+    <row r="70" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="C70" s="41"/>
+      <c r="H70" s="3"/>
+      <c r="M70" s="3"/>
+      <c r="Q70" s="3"/>
+      <c r="V70" s="3"/>
+      <c r="AA70" s="3"/>
+      <c r="AF70" s="3"/>
+      <c r="AK70" s="3"/>
+      <c r="AP70" s="3"/>
+      <c r="AU70" s="3"/>
+      <c r="AY70" s="3"/>
+      <c r="BD70" s="3"/>
+      <c r="BH70" s="3"/>
+      <c r="BM70" s="3"/>
+      <c r="BQ70" s="3"/>
+      <c r="BU70" s="3"/>
+      <c r="BZ70" s="3"/>
+    </row>
+    <row r="71" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H71" s="3"/>
+      <c r="M71" s="3"/>
+      <c r="Q71" s="3"/>
+      <c r="V71" s="3"/>
+      <c r="AA71" s="3"/>
+      <c r="AF71" s="3"/>
+      <c r="AK71" s="3"/>
+      <c r="AP71" s="3"/>
+      <c r="AU71" s="3"/>
+      <c r="AY71" s="3"/>
+      <c r="BD71" s="3"/>
+      <c r="BH71" s="3"/>
+      <c r="BM71" s="3"/>
+      <c r="BQ71" s="3"/>
+      <c r="BU71" s="3"/>
+      <c r="BZ71" s="3"/>
+    </row>
+    <row r="72" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H72" s="3"/>
+      <c r="M72" s="3"/>
+      <c r="Q72" s="3"/>
+      <c r="V72" s="3"/>
+      <c r="AA72" s="3"/>
+      <c r="AF72" s="3"/>
+      <c r="AK72" s="3"/>
+      <c r="AP72" s="3"/>
+      <c r="AU72" s="3"/>
+      <c r="AY72" s="3"/>
+      <c r="BD72" s="3"/>
+      <c r="BH72" s="3"/>
+      <c r="BM72" s="3"/>
+      <c r="BQ72" s="3"/>
+      <c r="BU72" s="3"/>
+      <c r="BZ72" s="3"/>
+    </row>
+    <row r="73" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H73" s="3"/>
+      <c r="M73" s="3"/>
+      <c r="Q73" s="3"/>
+      <c r="V73" s="3"/>
+      <c r="AA73" s="3"/>
+      <c r="AF73" s="3"/>
+      <c r="AK73" s="3"/>
+      <c r="AP73" s="3"/>
+      <c r="AU73" s="3"/>
+      <c r="AY73" s="3"/>
+      <c r="BD73" s="3"/>
+      <c r="BH73" s="3"/>
+      <c r="BM73" s="3"/>
+      <c r="BQ73" s="3"/>
+      <c r="BU73" s="3"/>
+      <c r="BZ73" s="3"/>
+    </row>
+    <row r="74" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H74" s="3"/>
+      <c r="M74" s="3"/>
+      <c r="Q74" s="3"/>
+      <c r="V74" s="3"/>
+      <c r="AA74" s="3"/>
+      <c r="AF74" s="3"/>
+      <c r="AK74" s="3"/>
+      <c r="AP74" s="3"/>
+      <c r="AU74" s="3"/>
+      <c r="AY74" s="3"/>
+      <c r="BD74" s="3"/>
+      <c r="BH74" s="3"/>
+      <c r="BM74" s="3"/>
+      <c r="BQ74" s="3"/>
+      <c r="BU74" s="3"/>
+      <c r="BZ74" s="3"/>
+    </row>
+    <row r="75" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H75" s="3"/>
+      <c r="M75" s="3"/>
+      <c r="Q75" s="3"/>
+      <c r="V75" s="3"/>
+      <c r="AA75" s="3"/>
+      <c r="AF75" s="3"/>
+      <c r="AK75" s="3"/>
+      <c r="AP75" s="3"/>
+      <c r="AU75" s="3"/>
+      <c r="AY75" s="3"/>
+      <c r="BD75" s="3"/>
+      <c r="BH75" s="3"/>
+      <c r="BM75" s="3"/>
+      <c r="BQ75" s="3"/>
+      <c r="BU75" s="3"/>
+      <c r="BZ75" s="3"/>
+    </row>
+    <row r="76" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="AA76" s="3"/>
+      <c r="AF76" s="3"/>
+      <c r="AK76" s="3"/>
+      <c r="AP76" s="3"/>
+      <c r="AU76" s="3"/>
+      <c r="AY76" s="3"/>
+      <c r="BD76" s="3"/>
+      <c r="BH76" s="3"/>
+      <c r="BM76" s="3"/>
+      <c r="BQ76" s="3"/>
+      <c r="BU76" s="3"/>
+      <c r="BZ76" s="3"/>
+    </row>
+    <row r="77" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H77" s="3"/>
+      <c r="M77" s="3"/>
+      <c r="Q77" s="3"/>
+      <c r="V77" s="3"/>
+      <c r="AA77" s="3"/>
+      <c r="AF77" s="3"/>
+      <c r="AK77" s="3"/>
+      <c r="AP77" s="3"/>
+      <c r="AU77" s="3"/>
+      <c r="AY77" s="3"/>
+      <c r="BD77" s="3"/>
+      <c r="BH77" s="3"/>
+      <c r="BM77" s="3"/>
+      <c r="BQ77" s="3"/>
+      <c r="BU77" s="3"/>
+      <c r="BZ77" s="3"/>
+    </row>
+    <row r="78" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H78" s="3"/>
+      <c r="M78" s="3"/>
+      <c r="Q78" s="3"/>
+      <c r="V78" s="3"/>
+      <c r="AA78" s="3"/>
+      <c r="AF78" s="3"/>
+      <c r="AK78" s="3"/>
+      <c r="AP78" s="3"/>
+      <c r="AU78" s="3"/>
+      <c r="AY78" s="3"/>
+      <c r="BD78" s="3"/>
+      <c r="BH78" s="3"/>
+      <c r="BM78" s="3"/>
+      <c r="BQ78" s="3"/>
+      <c r="BU78" s="3"/>
+      <c r="BZ78" s="3"/>
+    </row>
+    <row r="79" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H79" s="3"/>
+      <c r="M79" s="3"/>
+      <c r="Q79" s="3"/>
+      <c r="V79" s="3"/>
+      <c r="AA79" s="3"/>
+      <c r="AF79" s="3"/>
+      <c r="AK79" s="3"/>
+      <c r="AP79" s="3"/>
+      <c r="AU79" s="3"/>
+      <c r="AY79" s="3"/>
+      <c r="BD79" s="3"/>
+      <c r="BH79" s="3"/>
+      <c r="BM79" s="3"/>
+      <c r="BQ79" s="3"/>
+      <c r="BU79" s="3"/>
+      <c r="BZ79" s="3"/>
+    </row>
+    <row r="80" spans="3:78" x14ac:dyDescent="0.15">
+      <c r="H80" s="3"/>
+      <c r="M80" s="3"/>
+      <c r="Q80" s="3"/>
+      <c r="V80" s="3"/>
+      <c r="AA80" s="3"/>
+      <c r="AF80" s="3"/>
+      <c r="AK80" s="3"/>
+      <c r="AP80" s="3"/>
+      <c r="AU80" s="3"/>
+      <c r="AY80" s="3"/>
+      <c r="BD80" s="3"/>
+      <c r="BH80" s="3"/>
+      <c r="BM80" s="3"/>
+      <c r="BQ80" s="3"/>
+      <c r="BU80" s="3"/>
+      <c r="BZ80" s="3"/>
+    </row>
+    <row r="81" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="82" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="83" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="84" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="85" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="86" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="87" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="88" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="89" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="90" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="91" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="92" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="93" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="94" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="95" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="96" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="97" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="98" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="99" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="100" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="101" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="102" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="103" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="104" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="105" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="106" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="107" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="108" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="109" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="110" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="111" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="112" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="113" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="114" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="115" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="116" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="117" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="118" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="119" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="120" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="121" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="122" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="123" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="124" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="125" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="126" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="127" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="128" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="129" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="130" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="131" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="132" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="133" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="134" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="135" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="136" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="137" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="138" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="139" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="140" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="141" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="142" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="143" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="144" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="145" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="146" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="147" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="148" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="149" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="150" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="151" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="152" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="153" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="154" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="155" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="156" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="157" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="158" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="159" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="160" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="161" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="162" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="163" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="164" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="165" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="166" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="167" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="168" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="169" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="170" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="171" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="172" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="173" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="174" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="175" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="176" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="177" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="178" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="179" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="180" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="181" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="182" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="183" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="184" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="185" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="186" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="187" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="188" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="189" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="190" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="191" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="192" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="193" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="194" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="195" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="196" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="197" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="198" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="199" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="200" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="201" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="202" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="203" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="204" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="205" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="206" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="207" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="208" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="209" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="210" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="211" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="212" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="213" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="214" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="215" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="216" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="217" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="218" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="219" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="220" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="221" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="222" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="223" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="224" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="225" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="226" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="227" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="228" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="229" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="230" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="231" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="232" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="233" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="234" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="235" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="236" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="237" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="238" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="239" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="240" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="241" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="242" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="243" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="244" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="245" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="246" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="247" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="248" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="249" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="250" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="251" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="252" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="253" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="254" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="255" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="256" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="257" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="258" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="259" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="260" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="261" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="262" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="263" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="264" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="265" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="266" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="267" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="268" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="269" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="270" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="271" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="272" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="273" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="274" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="275" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="276" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="277" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="278" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="279" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="280" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="281" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="282" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="283" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="284" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="285" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="286" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="287" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="288" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="289" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="290" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="291" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="292" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="293" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="294" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="295" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="296" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="297" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="298" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="299" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="300" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="301" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="302" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="303" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="304" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="305" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="306" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="307" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="308" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="309" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="310" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="311" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="312" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="313" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="314" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="315" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="316" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="317" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="318" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="319" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="320" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="321" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="322" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="323" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="324" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="325" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="326" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="327" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="328" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="329" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="330" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="331" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="332" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="333" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="334" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="335" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="336" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="337" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="338" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="339" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="340" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="341" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="342" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="343" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="344" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="345" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="346" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="347" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="348" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="349" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="350" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="351" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="352" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="353" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="354" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="355" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="356" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="357" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="358" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="359" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="360" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="361" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="362" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="363" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="364" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="365" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="366" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="367" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="368" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="369" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="370" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="371" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="372" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="373" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="374" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="375" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="376" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="377" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="378" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="379" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="380" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="381" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="382" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="383" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="384" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="385" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="386" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="387" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="388" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="389" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="390" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="391" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="392" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="393" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="394" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="395" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="396" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="397" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="398" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="399" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="400" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="401" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="402" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="403" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="404" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="405" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="406" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="407" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="408" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="409" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="410" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="411" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="412" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="413" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="414" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="415" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="416" s="3" customFormat="1" x14ac:dyDescent="0.15"/>
+    <row r="417" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H417" s="3"/>
+      <c r="M417" s="3"/>
+      <c r="Q417" s="3"/>
+      <c r="V417" s="3"/>
+      <c r="AA417" s="3"/>
+      <c r="AF417" s="3"/>
+      <c r="AK417" s="3"/>
+      <c r="AP417" s="3"/>
+      <c r="AU417" s="3"/>
+      <c r="AY417" s="3"/>
+      <c r="BD417" s="3"/>
+      <c r="BH417" s="3"/>
+      <c r="BM417" s="3"/>
+      <c r="BQ417" s="3"/>
+      <c r="BU417" s="3"/>
+      <c r="BZ417" s="3"/>
+    </row>
+    <row r="418" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H418" s="3"/>
+      <c r="M418" s="3"/>
+      <c r="Q418" s="3"/>
+      <c r="V418" s="3"/>
+      <c r="AA418" s="3"/>
+      <c r="AF418" s="3"/>
+      <c r="AK418" s="3"/>
+      <c r="AP418" s="3"/>
+      <c r="AU418" s="3"/>
+      <c r="AY418" s="3"/>
+      <c r="BD418" s="3"/>
+      <c r="BH418" s="3"/>
+      <c r="BM418" s="3"/>
+      <c r="BQ418" s="3"/>
+      <c r="BU418" s="3"/>
+      <c r="BZ418" s="3"/>
+    </row>
+    <row r="419" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H419" s="3"/>
+      <c r="M419" s="3"/>
+      <c r="Q419" s="3"/>
+      <c r="V419" s="3"/>
+      <c r="AA419" s="3"/>
+      <c r="AF419" s="3"/>
+      <c r="AK419" s="3"/>
+      <c r="AP419" s="3"/>
+      <c r="AU419" s="3"/>
+      <c r="AY419" s="3"/>
+      <c r="BD419" s="3"/>
+      <c r="BH419" s="3"/>
+      <c r="BM419" s="3"/>
+      <c r="BQ419" s="3"/>
+      <c r="BU419" s="3"/>
+      <c r="BZ419" s="3"/>
+    </row>
+    <row r="420" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H420" s="3"/>
+      <c r="M420" s="3"/>
+      <c r="Q420" s="3"/>
+      <c r="V420" s="3"/>
+      <c r="AA420" s="3"/>
+      <c r="AF420" s="3"/>
+      <c r="AK420" s="3"/>
+      <c r="AP420" s="3"/>
+      <c r="AU420" s="3"/>
+      <c r="AY420" s="3"/>
+      <c r="BD420" s="3"/>
+      <c r="BH420" s="3"/>
+      <c r="BM420" s="3"/>
+      <c r="BQ420" s="3"/>
+      <c r="BU420" s="3"/>
+      <c r="BZ420" s="3"/>
+    </row>
+    <row r="421" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H421" s="3"/>
+      <c r="M421" s="3"/>
+      <c r="Q421" s="3"/>
+      <c r="V421" s="3"/>
+      <c r="AA421" s="3"/>
+      <c r="AF421" s="3"/>
+      <c r="AK421" s="3"/>
+      <c r="AP421" s="3"/>
+      <c r="AU421" s="3"/>
+      <c r="AY421" s="3"/>
+      <c r="BD421" s="3"/>
+      <c r="BH421" s="3"/>
+      <c r="BM421" s="3"/>
+      <c r="BQ421" s="3"/>
+      <c r="BU421" s="3"/>
+      <c r="BZ421" s="3"/>
+    </row>
+    <row r="422" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H422" s="3"/>
+      <c r="M422" s="3"/>
+      <c r="Q422" s="3"/>
+      <c r="V422" s="3"/>
+      <c r="AA422" s="3"/>
+      <c r="AF422" s="3"/>
+      <c r="AK422" s="3"/>
+      <c r="AP422" s="3"/>
+      <c r="AU422" s="3"/>
+      <c r="AY422" s="3"/>
+      <c r="BD422" s="3"/>
+      <c r="BH422" s="3"/>
+      <c r="BM422" s="3"/>
+      <c r="BQ422" s="3"/>
+      <c r="BU422" s="3"/>
+      <c r="BZ422" s="3"/>
+    </row>
+    <row r="423" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H423" s="3"/>
+      <c r="M423" s="3"/>
+      <c r="Q423" s="3"/>
+      <c r="V423" s="3"/>
+      <c r="AA423" s="3"/>
+      <c r="AF423" s="3"/>
+      <c r="AK423" s="3"/>
+      <c r="AP423" s="3"/>
+      <c r="AU423" s="3"/>
+      <c r="AY423" s="3"/>
+      <c r="BD423" s="3"/>
+      <c r="BH423" s="3"/>
+      <c r="BM423" s="3"/>
+      <c r="BQ423" s="3"/>
+      <c r="BU423" s="3"/>
+      <c r="BZ423" s="3"/>
+    </row>
+    <row r="424" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H424" s="3"/>
+      <c r="M424" s="3"/>
+      <c r="Q424" s="3"/>
+      <c r="V424" s="3"/>
+      <c r="AA424" s="3"/>
+      <c r="AF424" s="3"/>
+      <c r="AK424" s="3"/>
+      <c r="AP424" s="3"/>
+      <c r="AU424" s="3"/>
+      <c r="AY424" s="3"/>
+      <c r="BD424" s="3"/>
+      <c r="BH424" s="3"/>
+      <c r="BM424" s="3"/>
+      <c r="BQ424" s="3"/>
+      <c r="BU424" s="3"/>
+      <c r="BZ424" s="3"/>
+    </row>
+    <row r="425" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H425" s="3"/>
+      <c r="M425" s="3"/>
+      <c r="Q425" s="3"/>
+      <c r="V425" s="3"/>
+      <c r="AA425" s="3"/>
+      <c r="AF425" s="3"/>
+      <c r="AK425" s="3"/>
+      <c r="AP425" s="3"/>
+      <c r="AU425" s="3"/>
+      <c r="AY425" s="3"/>
+      <c r="BD425" s="3"/>
+      <c r="BH425" s="3"/>
+      <c r="BM425" s="3"/>
+      <c r="BQ425" s="3"/>
+      <c r="BU425" s="3"/>
+      <c r="BZ425" s="3"/>
+    </row>
+    <row r="426" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H426" s="3"/>
+      <c r="M426" s="3"/>
+      <c r="Q426" s="3"/>
+      <c r="V426" s="3"/>
+      <c r="AA426" s="3"/>
+      <c r="AF426" s="3"/>
+      <c r="AK426" s="3"/>
+      <c r="AP426" s="3"/>
+      <c r="AU426" s="3"/>
+      <c r="AY426" s="3"/>
+      <c r="BD426" s="3"/>
+      <c r="BH426" s="3"/>
+      <c r="BM426" s="3"/>
+      <c r="BQ426" s="3"/>
+      <c r="BU426" s="3"/>
+      <c r="BZ426" s="3"/>
+    </row>
+    <row r="427" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H427" s="3"/>
+      <c r="M427" s="3"/>
+      <c r="Q427" s="3"/>
+      <c r="V427" s="3"/>
+      <c r="AA427" s="3"/>
+      <c r="AF427" s="3"/>
+      <c r="AK427" s="3"/>
+      <c r="AP427" s="3"/>
+      <c r="AU427" s="3"/>
+      <c r="AY427" s="3"/>
+      <c r="BD427" s="3"/>
+      <c r="BH427" s="3"/>
+      <c r="BM427" s="3"/>
+      <c r="BQ427" s="3"/>
+      <c r="BU427" s="3"/>
+      <c r="BZ427" s="3"/>
+    </row>
+    <row r="428" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H428" s="3"/>
+      <c r="M428" s="3"/>
+      <c r="Q428" s="3"/>
+      <c r="V428" s="3"/>
+      <c r="AA428" s="3"/>
+      <c r="AF428" s="3"/>
+      <c r="AK428" s="3"/>
+      <c r="AP428" s="3"/>
+      <c r="AU428" s="3"/>
+      <c r="AY428" s="3"/>
+      <c r="BD428" s="3"/>
+      <c r="BH428" s="3"/>
+      <c r="BM428" s="3"/>
+      <c r="BQ428" s="3"/>
+      <c r="BU428" s="3"/>
+      <c r="BZ428" s="3"/>
+    </row>
+    <row r="429" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H429" s="3"/>
+      <c r="M429" s="3"/>
+      <c r="Q429" s="3"/>
+      <c r="V429" s="3"/>
+      <c r="AA429" s="3"/>
+      <c r="AF429" s="3"/>
+      <c r="AK429" s="3"/>
+      <c r="AP429" s="3"/>
+      <c r="AU429" s="3"/>
+      <c r="AY429" s="3"/>
+      <c r="BZ429" s="3"/>
+    </row>
+    <row r="430" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H430" s="3"/>
+      <c r="M430" s="3"/>
+      <c r="Q430" s="3"/>
+      <c r="V430" s="3"/>
+      <c r="AA430" s="3"/>
+      <c r="AF430" s="3"/>
+      <c r="AK430" s="3"/>
+      <c r="AP430" s="3"/>
+      <c r="AU430" s="3"/>
+    </row>
+    <row r="431" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H431" s="3"/>
+      <c r="M431" s="3"/>
+      <c r="Q431" s="3"/>
+      <c r="V431" s="3"/>
+      <c r="AA431" s="3"/>
+      <c r="AF431" s="3"/>
+      <c r="AK431" s="3"/>
+      <c r="AP431" s="3"/>
+      <c r="AU431" s="3"/>
+    </row>
+    <row r="432" spans="8:78" x14ac:dyDescent="0.15">
+      <c r="H432" s="3"/>
+      <c r="M432" s="3"/>
+      <c r="Q432" s="3"/>
+      <c r="V432" s="3"/>
+      <c r="AA432" s="3"/>
+      <c r="AF432" s="3"/>
+      <c r="AK432" s="3"/>
+      <c r="AP432" s="3"/>
+      <c r="AU432" s="3"/>
+    </row>
+    <row r="433" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H433" s="3"/>
+      <c r="M433" s="3"/>
+      <c r="Q433" s="3"/>
+      <c r="V433" s="3"/>
+      <c r="AA433" s="3"/>
+      <c r="AF433" s="3"/>
+      <c r="AK433" s="3"/>
+      <c r="AP433" s="3"/>
+      <c r="AU433" s="3"/>
+    </row>
+    <row r="434" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H434" s="3"/>
+      <c r="M434" s="3"/>
+      <c r="Q434" s="3"/>
+      <c r="V434" s="3"/>
+      <c r="AA434" s="3"/>
+      <c r="AF434" s="3"/>
+      <c r="AK434" s="3"/>
+      <c r="AP434" s="3"/>
+      <c r="AU434" s="3"/>
+    </row>
+    <row r="435" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H435" s="3"/>
+      <c r="M435" s="3"/>
+      <c r="Q435" s="3"/>
+      <c r="V435" s="3"/>
+      <c r="AA435" s="3"/>
+      <c r="AF435" s="3"/>
+      <c r="AK435" s="3"/>
+      <c r="AP435" s="3"/>
+      <c r="AU435" s="3"/>
+    </row>
+    <row r="436" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H436" s="3"/>
+      <c r="M436" s="3"/>
+      <c r="Q436" s="3"/>
+      <c r="V436" s="3"/>
+      <c r="AA436" s="3"/>
+      <c r="AF436" s="3"/>
+      <c r="AK436" s="3"/>
+      <c r="AP436" s="3"/>
+      <c r="AU436" s="3"/>
+    </row>
+    <row r="437" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H437" s="3"/>
+      <c r="M437" s="3"/>
+      <c r="Q437" s="3"/>
+      <c r="V437" s="3"/>
+      <c r="AA437" s="3"/>
+      <c r="AF437" s="3"/>
+      <c r="AK437" s="3"/>
+      <c r="AP437" s="3"/>
+      <c r="AU437" s="3"/>
+    </row>
+    <row r="438" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H438" s="3"/>
+      <c r="M438" s="3"/>
+      <c r="Q438" s="3"/>
+      <c r="V438" s="3"/>
+      <c r="AA438" s="3"/>
+      <c r="AF438" s="3"/>
+      <c r="AK438" s="3"/>
+      <c r="AP438" s="3"/>
+      <c r="AU438" s="3"/>
+    </row>
+    <row r="439" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H439" s="3"/>
+      <c r="M439" s="3"/>
+      <c r="Q439" s="3"/>
+      <c r="V439" s="3"/>
+      <c r="AA439" s="3"/>
+      <c r="AF439" s="3"/>
+      <c r="AK439" s="3"/>
+      <c r="AP439" s="3"/>
+      <c r="AU439" s="3"/>
+    </row>
+    <row r="440" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H440" s="3"/>
+      <c r="M440" s="3"/>
+      <c r="Q440" s="3"/>
+      <c r="V440" s="3"/>
+      <c r="AA440" s="3"/>
+      <c r="AF440" s="3"/>
+      <c r="AK440" s="3"/>
+      <c r="AP440" s="3"/>
+      <c r="AU440" s="3"/>
+    </row>
+    <row r="441" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H441" s="3"/>
+      <c r="M441" s="3"/>
+      <c r="Q441" s="3"/>
+      <c r="V441" s="3"/>
+      <c r="AA441" s="3"/>
+      <c r="AF441" s="3"/>
+      <c r="AK441" s="3"/>
+      <c r="AP441" s="3"/>
+      <c r="AU441" s="3"/>
+    </row>
+    <row r="442" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H442" s="3"/>
+      <c r="M442" s="3"/>
+      <c r="Q442" s="3"/>
+      <c r="V442" s="3"/>
+      <c r="AA442" s="3"/>
+      <c r="AF442" s="3"/>
+      <c r="AK442" s="3"/>
+      <c r="AP442" s="3"/>
+      <c r="AU442" s="3"/>
+    </row>
+    <row r="443" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H443" s="3"/>
+      <c r="M443" s="3"/>
+      <c r="Q443" s="3"/>
+      <c r="V443" s="3"/>
+      <c r="AA443" s="3"/>
+      <c r="AF443" s="3"/>
+      <c r="AK443" s="3"/>
+      <c r="AP443" s="3"/>
+      <c r="AU443" s="3"/>
+    </row>
+    <row r="444" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H444" s="3"/>
+      <c r="M444" s="3"/>
+      <c r="Q444" s="3"/>
+      <c r="V444" s="3"/>
+      <c r="AA444" s="3"/>
+      <c r="AF444" s="3"/>
+      <c r="AK444" s="3"/>
+      <c r="AP444" s="3"/>
+      <c r="AU444" s="3"/>
+    </row>
+    <row r="445" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H445" s="3"/>
+      <c r="M445" s="3"/>
+      <c r="Q445" s="3"/>
+      <c r="V445" s="3"/>
+      <c r="AA445" s="3"/>
+      <c r="AF445" s="3"/>
+      <c r="AK445" s="3"/>
+      <c r="AP445" s="3"/>
+      <c r="AU445" s="3"/>
+    </row>
+    <row r="446" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H446" s="3"/>
+      <c r="M446" s="3"/>
+      <c r="Q446" s="3"/>
+      <c r="V446" s="3"/>
+      <c r="AA446" s="3"/>
+      <c r="AF446" s="3"/>
+      <c r="AK446" s="3"/>
+      <c r="AP446" s="3"/>
+      <c r="AU446" s="3"/>
+    </row>
+    <row r="447" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H447" s="3"/>
+      <c r="M447" s="3"/>
+      <c r="Q447" s="3"/>
+      <c r="V447" s="3"/>
+      <c r="AA447" s="3"/>
+      <c r="AF447" s="3"/>
+      <c r="AK447" s="3"/>
+      <c r="AP447" s="3"/>
+      <c r="AU447" s="3"/>
+    </row>
+    <row r="448" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H448" s="3"/>
+      <c r="M448" s="3"/>
+      <c r="Q448" s="3"/>
+      <c r="V448" s="3"/>
+      <c r="AA448" s="3"/>
+      <c r="AF448" s="3"/>
+      <c r="AK448" s="3"/>
+      <c r="AP448" s="3"/>
+      <c r="AU448" s="3"/>
+    </row>
+    <row r="449" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H449" s="3"/>
+      <c r="M449" s="3"/>
+      <c r="Q449" s="3"/>
+      <c r="V449" s="3"/>
+      <c r="AA449" s="3"/>
+      <c r="AF449" s="3"/>
+      <c r="AK449" s="3"/>
+      <c r="AP449" s="3"/>
+      <c r="AU449" s="3"/>
+    </row>
+    <row r="450" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H450" s="3"/>
+      <c r="M450" s="3"/>
+      <c r="Q450" s="3"/>
+      <c r="V450" s="3"/>
+      <c r="AA450" s="3"/>
+      <c r="AF450" s="3"/>
+      <c r="AK450" s="3"/>
+      <c r="AP450" s="3"/>
+      <c r="AU450" s="3"/>
+    </row>
+    <row r="451" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H451" s="3"/>
+      <c r="M451" s="3"/>
+      <c r="Q451" s="3"/>
+      <c r="V451" s="3"/>
+      <c r="AA451" s="3"/>
+      <c r="AF451" s="3"/>
+      <c r="AK451" s="3"/>
+      <c r="AP451" s="3"/>
+      <c r="AU451" s="3"/>
+    </row>
+    <row r="452" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H452" s="3"/>
+      <c r="M452" s="3"/>
+      <c r="Q452" s="3"/>
+      <c r="V452" s="3"/>
+      <c r="AA452" s="3"/>
+      <c r="AF452" s="3"/>
+      <c r="AK452" s="3"/>
+      <c r="AP452" s="3"/>
+      <c r="AU452" s="3"/>
+    </row>
+    <row r="453" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H453" s="3"/>
+      <c r="M453" s="3"/>
+      <c r="Q453" s="3"/>
+      <c r="V453" s="3"/>
+      <c r="AA453" s="3"/>
+      <c r="AF453" s="3"/>
+      <c r="AK453" s="3"/>
+      <c r="AP453" s="3"/>
+      <c r="AU453" s="3"/>
+    </row>
+    <row r="454" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H454" s="3"/>
+      <c r="M454" s="3"/>
+      <c r="Q454" s="3"/>
+      <c r="V454" s="3"/>
+      <c r="AA454" s="3"/>
+      <c r="AF454" s="3"/>
+      <c r="AK454" s="3"/>
+      <c r="AP454" s="3"/>
+      <c r="AU454" s="3"/>
+    </row>
+    <row r="455" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H455" s="3"/>
+      <c r="M455" s="3"/>
+      <c r="Q455" s="3"/>
+      <c r="V455" s="3"/>
+      <c r="AA455" s="3"/>
+      <c r="AF455" s="3"/>
+      <c r="AK455" s="3"/>
+      <c r="AP455" s="3"/>
+      <c r="AU455" s="3"/>
+    </row>
+    <row r="456" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H456" s="3"/>
+      <c r="M456" s="3"/>
+      <c r="Q456" s="3"/>
+      <c r="V456" s="3"/>
+      <c r="AA456" s="3"/>
+      <c r="AF456" s="3"/>
+      <c r="AK456" s="3"/>
+      <c r="AP456" s="3"/>
+      <c r="AU456" s="3"/>
+    </row>
+    <row r="457" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H457" s="3"/>
+      <c r="M457" s="3"/>
+      <c r="Q457" s="3"/>
+      <c r="V457" s="3"/>
+      <c r="AA457" s="3"/>
+      <c r="AF457" s="3"/>
+      <c r="AK457" s="3"/>
+      <c r="AP457" s="3"/>
+      <c r="AU457" s="3"/>
+    </row>
+    <row r="458" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H458" s="3"/>
+      <c r="M458" s="3"/>
+      <c r="Q458" s="3"/>
+      <c r="V458" s="3"/>
+      <c r="AA458" s="3"/>
+      <c r="AF458" s="3"/>
+      <c r="AK458" s="3"/>
+      <c r="AP458" s="3"/>
+      <c r="AU458" s="3"/>
+    </row>
+    <row r="459" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H459" s="3"/>
+      <c r="M459" s="3"/>
+      <c r="Q459" s="3"/>
+      <c r="V459" s="3"/>
+      <c r="AA459" s="3"/>
+      <c r="AF459" s="3"/>
+      <c r="AK459" s="3"/>
+      <c r="AP459" s="3"/>
+      <c r="AU459" s="3"/>
+    </row>
+    <row r="460" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H460" s="3"/>
+      <c r="M460" s="3"/>
+      <c r="Q460" s="3"/>
+      <c r="V460" s="3"/>
+      <c r="AA460" s="3"/>
+      <c r="AF460" s="3"/>
+      <c r="AK460" s="3"/>
+      <c r="AP460" s="3"/>
+      <c r="AU460" s="3"/>
+    </row>
+    <row r="461" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H461" s="3"/>
+      <c r="M461" s="3"/>
+      <c r="Q461" s="3"/>
+      <c r="V461" s="3"/>
+      <c r="AA461" s="3"/>
+      <c r="AF461" s="3"/>
+      <c r="AK461" s="3"/>
+      <c r="AP461" s="3"/>
+      <c r="AU461" s="3"/>
+    </row>
+    <row r="462" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H462" s="3"/>
+      <c r="M462" s="3"/>
+      <c r="Q462" s="3"/>
+      <c r="V462" s="3"/>
+      <c r="AA462" s="3"/>
+      <c r="AF462" s="3"/>
+      <c r="AK462" s="3"/>
+      <c r="AP462" s="3"/>
+      <c r="AU462" s="3"/>
+    </row>
+    <row r="463" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H463" s="3"/>
+      <c r="M463" s="3"/>
+      <c r="Q463" s="3"/>
+      <c r="V463" s="3"/>
+      <c r="AA463" s="3"/>
+      <c r="AF463" s="3"/>
+      <c r="AK463" s="3"/>
+      <c r="AP463" s="3"/>
+      <c r="AU463" s="3"/>
+    </row>
+    <row r="464" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H464" s="3"/>
+      <c r="M464" s="3"/>
+      <c r="Q464" s="3"/>
+      <c r="V464" s="3"/>
+      <c r="AA464" s="3"/>
+      <c r="AF464" s="3"/>
+      <c r="AK464" s="3"/>
+      <c r="AP464" s="3"/>
+      <c r="AU464" s="3"/>
+    </row>
+    <row r="465" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H465" s="3"/>
+      <c r="M465" s="3"/>
+      <c r="Q465" s="3"/>
+      <c r="V465" s="3"/>
+      <c r="AA465" s="3"/>
+      <c r="AF465" s="3"/>
+      <c r="AK465" s="3"/>
+      <c r="AP465" s="3"/>
+      <c r="AU465" s="3"/>
+    </row>
+    <row r="466" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H466" s="3"/>
+      <c r="M466" s="3"/>
+      <c r="Q466" s="3"/>
+      <c r="V466" s="3"/>
+      <c r="AA466" s="3"/>
+      <c r="AF466" s="3"/>
+      <c r="AK466" s="3"/>
+      <c r="AP466" s="3"/>
+      <c r="AU466" s="3"/>
+    </row>
+    <row r="467" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H467" s="3"/>
+      <c r="M467" s="3"/>
+      <c r="Q467" s="3"/>
+      <c r="V467" s="3"/>
+      <c r="AA467" s="3"/>
+      <c r="AF467" s="3"/>
+      <c r="AK467" s="3"/>
+      <c r="AP467" s="3"/>
+      <c r="AU467" s="3"/>
+    </row>
+    <row r="468" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H468" s="3"/>
+      <c r="M468" s="3"/>
+      <c r="Q468" s="3"/>
+      <c r="V468" s="3"/>
+      <c r="AA468" s="3"/>
+      <c r="AF468" s="3"/>
+      <c r="AK468" s="3"/>
+      <c r="AP468" s="3"/>
+      <c r="AU468" s="3"/>
+    </row>
+    <row r="469" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H469" s="3"/>
+      <c r="M469" s="3"/>
+      <c r="Q469" s="3"/>
+      <c r="V469" s="3"/>
+      <c r="AA469" s="3"/>
+      <c r="AF469" s="3"/>
+      <c r="AK469" s="3"/>
+      <c r="AP469" s="3"/>
+      <c r="AU469" s="3"/>
+    </row>
+    <row r="470" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H470" s="3"/>
+      <c r="M470" s="3"/>
+      <c r="Q470" s="3"/>
+      <c r="V470" s="3"/>
+      <c r="AA470" s="3"/>
+      <c r="AF470" s="3"/>
+      <c r="AK470" s="3"/>
+      <c r="AP470" s="3"/>
+      <c r="AU470" s="3"/>
+    </row>
+    <row r="471" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H471" s="3"/>
+      <c r="M471" s="3"/>
+      <c r="Q471" s="3"/>
+      <c r="V471" s="3"/>
+      <c r="AA471" s="3"/>
+      <c r="AF471" s="3"/>
+      <c r="AK471" s="3"/>
+      <c r="AP471" s="3"/>
+      <c r="AU471" s="3"/>
+    </row>
+    <row r="472" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H472" s="3"/>
+      <c r="M472" s="3"/>
+      <c r="Q472" s="3"/>
+      <c r="V472" s="3"/>
+      <c r="AA472" s="3"/>
+      <c r="AF472" s="3"/>
+      <c r="AK472" s="3"/>
+      <c r="AP472" s="3"/>
+      <c r="AU472" s="3"/>
+    </row>
+    <row r="473" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H473" s="3"/>
+      <c r="M473" s="3"/>
+      <c r="Q473" s="3"/>
+      <c r="V473" s="3"/>
+      <c r="AA473" s="3"/>
+      <c r="AF473" s="3"/>
+      <c r="AK473" s="3"/>
+      <c r="AP473" s="3"/>
+      <c r="AU473" s="3"/>
+    </row>
+    <row r="474" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H474" s="3"/>
+      <c r="M474" s="3"/>
+      <c r="Q474" s="3"/>
+      <c r="V474" s="3"/>
+      <c r="AA474" s="3"/>
+      <c r="AF474" s="3"/>
+      <c r="AK474" s="3"/>
+      <c r="AP474" s="3"/>
+      <c r="AU474" s="3"/>
+    </row>
+    <row r="475" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H475" s="3"/>
+      <c r="M475" s="3"/>
+      <c r="Q475" s="3"/>
+      <c r="V475" s="3"/>
+      <c r="AA475" s="3"/>
+      <c r="AF475" s="3"/>
+      <c r="AK475" s="3"/>
+      <c r="AP475" s="3"/>
+      <c r="AU475" s="3"/>
+    </row>
+    <row r="476" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H476" s="3"/>
+      <c r="M476" s="3"/>
+      <c r="Q476" s="3"/>
+      <c r="V476" s="3"/>
+      <c r="AA476" s="3"/>
+      <c r="AF476" s="3"/>
+      <c r="AK476" s="3"/>
+      <c r="AP476" s="3"/>
+      <c r="AU476" s="3"/>
+    </row>
+    <row r="477" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H477" s="3"/>
+      <c r="M477" s="3"/>
+      <c r="Q477" s="3"/>
+      <c r="V477" s="3"/>
+      <c r="AA477" s="3"/>
+      <c r="AF477" s="3"/>
+      <c r="AK477" s="3"/>
+      <c r="AP477" s="3"/>
+      <c r="AU477" s="3"/>
+    </row>
+    <row r="478" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H478" s="3"/>
+      <c r="M478" s="3"/>
+      <c r="Q478" s="3"/>
+      <c r="V478" s="3"/>
+      <c r="AA478" s="3"/>
+      <c r="AF478" s="3"/>
+      <c r="AK478" s="3"/>
+      <c r="AP478" s="3"/>
+      <c r="AU478" s="3"/>
+    </row>
+    <row r="479" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H479" s="3"/>
+      <c r="M479" s="3"/>
+      <c r="Q479" s="3"/>
+      <c r="V479" s="3"/>
+      <c r="AA479" s="3"/>
+      <c r="AF479" s="3"/>
+      <c r="AK479" s="3"/>
+      <c r="AP479" s="3"/>
+      <c r="AU479" s="3"/>
+    </row>
+    <row r="480" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H480" s="3"/>
+      <c r="M480" s="3"/>
+      <c r="Q480" s="3"/>
+      <c r="V480" s="3"/>
+      <c r="AA480" s="3"/>
+      <c r="AF480" s="3"/>
+      <c r="AK480" s="3"/>
+      <c r="AP480" s="3"/>
+      <c r="AU480" s="3"/>
+    </row>
+    <row r="481" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H481" s="3"/>
+      <c r="M481" s="3"/>
+      <c r="Q481" s="3"/>
+      <c r="V481" s="3"/>
+      <c r="AA481" s="3"/>
+      <c r="AF481" s="3"/>
+      <c r="AK481" s="3"/>
+      <c r="AP481" s="3"/>
+      <c r="AU481" s="3"/>
+    </row>
+    <row r="482" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H482" s="3"/>
+      <c r="M482" s="3"/>
+      <c r="Q482" s="3"/>
+      <c r="V482" s="3"/>
+      <c r="AA482" s="3"/>
+      <c r="AF482" s="3"/>
+      <c r="AK482" s="3"/>
+      <c r="AP482" s="3"/>
+      <c r="AU482" s="3"/>
+    </row>
+    <row r="483" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H483" s="3"/>
+      <c r="M483" s="3"/>
+      <c r="Q483" s="3"/>
+      <c r="V483" s="3"/>
+      <c r="AA483" s="3"/>
+      <c r="AF483" s="3"/>
+      <c r="AK483" s="3"/>
+      <c r="AP483" s="3"/>
+      <c r="AU483" s="3"/>
+    </row>
+    <row r="484" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H484" s="3"/>
+      <c r="M484" s="3"/>
+      <c r="Q484" s="3"/>
+      <c r="V484" s="3"/>
+      <c r="AA484" s="3"/>
+      <c r="AF484" s="3"/>
+      <c r="AK484" s="3"/>
+      <c r="AP484" s="3"/>
+      <c r="AU484" s="3"/>
+    </row>
+    <row r="485" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H485" s="3"/>
+      <c r="M485" s="3"/>
+      <c r="Q485" s="3"/>
+      <c r="V485" s="3"/>
+      <c r="AA485" s="3"/>
+      <c r="AF485" s="3"/>
+      <c r="AK485" s="3"/>
+      <c r="AP485" s="3"/>
+      <c r="AU485" s="3"/>
+    </row>
+    <row r="486" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H486" s="3"/>
+      <c r="M486" s="3"/>
+      <c r="Q486" s="3"/>
+      <c r="V486" s="3"/>
+      <c r="AA486" s="3"/>
+      <c r="AF486" s="3"/>
+      <c r="AK486" s="3"/>
+      <c r="AP486" s="3"/>
+      <c r="AU486" s="3"/>
+    </row>
+    <row r="487" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H487" s="3"/>
+      <c r="M487" s="3"/>
+      <c r="Q487" s="3"/>
+      <c r="V487" s="3"/>
+      <c r="AA487" s="3"/>
+      <c r="AF487" s="3"/>
+      <c r="AK487" s="3"/>
+      <c r="AP487" s="3"/>
+      <c r="AU487" s="3"/>
+    </row>
+    <row r="488" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H488" s="3"/>
+      <c r="M488" s="3"/>
+      <c r="Q488" s="3"/>
+      <c r="V488" s="3"/>
+      <c r="AA488" s="3"/>
+      <c r="AF488" s="3"/>
+      <c r="AK488" s="3"/>
+      <c r="AP488" s="3"/>
+      <c r="AU488" s="3"/>
+    </row>
+    <row r="489" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H489" s="3"/>
+      <c r="M489" s="3"/>
+      <c r="Q489" s="3"/>
+      <c r="V489" s="3"/>
+      <c r="AA489" s="3"/>
+      <c r="AF489" s="3"/>
+      <c r="AK489" s="3"/>
+      <c r="AP489" s="3"/>
+      <c r="AU489" s="3"/>
+    </row>
+    <row r="490" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H490" s="3"/>
+      <c r="M490" s="3"/>
+      <c r="Q490" s="3"/>
+      <c r="V490" s="3"/>
+      <c r="AA490" s="3"/>
+      <c r="AF490" s="3"/>
+      <c r="AK490" s="3"/>
+      <c r="AP490" s="3"/>
+      <c r="AU490" s="3"/>
+    </row>
+    <row r="491" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H491" s="3"/>
+      <c r="M491" s="3"/>
+      <c r="Q491" s="3"/>
+      <c r="V491" s="3"/>
+      <c r="AA491" s="3"/>
+      <c r="AF491" s="3"/>
+      <c r="AK491" s="3"/>
+      <c r="AP491" s="3"/>
+      <c r="AU491" s="3"/>
+    </row>
+    <row r="492" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H492" s="3"/>
+      <c r="M492" s="3"/>
+      <c r="Q492" s="3"/>
+      <c r="V492" s="3"/>
+      <c r="AA492" s="3"/>
+      <c r="AF492" s="3"/>
+      <c r="AK492" s="3"/>
+      <c r="AP492" s="3"/>
+      <c r="AU492" s="3"/>
+    </row>
+    <row r="493" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H493" s="3"/>
+      <c r="M493" s="3"/>
+      <c r="Q493" s="3"/>
+      <c r="V493" s="3"/>
+      <c r="AA493" s="3"/>
+      <c r="AF493" s="3"/>
+      <c r="AK493" s="3"/>
+      <c r="AP493" s="3"/>
+      <c r="AU493" s="3"/>
+    </row>
+    <row r="494" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H494" s="3"/>
+      <c r="M494" s="3"/>
+      <c r="Q494" s="3"/>
+      <c r="V494" s="3"/>
+      <c r="AA494" s="3"/>
+      <c r="AF494" s="3"/>
+      <c r="AK494" s="3"/>
+      <c r="AP494" s="3"/>
+      <c r="AU494" s="3"/>
+    </row>
+    <row r="495" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H495" s="3"/>
+      <c r="M495" s="3"/>
+      <c r="Q495" s="3"/>
+      <c r="V495" s="3"/>
+      <c r="AA495" s="3"/>
+      <c r="AF495" s="3"/>
+      <c r="AK495" s="3"/>
+      <c r="AP495" s="3"/>
+      <c r="AU495" s="3"/>
+    </row>
+    <row r="496" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H496" s="3"/>
+      <c r="M496" s="3"/>
+      <c r="Q496" s="3"/>
+      <c r="V496" s="3"/>
+      <c r="AA496" s="3"/>
+      <c r="AF496" s="3"/>
+      <c r="AK496" s="3"/>
+      <c r="AP496" s="3"/>
+      <c r="AU496" s="3"/>
+    </row>
+    <row r="497" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H497" s="3"/>
+      <c r="M497" s="3"/>
+      <c r="Q497" s="3"/>
+      <c r="V497" s="3"/>
+      <c r="AA497" s="3"/>
+      <c r="AF497" s="3"/>
+      <c r="AK497" s="3"/>
+      <c r="AP497" s="3"/>
+      <c r="AU497" s="3"/>
+    </row>
+    <row r="498" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H498" s="3"/>
+      <c r="M498" s="3"/>
+      <c r="Q498" s="3"/>
+      <c r="V498" s="3"/>
+      <c r="AA498" s="3"/>
+      <c r="AF498" s="3"/>
+      <c r="AK498" s="3"/>
+      <c r="AP498" s="3"/>
+      <c r="AU498" s="3"/>
+    </row>
+    <row r="499" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H499" s="3"/>
+      <c r="M499" s="3"/>
+      <c r="Q499" s="3"/>
+      <c r="V499" s="3"/>
+      <c r="AA499" s="3"/>
+      <c r="AF499" s="3"/>
+      <c r="AK499" s="3"/>
+      <c r="AP499" s="3"/>
+      <c r="AU499" s="3"/>
+    </row>
+    <row r="500" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H500" s="3"/>
+      <c r="M500" s="3"/>
+      <c r="Q500" s="3"/>
+      <c r="V500" s="3"/>
+      <c r="AA500" s="3"/>
+      <c r="AF500" s="3"/>
+      <c r="AK500" s="3"/>
+      <c r="AP500" s="3"/>
+      <c r="AU500" s="3"/>
+    </row>
+    <row r="501" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H501" s="3"/>
+      <c r="M501" s="3"/>
+      <c r="Q501" s="3"/>
+      <c r="V501" s="3"/>
+      <c r="AA501" s="3"/>
+      <c r="AF501" s="3"/>
+      <c r="AK501" s="3"/>
+      <c r="AP501" s="3"/>
+      <c r="AU501" s="3"/>
+    </row>
+    <row r="502" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H502" s="3"/>
+      <c r="M502" s="3"/>
+      <c r="Q502" s="3"/>
+      <c r="V502" s="3"/>
+      <c r="AA502" s="3"/>
+      <c r="AF502" s="3"/>
+      <c r="AK502" s="3"/>
+      <c r="AP502" s="3"/>
+      <c r="AU502" s="3"/>
+    </row>
+    <row r="503" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H503" s="3"/>
+      <c r="M503" s="3"/>
+      <c r="Q503" s="3"/>
+      <c r="V503" s="3"/>
+      <c r="AA503" s="3"/>
+      <c r="AF503" s="3"/>
+      <c r="AK503" s="3"/>
+      <c r="AP503" s="3"/>
+      <c r="AU503" s="3"/>
+    </row>
+    <row r="504" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H504" s="3"/>
+      <c r="M504" s="3"/>
+      <c r="Q504" s="3"/>
+      <c r="V504" s="3"/>
+      <c r="AA504" s="3"/>
+      <c r="AF504" s="3"/>
+      <c r="AK504" s="3"/>
+      <c r="AP504" s="3"/>
+      <c r="AU504" s="3"/>
+    </row>
+    <row r="505" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H505" s="3"/>
+      <c r="M505" s="3"/>
+      <c r="Q505" s="3"/>
+      <c r="V505" s="3"/>
+      <c r="AA505" s="3"/>
+      <c r="AF505" s="3"/>
+      <c r="AK505" s="3"/>
+      <c r="AP505" s="3"/>
+      <c r="AU505" s="3"/>
+    </row>
+    <row r="506" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H506" s="3"/>
+      <c r="M506" s="3"/>
+      <c r="Q506" s="3"/>
+      <c r="V506" s="3"/>
+      <c r="AA506" s="3"/>
+      <c r="AF506" s="3"/>
+      <c r="AK506" s="3"/>
+      <c r="AP506" s="3"/>
+      <c r="AU506" s="3"/>
+    </row>
+    <row r="507" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H507" s="3"/>
+      <c r="M507" s="3"/>
+      <c r="Q507" s="3"/>
+      <c r="V507" s="3"/>
+      <c r="AA507" s="3"/>
+      <c r="AF507" s="3"/>
+      <c r="AK507" s="3"/>
+      <c r="AP507" s="3"/>
+      <c r="AU507" s="3"/>
+    </row>
+    <row r="508" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H508" s="3"/>
+      <c r="M508" s="3"/>
+      <c r="Q508" s="3"/>
+      <c r="V508" s="3"/>
+      <c r="AA508" s="3"/>
+      <c r="AF508" s="3"/>
+      <c r="AK508" s="3"/>
+      <c r="AP508" s="3"/>
+      <c r="AU508" s="3"/>
+    </row>
+    <row r="509" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H509" s="3"/>
+      <c r="M509" s="3"/>
+      <c r="Q509" s="3"/>
+      <c r="V509" s="3"/>
+      <c r="AA509" s="3"/>
+      <c r="AF509" s="3"/>
+      <c r="AK509" s="3"/>
+      <c r="AP509" s="3"/>
+      <c r="AU509" s="3"/>
+    </row>
+    <row r="510" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H510" s="3"/>
+      <c r="M510" s="3"/>
+      <c r="Q510" s="3"/>
+      <c r="V510" s="3"/>
+      <c r="AA510" s="3"/>
+      <c r="AF510" s="3"/>
+      <c r="AK510" s="3"/>
+      <c r="AP510" s="3"/>
+      <c r="AU510" s="3"/>
+    </row>
+    <row r="511" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H511" s="3"/>
+      <c r="M511" s="3"/>
+      <c r="Q511" s="3"/>
+      <c r="V511" s="3"/>
+      <c r="AA511" s="3"/>
+      <c r="AF511" s="3"/>
+      <c r="AK511" s="3"/>
+      <c r="AP511" s="3"/>
+      <c r="AU511" s="3"/>
+    </row>
+    <row r="512" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H512" s="3"/>
+      <c r="M512" s="3"/>
+      <c r="Q512" s="3"/>
+      <c r="V512" s="3"/>
+      <c r="AA512" s="3"/>
+      <c r="AF512" s="3"/>
+      <c r="AK512" s="3"/>
+      <c r="AP512" s="3"/>
+      <c r="AU512" s="3"/>
+    </row>
+    <row r="513" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H513" s="3"/>
+      <c r="M513" s="3"/>
+      <c r="Q513" s="3"/>
+      <c r="V513" s="3"/>
+      <c r="AA513" s="3"/>
+      <c r="AF513" s="3"/>
+      <c r="AK513" s="3"/>
+      <c r="AP513" s="3"/>
+      <c r="AU513" s="3"/>
+    </row>
+    <row r="514" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H514" s="3"/>
+      <c r="M514" s="3"/>
+      <c r="Q514" s="3"/>
+      <c r="V514" s="3"/>
+      <c r="AA514" s="3"/>
+      <c r="AF514" s="3"/>
+      <c r="AK514" s="3"/>
+      <c r="AP514" s="3"/>
+      <c r="AU514" s="3"/>
+    </row>
+    <row r="515" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H515" s="3"/>
+      <c r="M515" s="3"/>
+      <c r="Q515" s="3"/>
+      <c r="V515" s="3"/>
+      <c r="AA515" s="3"/>
+      <c r="AF515" s="3"/>
+      <c r="AK515" s="3"/>
+      <c r="AP515" s="3"/>
+      <c r="AU515" s="3"/>
+    </row>
+    <row r="516" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H516" s="3"/>
+      <c r="M516" s="3"/>
+      <c r="Q516" s="3"/>
+      <c r="V516" s="3"/>
+      <c r="AA516" s="3"/>
+      <c r="AF516" s="3"/>
+      <c r="AK516" s="3"/>
+      <c r="AP516" s="3"/>
+      <c r="AU516" s="3"/>
+    </row>
+    <row r="517" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H517" s="3"/>
+      <c r="M517" s="3"/>
+      <c r="Q517" s="3"/>
+      <c r="V517" s="3"/>
+      <c r="AA517" s="3"/>
+      <c r="AF517" s="3"/>
+      <c r="AK517" s="3"/>
+      <c r="AP517" s="3"/>
+      <c r="AU517" s="3"/>
+    </row>
+    <row r="518" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H518" s="3"/>
+      <c r="M518" s="3"/>
+      <c r="Q518" s="3"/>
+      <c r="V518" s="3"/>
+      <c r="AA518" s="3"/>
+      <c r="AF518" s="3"/>
+      <c r="AK518" s="3"/>
+      <c r="AP518" s="3"/>
+      <c r="AU518" s="3"/>
+    </row>
+    <row r="519" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H519" s="3"/>
+      <c r="M519" s="3"/>
+      <c r="Q519" s="3"/>
+      <c r="V519" s="3"/>
+      <c r="AA519" s="3"/>
+      <c r="AF519" s="3"/>
+      <c r="AK519" s="3"/>
+      <c r="AP519" s="3"/>
+      <c r="AU519" s="3"/>
+    </row>
+    <row r="520" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H520" s="3"/>
+      <c r="M520" s="3"/>
+      <c r="Q520" s="3"/>
+      <c r="V520" s="3"/>
+      <c r="AA520" s="3"/>
+      <c r="AF520" s="3"/>
+      <c r="AK520" s="3"/>
+      <c r="AP520" s="3"/>
+      <c r="AU520" s="3"/>
+    </row>
+    <row r="521" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H521" s="3"/>
+      <c r="M521" s="3"/>
+      <c r="Q521" s="3"/>
+      <c r="V521" s="3"/>
+      <c r="AA521" s="3"/>
+      <c r="AF521" s="3"/>
+      <c r="AK521" s="3"/>
+      <c r="AP521" s="3"/>
+      <c r="AU521" s="3"/>
+    </row>
+    <row r="522" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H522" s="3"/>
+      <c r="M522" s="3"/>
+      <c r="Q522" s="3"/>
+      <c r="V522" s="3"/>
+      <c r="AA522" s="3"/>
+      <c r="AF522" s="3"/>
+      <c r="AK522" s="3"/>
+      <c r="AP522" s="3"/>
+      <c r="AU522" s="3"/>
+    </row>
+    <row r="523" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H523" s="3"/>
+      <c r="M523" s="3"/>
+      <c r="Q523" s="3"/>
+      <c r="V523" s="3"/>
+      <c r="AA523" s="3"/>
+      <c r="AF523" s="3"/>
+      <c r="AK523" s="3"/>
+      <c r="AP523" s="3"/>
+      <c r="AU523" s="3"/>
+    </row>
+    <row r="524" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H524" s="3"/>
+      <c r="M524" s="3"/>
+      <c r="Q524" s="3"/>
+      <c r="V524" s="3"/>
+      <c r="AA524" s="3"/>
+      <c r="AF524" s="3"/>
+      <c r="AK524" s="3"/>
+      <c r="AP524" s="3"/>
+      <c r="AU524" s="3"/>
+    </row>
+    <row r="525" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H525" s="3"/>
+      <c r="M525" s="3"/>
+      <c r="Q525" s="3"/>
+      <c r="V525" s="3"/>
+      <c r="AA525" s="3"/>
+      <c r="AF525" s="3"/>
+      <c r="AK525" s="3"/>
+      <c r="AP525" s="3"/>
+      <c r="AU525" s="3"/>
+    </row>
+    <row r="526" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H526" s="3"/>
+      <c r="M526" s="3"/>
+      <c r="Q526" s="3"/>
+      <c r="V526" s="3"/>
+      <c r="AA526" s="3"/>
+      <c r="AF526" s="3"/>
+      <c r="AK526" s="3"/>
+      <c r="AP526" s="3"/>
+      <c r="AU526" s="3"/>
+    </row>
+    <row r="527" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H527" s="3"/>
+      <c r="M527" s="3"/>
+      <c r="Q527" s="3"/>
+      <c r="V527" s="3"/>
+      <c r="AA527" s="3"/>
+      <c r="AF527" s="3"/>
+      <c r="AK527" s="3"/>
+      <c r="AP527" s="3"/>
+      <c r="AU527" s="3"/>
+    </row>
+    <row r="528" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H528" s="3"/>
+      <c r="M528" s="3"/>
+      <c r="Q528" s="3"/>
+      <c r="V528" s="3"/>
+      <c r="AA528" s="3"/>
+      <c r="AF528" s="3"/>
+      <c r="AK528" s="3"/>
+      <c r="AP528" s="3"/>
+      <c r="AU528" s="3"/>
+    </row>
+    <row r="529" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H529" s="3"/>
+      <c r="M529" s="3"/>
+      <c r="Q529" s="3"/>
+      <c r="V529" s="3"/>
+      <c r="AA529" s="3"/>
+      <c r="AF529" s="3"/>
+      <c r="AK529" s="3"/>
+      <c r="AP529" s="3"/>
+      <c r="AU529" s="3"/>
+    </row>
+    <row r="530" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H530" s="3"/>
+      <c r="M530" s="3"/>
+      <c r="Q530" s="3"/>
+      <c r="V530" s="3"/>
+      <c r="AA530" s="3"/>
+      <c r="AF530" s="3"/>
+      <c r="AK530" s="3"/>
+      <c r="AP530" s="3"/>
+      <c r="AU530" s="3"/>
+    </row>
+    <row r="531" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H531" s="3"/>
+      <c r="M531" s="3"/>
+      <c r="Q531" s="3"/>
+      <c r="V531" s="3"/>
+      <c r="AA531" s="3"/>
+      <c r="AF531" s="3"/>
+      <c r="AK531" s="3"/>
+      <c r="AP531" s="3"/>
+      <c r="AU531" s="3"/>
+    </row>
+    <row r="532" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H532" s="3"/>
+      <c r="M532" s="3"/>
+      <c r="Q532" s="3"/>
+      <c r="V532" s="3"/>
+      <c r="AA532" s="3"/>
+      <c r="AF532" s="3"/>
+      <c r="AK532" s="3"/>
+      <c r="AP532" s="3"/>
+      <c r="AU532" s="3"/>
+    </row>
+    <row r="533" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H533" s="3"/>
+      <c r="M533" s="3"/>
+      <c r="Q533" s="3"/>
+      <c r="V533" s="3"/>
+      <c r="AA533" s="3"/>
+      <c r="AF533" s="3"/>
+      <c r="AK533" s="3"/>
+      <c r="AP533" s="3"/>
+      <c r="AU533" s="3"/>
+    </row>
+    <row r="534" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H534" s="3"/>
+      <c r="M534" s="3"/>
+      <c r="Q534" s="3"/>
+      <c r="V534" s="3"/>
+      <c r="AA534" s="3"/>
+      <c r="AF534" s="3"/>
+      <c r="AK534" s="3"/>
+      <c r="AP534" s="3"/>
+      <c r="AU534" s="3"/>
+    </row>
+    <row r="535" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H535" s="3"/>
+      <c r="M535" s="3"/>
+      <c r="Q535" s="3"/>
+      <c r="V535" s="3"/>
+      <c r="AA535" s="3"/>
+      <c r="AF535" s="3"/>
+      <c r="AK535" s="3"/>
+      <c r="AP535" s="3"/>
+      <c r="AU535" s="3"/>
+    </row>
+    <row r="536" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H536" s="3"/>
+      <c r="M536" s="3"/>
+      <c r="Q536" s="3"/>
+      <c r="V536" s="3"/>
+      <c r="AA536" s="3"/>
+      <c r="AF536" s="3"/>
+      <c r="AK536" s="3"/>
+      <c r="AP536" s="3"/>
+      <c r="AU536" s="3"/>
+    </row>
+    <row r="537" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H537" s="3"/>
+      <c r="M537" s="3"/>
+      <c r="Q537" s="3"/>
+      <c r="V537" s="3"/>
+      <c r="AA537" s="3"/>
+      <c r="AF537" s="3"/>
+      <c r="AK537" s="3"/>
+      <c r="AP537" s="3"/>
+      <c r="AU537" s="3"/>
+    </row>
+    <row r="538" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H538" s="3"/>
+      <c r="M538" s="3"/>
+      <c r="Q538" s="3"/>
+      <c r="V538" s="3"/>
+      <c r="AA538" s="3"/>
+      <c r="AF538" s="3"/>
+      <c r="AK538" s="3"/>
+      <c r="AP538" s="3"/>
+      <c r="AU538" s="3"/>
+    </row>
+    <row r="539" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H539" s="3"/>
+      <c r="M539" s="3"/>
+      <c r="Q539" s="3"/>
+      <c r="V539" s="3"/>
+      <c r="AA539" s="3"/>
+      <c r="AF539" s="3"/>
+      <c r="AK539" s="3"/>
+      <c r="AP539" s="3"/>
+      <c r="AU539" s="3"/>
+    </row>
+    <row r="540" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H540" s="3"/>
+      <c r="M540" s="3"/>
+      <c r="Q540" s="3"/>
+      <c r="V540" s="3"/>
+      <c r="AA540" s="3"/>
+      <c r="AF540" s="3"/>
+      <c r="AK540" s="3"/>
+      <c r="AP540" s="3"/>
+      <c r="AU540" s="3"/>
+    </row>
+    <row r="541" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H541" s="3"/>
+      <c r="M541" s="3"/>
+      <c r="Q541" s="3"/>
+      <c r="V541" s="3"/>
+      <c r="AA541" s="3"/>
+      <c r="AF541" s="3"/>
+      <c r="AK541" s="3"/>
+      <c r="AP541" s="3"/>
+      <c r="AU541" s="3"/>
+    </row>
+    <row r="542" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H542" s="3"/>
+      <c r="M542" s="3"/>
+      <c r="Q542" s="3"/>
+      <c r="V542" s="3"/>
+      <c r="AA542" s="3"/>
+      <c r="AF542" s="3"/>
+      <c r="AK542" s="3"/>
+      <c r="AP542" s="3"/>
+      <c r="AU542" s="3"/>
+    </row>
+    <row r="543" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H543" s="3"/>
+      <c r="M543" s="3"/>
+      <c r="Q543" s="3"/>
+      <c r="V543" s="3"/>
+      <c r="AA543" s="3"/>
+      <c r="AF543" s="3"/>
+      <c r="AK543" s="3"/>
+      <c r="AP543" s="3"/>
+      <c r="AU543" s="3"/>
+    </row>
+    <row r="544" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H544" s="3"/>
+      <c r="M544" s="3"/>
+      <c r="Q544" s="3"/>
+      <c r="V544" s="3"/>
+      <c r="AA544" s="3"/>
+      <c r="AF544" s="3"/>
+      <c r="AK544" s="3"/>
+      <c r="AP544" s="3"/>
+      <c r="AU544" s="3"/>
+    </row>
+    <row r="545" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H545" s="3"/>
+      <c r="M545" s="3"/>
+      <c r="Q545" s="3"/>
+      <c r="V545" s="3"/>
+      <c r="AA545" s="3"/>
+      <c r="AF545" s="3"/>
+      <c r="AK545" s="3"/>
+      <c r="AP545" s="3"/>
+      <c r="AU545" s="3"/>
+    </row>
+    <row r="546" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H546" s="3"/>
+      <c r="M546" s="3"/>
+      <c r="Q546" s="3"/>
+      <c r="V546" s="3"/>
+      <c r="AA546" s="3"/>
+      <c r="AF546" s="3"/>
+      <c r="AK546" s="3"/>
+      <c r="AP546" s="3"/>
+      <c r="AU546" s="3"/>
+    </row>
+    <row r="547" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H547" s="3"/>
+      <c r="M547" s="3"/>
+      <c r="Q547" s="3"/>
+      <c r="V547" s="3"/>
+      <c r="AA547" s="3"/>
+      <c r="AF547" s="3"/>
+      <c r="AK547" s="3"/>
+      <c r="AP547" s="3"/>
+      <c r="AU547" s="3"/>
+    </row>
+    <row r="548" spans="8:47" x14ac:dyDescent="0.15">
+      <c r="H548" s="3"/>
+      <c r="M548" s="3"/>
+      <c r="Q548" s="3"/>
+      <c r="V548" s="3"/>
+      <c r="AA548" s="3"/>
+      <c r="AF548" s="3"/>
+      <c r="AK548" s="3"/>
+      <c r="AP548" s="3"/>
+      <c r="AU548" s="3"/>
+    </row>
+  </sheetData>
+  <mergeCells count="28">
+    <mergeCell ref="D39:D41"/>
+    <mergeCell ref="D52:D53"/>
+    <mergeCell ref="D42:D43"/>
+    <mergeCell ref="D44:D45"/>
+    <mergeCell ref="D46:D47"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="D33:D34"/>
+    <mergeCell ref="D37:D38"/>
+    <mergeCell ref="D54:D55"/>
+    <mergeCell ref="D56:D57"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:D4"/>
+    <mergeCell ref="D35:D36"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="D25:D26"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="31" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
 </file>
--- a/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
+++ b/뷰어 샘플 개발 일정표_윤은지_250916.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\sample\2\Qt3DViewer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1056BD-9380-44A3-887C-97C1E55549FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B366903-AFC7-4849-A682-4A3F9BE6A0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="3990" windowWidth="39510" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8700" yWindow="3990" windowWidth="34935" windowHeight="21540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Viewer 샘플" sheetId="8" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="71">
   <si>
     <t>구 분</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -302,6 +302,10 @@
   </si>
   <si>
     <t>11월 28일</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>11월 19일</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -5858,11 +5862,13 @@
       <c r="AN55" s="88"/>
       <c r="AO55" s="88"/>
       <c r="AP55" s="86"/>
-      <c r="AQ55" s="21"/>
-      <c r="AR55" s="18"/>
-      <c r="AS55" s="18"/>
-      <c r="AT55" s="18"/>
-      <c r="AU55" s="26"/>
+      <c r="AQ55" s="87"/>
+      <c r="AR55" s="88"/>
+      <c r="AS55" s="88"/>
+      <c r="AT55" s="88"/>
+      <c r="AU55" s="79" t="s">
+        <v>70</v>
+      </c>
       <c r="AY55" s="3"/>
       <c r="BD55" s="3"/>
       <c r="BH55" s="3"/>
@@ -5971,16 +5977,18 @@
       <c r="AI57" s="13"/>
       <c r="AJ57" s="13"/>
       <c r="AK57" s="14"/>
-      <c r="AL57" s="21"/>
-      <c r="AM57" s="18"/>
-      <c r="AN57" s="18"/>
-      <c r="AO57" s="25"/>
-      <c r="AP57" s="26"/>
-      <c r="AQ57" s="21"/>
-      <c r="AR57" s="18"/>
-      <c r="AS57" s="18"/>
-      <c r="AT57" s="18"/>
-      <c r="AU57" s="26"/>
+      <c r="AL57" s="87"/>
+      <c r="AM57" s="88"/>
+      <c r="AN57" s="88"/>
+      <c r="AO57" s="88"/>
+      <c r="AP57" s="86"/>
+      <c r="AQ57" s="87"/>
+      <c r="AR57" s="88"/>
+      <c r="AS57" s="88"/>
+      <c r="AT57" s="88"/>
+      <c r="AU57" s="79" t="s">
+        <v>70</v>
+      </c>
       <c r="AY57" s="3"/>
       <c r="BD57" s="3"/>
       <c r="BH57" s="3"/>
